--- a/01_組織工作盤查.xlsx
+++ b/01_組織工作盤查.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Development\LeaderMethodology\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEB6B5AC-5453-4891-9260-3491C4144CB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53DBD9E0-C381-4615-96AA-A612115E9028}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" activeTab="1" xr2:uid="{6274A289-9C1F-4174-8A94-9BA38FCDDB48}"/>
   </bookViews>
@@ -20,8 +20,12 @@
     <sheet name="3.製程設備&amp;機台資訊" sheetId="5" r:id="rId5"/>
     <sheet name="4.生產計劃Schedule" sheetId="8" r:id="rId6"/>
     <sheet name="A.製程 Recipe 保存、資訊流、Server 架構、資訊" sheetId="9" r:id="rId7"/>
-    <sheet name="X.Sample" sheetId="7" r:id="rId8"/>
-    <sheet name="TB_Check" sheetId="4" r:id="rId9"/>
+    <sheet name="B.製造 CIM" sheetId="10" r:id="rId8"/>
+    <sheet name="C.製程動作分析盤點" sheetId="11" r:id="rId9"/>
+    <sheet name="C.Chart" sheetId="14" r:id="rId10"/>
+    <sheet name="X.Sample" sheetId="7" r:id="rId11"/>
+    <sheet name="TB_Check" sheetId="4" r:id="rId12"/>
+    <sheet name="TB_製程動作分析盤點" sheetId="12" r:id="rId13"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,8 +47,45 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Cheng Ting Tsai</author>
+  </authors>
+  <commentList>
+    <comment ref="A2" authorId="0" shapeId="0" xr:uid="{0BF312DB-184D-40CB-BC72-BBF1D83FFAE4}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="20"/>
+            <color indexed="81"/>
+            <rFont val="微軟正黑體"/>
+            <family val="2"/>
+            <charset val="136"/>
+          </rPr>
+          <t>Cheng Ting Tsai:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="20"/>
+            <color indexed="81"/>
+            <rFont val="微軟正黑體"/>
+            <family val="2"/>
+            <charset val="136"/>
+          </rPr>
+          <t xml:space="preserve">
+1.請拆解成單一動作
+2.請在Note欄位說明及提供:目前生產中做常遇到的瓶頸</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="156">
   <si>
     <t>文件名稱/Document</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -411,12 +452,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>請說明及提供:企業內部與製造生產有關系統(MES、SAP、ERP等) Server架構及管理方式
-(包含使用 VM? 叢集?異地備援?機房?規格?RAID?)
-有架構圖最好</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>請說明及提供:企業內部 Recipe檔案、機台 Log 等關鍵製程檔案資訊之保存方式
 (包含使用Synology?使用Azure?叢集、異地備援、防竄改、版本控制)
 有架構圖最好</t>
@@ -456,6 +491,545 @@
   </si>
   <si>
     <t>新產品及機台導入(For 製造產品、設備單位Owner)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>請說明及提供:企業內部與製造生產有關系統(MES、SAP、ERP等) Server架構及管理方式
+(包含使用 VM? 叢集?HAProxy?異地備援?機房?規格?RAID?)
+有架構圖最好</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>請說明及提供:廠內各製程或產品使用之搬運/移動/配送方式
+(包含身分綁定、身分確認、命名規則、分配方式)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>請說明及提供:廠內各製程使用之容器、包材、箱子、貨架的管理方式
+(包含身分綁定、身分確認、命名規則、分配方式)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>請說明及提供:廠內各製程或產品使用之材料、配件、治具
+(包含身分綁定、身分確認、命名規則、分配方式)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>請說明及提供:廠內製程參數/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei UI"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>數據收集方式及卡控方式</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei Light"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t xml:space="preserve">
+(包含客戶Review時的資訊)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>請說明及提供:廠內各製程或產品之報表、圖表
+(包含誰看、怎麼呈現、怎麼推播、怎麼提供給預期使用者、怎麼管理)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>請說明及提供:廠內客戶工單下線、B2B、帳目交握等架構
+(包含觸發時機、觸發方法、邏輯、格式)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>請說明及提供:客戶要求的產出、良率相關之報表、圖表
+(包含客戶的誰看、何時提供、怎麼呈現、怎麼配送、管制哪些項目)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>請說明及提供:廠內製程 CIM/Automation 架構及使用手冊
+(包含SECS/GEM、WebServcie、MQ等)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>請說明及提供:廠內各製程或產品使用之 Recipe 配方
+(包含卡控、上下限、配方設置自動化、SetGolden、GoldenReicpe管理)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>請說明及提供:廠內各製程或產品生產之流程履歷
+(包含進站、近機、出站、出機、重工、報廢、入庫、出廠、材料用量、耗材用量、能源度數、水量等、流程前後關係)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>線別</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>站點</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>作業動作</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>動作</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>管制機制
+(若有請填寫規格編號及章節；反之為NA)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>短期對策</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>長期對策</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Risk Level
+高(錯\漏\混)
+中(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei UI"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>外觀不符\帳料不符</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei Light"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>)
+低(資料\動作不符)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>高</t>
+  </si>
+  <si>
+    <t>高</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>低</t>
+  </si>
+  <si>
+    <t>低</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>廠內系統</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>人檢</t>
+  </si>
+  <si>
+    <t>人檢</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>機台設備</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>卡控類型
+(廠內系統/機台設備/人檢/客戶)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>客戶</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>範例A line</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>測試</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>測試前</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>人員至待測區取貨</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>動作描述</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>動作風險</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>混料</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>須由全能工在備料前確認後在流程卡上簽名</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自動搬運</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>動作類型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>加工</t>
+  </si>
+  <si>
+    <t>加工</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>搬運</t>
+  </si>
+  <si>
+    <t>搬運</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>儲存</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>停滯</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>檢查</t>
+  </si>
+  <si>
+    <t>檢查</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>等待</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>取貨時人員自行檢查</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>確認箱子內產品與Schedule工單、數量、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei UI"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>測試站點一致</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>混料/資料不符/數量不符</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei Light"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>混料</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei Light"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>資料不符</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei Light"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>數量不符</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei Light"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>混料</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei Light"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>資料不符</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>資料不符</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei Light"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>資料不符</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei Light"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>數量不符</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>數量不符</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>錯程式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>錯流程卡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>好壞品混</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GAP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>資料缺少</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>報表格式錯誤</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>測試中</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>起測時間紀錄</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>遺忘</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>遺忘</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>資料缺少</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>遺忘/資料缺少</t>
+  </si>
+  <si>
+    <t>人員自行提醒自己(人體鬧鐘)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>買鬧鐘給人員提醒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Automation+2DID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Automation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>測試中每隔30分鐘紀錄產出資訊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>偵測風險 
+高(全廠內無法偵測)
+中(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei UI"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>下一站可以</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei Light"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>偵測)
+低(當站可以偵測)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Risk Level
+高(錯\漏\混)
+中(外觀不符\帳料不符)
+低(資料\動作不符)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>偵測風險
+高(全廠內無法偵測)
+中(下一站可以偵測)
+低(當站可以偵測)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Note</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -463,7 +1037,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <fonts count="18">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -528,8 +1102,72 @@
       <family val="2"/>
       <charset val="136"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="細明體"/>
+      <family val="3"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Microsoft JhengHei"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Microsoft JhengHei Light"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="細明體"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="微軟正黑體"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="微軟正黑體"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color indexed="81"/>
+      <name val="微軟正黑體"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="20"/>
+      <color indexed="81"/>
+      <name val="微軟正黑體"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -539,6 +1177,30 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00FFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF8000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE40A4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -572,7 +1234,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -596,12 +1258,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
@@ -645,21 +1301,147 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="14" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF8000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDE40A4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FF00FFFF"/>
+      <color rgb="FFFF8000"/>
+      <color rgb="FFDE40A4"/>
+      <color rgb="FFFF0000"/>
+      <color rgb="FFFF0066"/>
+      <color rgb="FFFF6600"/>
+      <color rgb="FFFFCC66"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -669,6 +1451,2057 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-TW"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:view3D>
+      <c:rotX val="50"/>
+      <c:rotY val="0"/>
+      <c:depthPercent val="100"/>
+      <c:rAngAx val="0"/>
+    </c:view3D>
+    <c:floor>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:floor>
+    <c:sideWall>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:sideWall>
+    <c:backWall>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:backWall>
+    <c:plotArea>
+      <c:layout/>
+      <c:pie3DChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'C.Chart'!$A$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>動作</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="20000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:sp3d/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000004-F24B-4219-8460-0F96122E9466}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="FF0066"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="20000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:sp3d/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-F24B-4219-8460-0F96122E9466}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="FF8000"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="20000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:sp3d/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000006-F24B-4219-8460-0F96122E9466}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dLbls>
+            <c:spPr>
+              <a:pattFill prst="pct75">
+                <a:fgClr>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:fgClr>
+                <a:bgClr>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:bgClr>
+              </a:pattFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="40000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="lt1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="zh-TW"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="1"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="1"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>('C.Chart'!$B$2,'C.Chart'!$D$2,'C.Chart'!$F$2)</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>高</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>中</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>低</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>('C.Chart'!$C$3,'C.Chart'!$E$3,'C.Chart'!$G$3)</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-F24B-4219-8460-0F96122E9466}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="ctr"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="1"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="0"/>
+        </c:dLbls>
+      </c:pie3DChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="39000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-TW"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="0"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="25000"/>
+          <a:lumOff val="75000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="zh-TW"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-TW"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:view3D>
+      <c:rotX val="50"/>
+      <c:rotY val="0"/>
+      <c:depthPercent val="100"/>
+      <c:rAngAx val="0"/>
+    </c:view3D>
+    <c:floor>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:floor>
+    <c:sideWall>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:sideWall>
+    <c:backWall>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:backWall>
+    <c:plotArea>
+      <c:layout/>
+      <c:pie3DChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'C.Chart'!$A$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>動作</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="20000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:sp3d/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-F3AE-4878-A173-1C825F3EF3AB}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="DE40A4"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="20000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:sp3d/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-F3AE-4878-A173-1C825F3EF3AB}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="FF8000"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="20000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:sp3d/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-F3AE-4878-A173-1C825F3EF3AB}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dLbls>
+            <c:spPr>
+              <a:pattFill prst="pct75">
+                <a:fgClr>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:fgClr>
+                <a:bgClr>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:bgClr>
+              </a:pattFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="40000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="lt1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="zh-TW"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="1"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="1"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>('C.Chart'!$B$2,'C.Chart'!$D$2,'C.Chart'!$F$2)</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>高</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>中</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>低</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>('C.Chart'!$I$3,'C.Chart'!$K$3,'C.Chart'!$M$3)</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-F3AE-4878-A173-1C825F3EF3AB}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="ctr"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="1"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="0"/>
+        </c:dLbls>
+      </c:pie3DChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="39000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-TW"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="0"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="25000"/>
+          <a:lumOff val="75000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="zh-TW"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="264">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200" cap="all" baseline="0"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:gradFill flip="none" rotWithShape="1">
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="lt1"/>
+          </a:gs>
+          <a:gs pos="39000">
+            <a:schemeClr val="lt1"/>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="lt1">
+              <a:lumMod val="75000"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:path path="circle">
+          <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+        </a:path>
+        <a:tileRect/>
+      </a:gradFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:pattFill prst="pct75">
+        <a:fgClr>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:fgClr>
+        <a:bgClr>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:bgClr>
+      </a:pattFill>
+      <a:effectLst>
+        <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="40000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:spPr>
+    <cs:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:pattFill prst="pct75">
+        <a:fgClr>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:fgClr>
+        <a:bgClr>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:bgClr>
+      </a:pattFill>
+      <a:effectLst>
+        <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="40000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:spPr>
+    <cs:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:effectLst>
+        <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="20000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:effectLst>
+        <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="20000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="31750" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:alpha val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr">
+          <a:alpha val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="50000"/>
+          <a:lumOff val="50000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="100000">
+              <a:schemeClr val="dk1">
+                <a:lumMod val="95000"/>
+                <a:lumOff val="5000"/>
+                <a:alpha val="42000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="0">
+              <a:schemeClr val="lt1">
+                <a:lumMod val="75000"/>
+                <a:alpha val="36000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="100000">
+              <a:schemeClr val="dk1">
+                <a:lumMod val="95000"/>
+                <a:lumOff val="5000"/>
+                <a:alpha val="42000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="0">
+              <a:schemeClr val="lt1">
+                <a:lumMod val="75000"/>
+                <a:alpha val="36000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1">
+          <a:lumMod val="95000"/>
+          <a:alpha val="39000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="31750" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1800" b="1" kern="1200" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="264">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200" cap="all" baseline="0"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:gradFill flip="none" rotWithShape="1">
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="lt1"/>
+          </a:gs>
+          <a:gs pos="39000">
+            <a:schemeClr val="lt1"/>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="lt1">
+              <a:lumMod val="75000"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:path path="circle">
+          <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+        </a:path>
+        <a:tileRect/>
+      </a:gradFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:pattFill prst="pct75">
+        <a:fgClr>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:fgClr>
+        <a:bgClr>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:bgClr>
+      </a:pattFill>
+      <a:effectLst>
+        <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="40000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:spPr>
+    <cs:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:pattFill prst="pct75">
+        <a:fgClr>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:fgClr>
+        <a:bgClr>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:bgClr>
+      </a:pattFill>
+      <a:effectLst>
+        <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="40000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:spPr>
+    <cs:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:effectLst>
+        <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="20000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:effectLst>
+        <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="20000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="31750" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:alpha val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr">
+          <a:alpha val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="50000"/>
+          <a:lumOff val="50000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="100000">
+              <a:schemeClr val="dk1">
+                <a:lumMod val="95000"/>
+                <a:lumOff val="5000"/>
+                <a:alpha val="42000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="0">
+              <a:schemeClr val="lt1">
+                <a:lumMod val="75000"/>
+                <a:alpha val="36000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="100000">
+              <a:schemeClr val="dk1">
+                <a:lumMod val="95000"/>
+                <a:lumOff val="5000"/>
+                <a:alpha val="42000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="0">
+              <a:schemeClr val="lt1">
+                <a:lumMod val="75000"/>
+                <a:alpha val="36000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1">
+          <a:lumMod val="95000"/>
+          <a:alpha val="39000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="31750" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1800" b="1" kern="1200" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>68580</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>137160</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>845820</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>255270</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="圖表 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CA20667E-DD1D-6395-D1DC-3F0C048FFD14}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>22860</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>137160</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>137160</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>213360</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="7" name="圖表 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{76DB6851-2866-40C1-8E6C-1E4E396ABD60}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1081,6 +3914,497 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF825C7D-8759-41E7-B6E6-4A099ED2B7DC}">
+  <sheetPr>
+    <tabColor rgb="FFFFFF00"/>
+  </sheetPr>
+  <dimension ref="A1:AC14"/>
+  <sheetFormatPr defaultColWidth="3.6640625" defaultRowHeight="21"/>
+  <cols>
+    <col min="1" max="1" width="7.77734375" style="39" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="3.5546875" style="22" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" style="22" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="3.5546875" style="39" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.44140625" style="40" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="3.5546875" style="40" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.44140625" style="40" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="3.5546875" style="22" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.44140625" style="22" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="3.5546875" style="22" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.44140625" style="22" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="3.5546875" style="22" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.44140625" style="22" customWidth="1"/>
+    <col min="14" max="14" width="7.77734375" style="22" bestFit="1" customWidth="1"/>
+    <col min="15" max="24" width="3.6640625" style="22"/>
+    <col min="25" max="25" width="11.6640625" style="22" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="25.109375" style="22" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="3.5546875" style="39" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="12.44140625" style="40" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="3.6640625" style="22"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:29" ht="66.599999999999994" customHeight="1">
+      <c r="A1" s="42" t="s">
+        <v>92</v>
+      </c>
+      <c r="B1" s="43" t="s">
+        <v>154</v>
+      </c>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43" t="s">
+        <v>153</v>
+      </c>
+      <c r="I1" s="43"/>
+      <c r="J1" s="43"/>
+      <c r="K1" s="43"/>
+      <c r="L1" s="43"/>
+      <c r="M1" s="43"/>
+    </row>
+    <row r="2" spans="1:29" ht="15.6">
+      <c r="A2" s="42"/>
+      <c r="B2" s="46" t="s">
+        <v>98</v>
+      </c>
+      <c r="C2" s="46"/>
+      <c r="D2" s="47" t="s">
+        <v>99</v>
+      </c>
+      <c r="E2" s="47"/>
+      <c r="F2" s="48" t="s">
+        <v>101</v>
+      </c>
+      <c r="G2" s="48"/>
+      <c r="H2" s="46" t="s">
+        <v>98</v>
+      </c>
+      <c r="I2" s="46"/>
+      <c r="J2" s="47" t="s">
+        <v>99</v>
+      </c>
+      <c r="K2" s="47"/>
+      <c r="L2" s="48" t="s">
+        <v>101</v>
+      </c>
+      <c r="M2" s="48"/>
+      <c r="AA2" s="22"/>
+      <c r="AB2" s="22"/>
+    </row>
+    <row r="3" spans="1:29">
+      <c r="A3" s="44">
+        <f>COUNT('C.製程動作分析盤點'!A:A)</f>
+        <v>4</v>
+      </c>
+      <c r="B3" s="44">
+        <f>COUNTIF('C.製程動作分析盤點'!J:J,"高")</f>
+        <v>0</v>
+      </c>
+      <c r="C3" s="45">
+        <f>B3/$A$3</f>
+        <v>0</v>
+      </c>
+      <c r="D3" s="44">
+        <f>COUNTIF('C.製程動作分析盤點'!J:J,"中")</f>
+        <v>0</v>
+      </c>
+      <c r="E3" s="45">
+        <f>D3/$A$3</f>
+        <v>0</v>
+      </c>
+      <c r="F3" s="44">
+        <f>COUNTIF('C.製程動作分析盤點'!J:J,"低")</f>
+        <v>4</v>
+      </c>
+      <c r="G3" s="45">
+        <f>F3/$A$3</f>
+        <v>1</v>
+      </c>
+      <c r="H3" s="44">
+        <f>COUNTIF('C.製程動作分析盤點'!K:K,"高")</f>
+        <v>2</v>
+      </c>
+      <c r="I3" s="45">
+        <f>H3/$A$3</f>
+        <v>0.5</v>
+      </c>
+      <c r="J3" s="44">
+        <f>COUNTIF('C.製程動作分析盤點'!K:K,"中")</f>
+        <v>0</v>
+      </c>
+      <c r="K3" s="45">
+        <f>J3/$A$3</f>
+        <v>0</v>
+      </c>
+      <c r="L3" s="44">
+        <f>COUNTIF('C.製程動作分析盤點'!K:K,"低")</f>
+        <v>2</v>
+      </c>
+      <c r="M3" s="45">
+        <f>L3/$A$3</f>
+        <v>0.5</v>
+      </c>
+      <c r="AA3" s="22"/>
+      <c r="AB3" s="22"/>
+    </row>
+    <row r="4" spans="1:29">
+      <c r="B4" s="41"/>
+      <c r="C4" s="41"/>
+      <c r="F4" s="39"/>
+      <c r="G4" s="39"/>
+      <c r="AA4" s="22"/>
+      <c r="AB4" s="22"/>
+    </row>
+    <row r="5" spans="1:29">
+      <c r="B5" s="41"/>
+      <c r="C5" s="41"/>
+      <c r="F5" s="39"/>
+      <c r="G5" s="39"/>
+      <c r="AA5" s="22"/>
+      <c r="AB5" s="22"/>
+    </row>
+    <row r="6" spans="1:29">
+      <c r="B6" s="39"/>
+      <c r="C6" s="39"/>
+      <c r="E6" s="39"/>
+      <c r="F6" s="39"/>
+      <c r="G6" s="39"/>
+      <c r="AA6" s="22"/>
+      <c r="AB6" s="22"/>
+    </row>
+    <row r="7" spans="1:29">
+      <c r="B7" s="39"/>
+      <c r="C7" s="39"/>
+      <c r="E7" s="39"/>
+      <c r="F7" s="39"/>
+      <c r="G7" s="39"/>
+      <c r="Y7" s="39"/>
+      <c r="Z7" s="39"/>
+      <c r="AB7" s="39"/>
+      <c r="AC7" s="39"/>
+    </row>
+    <row r="11" spans="1:29">
+      <c r="F11" s="22"/>
+      <c r="G11" s="22"/>
+    </row>
+    <row r="12" spans="1:29">
+      <c r="F12" s="22"/>
+      <c r="G12" s="22"/>
+    </row>
+    <row r="13" spans="1:29">
+      <c r="F13" s="22"/>
+      <c r="G13" s="22"/>
+    </row>
+    <row r="14" spans="1:29">
+      <c r="F14" s="22"/>
+      <c r="G14" s="22"/>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="H1:M1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="B1:G1"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A41FB531-20B2-41BA-83FF-D38C4F8DED83}">
+  <sheetPr>
+    <tabColor rgb="FFFFFF00"/>
+  </sheetPr>
+  <dimension ref="A1:C13"/>
+  <sheetFormatPr defaultRowHeight="15.6"/>
+  <cols>
+    <col min="1" max="1" width="7.5546875" style="21" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="97" style="19" customWidth="1"/>
+    <col min="3" max="3" width="7.88671875" style="21" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.88671875" style="19"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="18" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="16">
+        <v>1</v>
+      </c>
+      <c r="B2" s="20"/>
+      <c r="C2" s="18"/>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="16">
+        <v>2</v>
+      </c>
+      <c r="B3" s="20"/>
+      <c r="C3" s="18"/>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="16">
+        <v>3</v>
+      </c>
+      <c r="B4" s="20"/>
+      <c r="C4" s="18"/>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="16">
+        <v>4</v>
+      </c>
+      <c r="B5" s="20"/>
+      <c r="C5" s="18"/>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="16">
+        <v>5</v>
+      </c>
+      <c r="B6" s="20"/>
+      <c r="C6" s="18"/>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="16">
+        <v>6</v>
+      </c>
+      <c r="B7" s="20"/>
+      <c r="C7" s="18"/>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="16">
+        <v>7</v>
+      </c>
+      <c r="B8" s="20"/>
+      <c r="C8" s="18"/>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="16">
+        <v>8</v>
+      </c>
+      <c r="B9" s="20"/>
+      <c r="C9" s="18"/>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="16">
+        <v>9</v>
+      </c>
+      <c r="B10" s="20"/>
+      <c r="C10" s="18"/>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="16">
+        <v>10</v>
+      </c>
+      <c r="B11" s="20"/>
+      <c r="C11" s="18"/>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="16">
+        <v>11</v>
+      </c>
+      <c r="B12" s="20"/>
+      <c r="C12" s="18"/>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="16">
+        <v>12</v>
+      </c>
+      <c r="B13" s="20"/>
+      <c r="C13" s="18"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" showInputMessage="1" showErrorMessage="1" xr:uid="{B39E6D02-B52F-41F2-B192-27651BF65DED}">
+          <x14:formula1>
+            <xm:f>TB_Check!$A:$A</xm:f>
+          </x14:formula1>
+          <xm:sqref>C1:C1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B93460E-9148-431A-9979-64DD88E80E79}">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="15.6"/>
+  <cols>
+    <col min="1" max="16384" width="8.88671875" style="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" s="8" t="s">
+        <v>26</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7838456F-A1DD-4730-9800-D417F66E90E7}">
+  <dimension ref="A1:J14"/>
+  <sheetFormatPr defaultRowHeight="15.6"/>
+  <cols>
+    <col min="1" max="1" width="10.44140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="3.77734375" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.33203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.88671875" style="7"/>
+    <col min="5" max="5" width="25" style="7" customWidth="1"/>
+    <col min="6" max="9" width="8.88671875" style="7"/>
+    <col min="10" max="10" width="28" style="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="8.88671875" style="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="A1" s="29" t="s">
+        <v>103</v>
+      </c>
+      <c r="B1" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="D1" s="27" t="s">
+        <v>120</v>
+      </c>
+      <c r="E1" s="29" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="29" t="s">
+        <v>106</v>
+      </c>
+      <c r="B2" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="D2" s="27" t="s">
+        <v>127</v>
+      </c>
+      <c r="E2" s="36" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="29" t="s">
+        <v>105</v>
+      </c>
+      <c r="B3" s="27" t="s">
+        <v>101</v>
+      </c>
+      <c r="D3" s="27" t="s">
+        <v>126</v>
+      </c>
+      <c r="E3" s="36" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="29" t="s">
+        <v>108</v>
+      </c>
+      <c r="D4" s="27" t="s">
+        <v>122</v>
+      </c>
+      <c r="E4" s="29" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="D5" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="E5" s="36" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="D6" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="E6" s="29" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="E7" s="27" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="E8" s="27" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="E9" s="27" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="E10" s="8" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="16.2">
+      <c r="E11" s="37" t="s">
+        <v>140</v>
+      </c>
+      <c r="J11" s="28"/>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="E12" s="27" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="E13" s="37" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="16.2">
+      <c r="E14" s="36" t="s">
+        <v>145</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23AB2657-31BE-4673-A00D-DE3051816597}">
   <sheetPr>
@@ -1089,29 +4413,29 @@
   <dimension ref="A1:E15"/>
   <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="6" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.5546875" style="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="65.33203125" style="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.88671875" style="11" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15" style="11" customWidth="1"/>
-    <col min="6" max="10" width="8.88671875" style="11"/>
-    <col min="11" max="11" width="10.6640625" style="11" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="8.88671875" style="11"/>
+    <col min="1" max="1" width="6" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.5546875" style="22" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="65.33203125" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.88671875" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15" style="9" customWidth="1"/>
+    <col min="6" max="10" width="8.88671875" style="9"/>
+    <col min="11" max="11" width="10.6640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="8.88671875" style="9"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="33" customHeight="1">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="26" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="B1" s="24" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="24"/>
+      <c r="A2" s="26"/>
       <c r="B2" s="6" t="s">
         <v>18</v>
       </c>
@@ -1126,7 +4450,7 @@
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="24"/>
+      <c r="A3" s="26"/>
       <c r="B3" s="6">
         <v>1</v>
       </c>
@@ -1137,7 +4461,7 @@
       <c r="E3" s="1"/>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="24"/>
+      <c r="A4" s="26"/>
       <c r="B4" s="6">
         <v>2</v>
       </c>
@@ -1148,7 +4472,7 @@
       <c r="E4" s="1"/>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="24"/>
+      <c r="A5" s="26"/>
       <c r="B5" s="6">
         <v>3</v>
       </c>
@@ -1159,7 +4483,7 @@
       <c r="E5" s="1"/>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="24"/>
+      <c r="A6" s="26"/>
       <c r="B6" s="6">
         <v>4</v>
       </c>
@@ -1170,21 +4494,21 @@
       <c r="E6" s="1"/>
     </row>
     <row r="7" spans="1:5">
-      <c r="B7" s="11"/>
+      <c r="B7" s="9"/>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="24" t="s">
+      <c r="A8" s="26" t="s">
         <v>59</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
+      <c r="C8" s="25"/>
+      <c r="D8" s="25"/>
+      <c r="E8" s="25"/>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="24"/>
+      <c r="A9" s="26"/>
       <c r="B9" s="6" t="s">
         <v>18</v>
       </c>
@@ -1199,51 +4523,51 @@
       </c>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="24"/>
+      <c r="A10" s="26"/>
       <c r="B10" s="6" t="s">
         <v>61</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D10" s="5"/>
       <c r="E10" s="1"/>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="24"/>
+      <c r="A11" s="26"/>
       <c r="B11" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="C11" s="26" t="s">
-        <v>76</v>
+      <c r="C11" s="1" t="s">
+        <v>75</v>
       </c>
       <c r="D11" s="5"/>
       <c r="E11" s="1"/>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="24"/>
+      <c r="A12" s="26"/>
       <c r="B12" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="C12" s="26" t="s">
-        <v>75</v>
+      <c r="C12" s="1" t="s">
+        <v>74</v>
       </c>
       <c r="D12" s="5"/>
       <c r="E12" s="1"/>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="24"/>
+      <c r="A13" s="26"/>
       <c r="B13" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="C13" s="26" t="s">
-        <v>78</v>
+      <c r="C13" s="23" t="s">
+        <v>77</v>
       </c>
       <c r="D13" s="5"/>
       <c r="E13" s="1"/>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="24"/>
+      <c r="A14" s="26"/>
       <c r="B14" s="6" t="s">
         <v>65</v>
       </c>
@@ -1252,7 +4576,7 @@
       <c r="E14" s="1"/>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="24"/>
+      <c r="A15" s="26"/>
       <c r="B15" s="6" t="s">
         <v>66</v>
       </c>
@@ -1292,130 +4616,130 @@
   <dimension ref="A1:C13"/>
   <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="7.5546875" style="23" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="97" style="21" customWidth="1"/>
-    <col min="3" max="3" width="7.88671875" style="23" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.88671875" style="21"/>
+    <col min="1" max="1" width="7.5546875" style="21" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="97" style="19" customWidth="1"/>
+    <col min="3" max="3" width="7.88671875" style="21" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.88671875" style="19"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="C1" s="18" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="31.2">
-      <c r="A2" s="18">
+      <c r="A2" s="16">
         <v>1</v>
       </c>
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="20"/>
+      <c r="C2" s="18"/>
     </row>
     <row r="3" spans="1:3" ht="93.6">
-      <c r="A3" s="18">
+      <c r="A3" s="16">
         <v>2</v>
       </c>
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="C3" s="20"/>
+      <c r="C3" s="18"/>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="18">
+      <c r="A4" s="16">
         <v>3</v>
       </c>
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="C4" s="20"/>
+      <c r="C4" s="18"/>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="18">
+      <c r="A5" s="16">
         <v>4</v>
       </c>
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="C5" s="20"/>
+      <c r="C5" s="18"/>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="18">
+      <c r="A6" s="16">
         <v>5</v>
       </c>
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="C6" s="20"/>
+      <c r="C6" s="18"/>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="18">
+      <c r="A7" s="16">
         <v>6</v>
       </c>
-      <c r="B7" s="22" t="s">
+      <c r="B7" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="C7" s="20"/>
+      <c r="C7" s="18"/>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="18">
+      <c r="A8" s="16">
         <v>7</v>
       </c>
-      <c r="B8" s="22" t="s">
+      <c r="B8" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="C8" s="20"/>
+      <c r="C8" s="18"/>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="18">
+      <c r="A9" s="16">
         <v>8</v>
       </c>
-      <c r="B9" s="22" t="s">
+      <c r="B9" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="C9" s="20"/>
+      <c r="C9" s="18"/>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="18">
+      <c r="A10" s="16">
         <v>9</v>
       </c>
-      <c r="B10" s="22" t="s">
+      <c r="B10" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="C10" s="20"/>
+      <c r="C10" s="18"/>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="18">
+      <c r="A11" s="16">
         <v>10</v>
       </c>
-      <c r="B11" s="22" t="s">
+      <c r="B11" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="C11" s="20"/>
+      <c r="C11" s="18"/>
     </row>
     <row r="12" spans="1:3" ht="31.2">
-      <c r="A12" s="18">
+      <c r="A12" s="16">
         <v>11</v>
       </c>
-      <c r="B12" s="22" t="s">
+      <c r="B12" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="C12" s="20"/>
+      <c r="C12" s="18"/>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="18">
+      <c r="A13" s="16">
         <v>12</v>
       </c>
-      <c r="B13" s="22" t="s">
+      <c r="B13" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="C13" s="20"/>
+      <c r="C13" s="18"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -1443,126 +4767,126 @@
   <dimension ref="A1:C18"/>
   <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="7.5546875" style="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="71.5546875" style="15" customWidth="1"/>
-    <col min="3" max="3" width="16.21875" style="17" customWidth="1"/>
-    <col min="4" max="16384" width="8.88671875" style="15"/>
+    <col min="1" max="1" width="7.5546875" style="15" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="71.5546875" style="13" customWidth="1"/>
+    <col min="3" max="3" width="16.21875" style="15" customWidth="1"/>
+    <col min="4" max="16384" width="8.88671875" style="13"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="12" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="31.2">
-      <c r="A2" s="12">
+      <c r="A2" s="10">
         <v>1</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="C2" s="14"/>
+      <c r="C2" s="12"/>
     </row>
     <row r="3" spans="1:3" ht="31.2">
-      <c r="A3" s="12">
+      <c r="A3" s="10">
         <v>2</v>
       </c>
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="C3" s="14"/>
+      <c r="C3" s="12"/>
     </row>
     <row r="4" spans="1:3" ht="31.2">
-      <c r="A4" s="12">
+      <c r="A4" s="10">
         <v>3</v>
       </c>
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="C4" s="14"/>
+      <c r="C4" s="12"/>
     </row>
     <row r="5" spans="1:3" ht="46.8">
-      <c r="A5" s="12">
+      <c r="A5" s="10">
         <v>4</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="C5" s="14"/>
+      <c r="C5" s="12"/>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="12">
+      <c r="A6" s="10">
         <v>5</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="C6" s="14"/>
+      <c r="C6" s="12"/>
     </row>
     <row r="7" spans="1:3" ht="31.2">
-      <c r="A7" s="12">
+      <c r="A7" s="10">
         <v>6</v>
       </c>
-      <c r="B7" s="16" t="s">
+      <c r="B7" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="C7" s="14"/>
+      <c r="C7" s="12"/>
     </row>
     <row r="8" spans="1:3" ht="46.8">
-      <c r="A8" s="12">
+      <c r="A8" s="10">
         <v>7</v>
       </c>
-      <c r="B8" s="16" t="s">
+      <c r="B8" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="C8" s="14"/>
+      <c r="C8" s="12"/>
     </row>
     <row r="9" spans="1:3" ht="62.4">
-      <c r="A9" s="12">
+      <c r="A9" s="10">
         <v>8</v>
       </c>
-      <c r="B9" s="16" t="s">
+      <c r="B9" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="C9" s="14"/>
+      <c r="C9" s="12"/>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="15"/>
-      <c r="C10" s="15"/>
+      <c r="A10" s="13"/>
+      <c r="C10" s="13"/>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="15"/>
-      <c r="C11" s="15"/>
+      <c r="A11" s="13"/>
+      <c r="C11" s="13"/>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="15"/>
-      <c r="C12" s="15"/>
+      <c r="A12" s="13"/>
+      <c r="C12" s="13"/>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="15"/>
-      <c r="C13" s="15"/>
+      <c r="A13" s="13"/>
+      <c r="C13" s="13"/>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="15"/>
-      <c r="C14" s="15"/>
+      <c r="A14" s="13"/>
+      <c r="C14" s="13"/>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="15"/>
-      <c r="C15" s="15"/>
+      <c r="A15" s="13"/>
+      <c r="C15" s="13"/>
     </row>
     <row r="17" spans="2:2" ht="31.2">
-      <c r="B17" s="16" t="s">
+      <c r="B17" s="14" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="18" spans="2:2">
-      <c r="B18" s="15" t="s">
+      <c r="B18" s="13" t="s">
         <v>52</v>
       </c>
     </row>
@@ -1592,75 +4916,75 @@
   <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="7.5546875" style="23" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="74.44140625" style="21" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.88671875" style="23" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.88671875" style="21"/>
+    <col min="1" max="1" width="7.5546875" style="21" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="74.44140625" style="19" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.88671875" style="21" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.88671875" style="19"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="C1" s="18" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="18">
+      <c r="A2" s="16">
         <v>1</v>
       </c>
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="C2" s="20"/>
+      <c r="C2" s="18"/>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="18">
+      <c r="A3" s="16">
         <v>2</v>
       </c>
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="C3" s="20"/>
+      <c r="C3" s="18"/>
     </row>
     <row r="4" spans="1:3" ht="46.8">
-      <c r="A4" s="18">
+      <c r="A4" s="16">
         <v>3</v>
       </c>
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="C4" s="20"/>
+      <c r="C4" s="18"/>
     </row>
     <row r="5" spans="1:3" ht="46.8">
-      <c r="A5" s="18">
+      <c r="A5" s="16">
         <v>4</v>
       </c>
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="C5" s="20"/>
+      <c r="C5" s="18"/>
     </row>
     <row r="6" spans="1:3" ht="31.2">
-      <c r="A6" s="18">
+      <c r="A6" s="16">
         <v>5</v>
       </c>
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="C6" s="20"/>
+      <c r="C6" s="18"/>
     </row>
     <row r="9" spans="1:3" ht="31.2">
-      <c r="B9" s="16" t="s">
+      <c r="B9" s="14" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="13" t="s">
         <v>52</v>
       </c>
     </row>
@@ -1690,82 +5014,82 @@
   <dimension ref="A1:C13"/>
   <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="7.5546875" style="23" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="97" style="21" customWidth="1"/>
-    <col min="3" max="3" width="7.88671875" style="23" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.88671875" style="21"/>
+    <col min="1" max="1" width="7.5546875" style="21" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="97" style="19" customWidth="1"/>
+    <col min="3" max="3" width="7.88671875" style="21" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.88671875" style="19"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="C1" s="18" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="31.2">
-      <c r="A2" s="18">
+      <c r="A2" s="16">
         <v>1</v>
       </c>
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="C2" s="20"/>
+      <c r="C2" s="18"/>
     </row>
     <row r="3" spans="1:3" ht="46.8">
-      <c r="A3" s="18">
+      <c r="A3" s="16">
         <v>2</v>
       </c>
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="C3" s="18"/>
+    </row>
+    <row r="4" spans="1:3" ht="46.8">
+      <c r="A4" s="16">
+        <v>3</v>
+      </c>
+      <c r="B4" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="C3" s="20"/>
-    </row>
-    <row r="4" spans="1:3" ht="46.8">
-      <c r="A4" s="18">
-        <v>3</v>
-      </c>
-      <c r="B4" s="22" t="s">
-        <v>73</v>
-      </c>
-      <c r="C4" s="20"/>
+      <c r="C4" s="18"/>
     </row>
     <row r="5" spans="1:3" ht="31.2">
-      <c r="A5" s="18">
+      <c r="A5" s="16">
         <v>4</v>
       </c>
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="C5" s="20"/>
+      <c r="C5" s="18"/>
     </row>
     <row r="6" spans="1:3">
-      <c r="B6" s="23"/>
+      <c r="B6" s="21"/>
     </row>
     <row r="7" spans="1:3">
-      <c r="B7" s="23"/>
+      <c r="B7" s="21"/>
     </row>
     <row r="8" spans="1:3">
-      <c r="B8" s="23"/>
+      <c r="B8" s="21"/>
     </row>
     <row r="9" spans="1:3">
-      <c r="B9" s="23"/>
+      <c r="B9" s="21"/>
     </row>
     <row r="10" spans="1:3">
-      <c r="B10" s="23"/>
+      <c r="B10" s="21"/>
     </row>
     <row r="11" spans="1:3">
-      <c r="B11" s="23"/>
+      <c r="B11" s="21"/>
     </row>
     <row r="12" spans="1:3">
-      <c r="B12" s="23"/>
+      <c r="B12" s="21"/>
     </row>
     <row r="13" spans="1:3">
-      <c r="B13" s="23"/>
+      <c r="B13" s="21"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -1793,99 +5117,99 @@
   <dimension ref="A1:D14"/>
   <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="7.5546875" style="23" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="97" style="21" customWidth="1"/>
-    <col min="3" max="3" width="7.88671875" style="23" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.88671875" style="21"/>
+    <col min="1" max="1" width="7.5546875" style="21" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="97" style="19" customWidth="1"/>
+    <col min="3" max="3" width="7.88671875" style="21" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.88671875" style="19"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="C1" s="18" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="46.8">
-      <c r="A2" s="18">
+      <c r="A2" s="16">
         <v>1</v>
       </c>
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="C2" s="20"/>
+      <c r="C2" s="18"/>
     </row>
     <row r="3" spans="1:4" ht="46.8">
-      <c r="A3" s="18">
+      <c r="A3" s="16">
         <v>2</v>
       </c>
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="C3" s="20"/>
+      <c r="C3" s="18"/>
     </row>
     <row r="4" spans="1:4" ht="46.8">
-      <c r="A4" s="18">
+      <c r="A4" s="16">
         <v>3</v>
       </c>
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="C4" s="18"/>
+    </row>
+    <row r="5" spans="1:4" ht="46.8">
+      <c r="A5" s="16">
+        <v>4</v>
+      </c>
+      <c r="B5" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="C4" s="20"/>
-    </row>
-    <row r="5" spans="1:4" ht="46.8">
-      <c r="A5" s="18">
-        <v>4</v>
-      </c>
-      <c r="B5" s="22" t="s">
+      <c r="C5" s="18"/>
+    </row>
+    <row r="6" spans="1:4" ht="31.2">
+      <c r="A6" s="16">
+        <v>5</v>
+      </c>
+      <c r="B6" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="C5" s="20"/>
-    </row>
-    <row r="6" spans="1:4" ht="31.2">
-      <c r="A6" s="18">
-        <v>5</v>
-      </c>
-      <c r="B6" s="22" t="s">
-        <v>71</v>
-      </c>
-      <c r="C6" s="20"/>
+      <c r="C6" s="18"/>
     </row>
     <row r="7" spans="1:4">
-      <c r="B7" s="23"/>
-      <c r="D7" s="23"/>
+      <c r="B7" s="21"/>
+      <c r="D7" s="21"/>
     </row>
     <row r="8" spans="1:4">
-      <c r="B8" s="23"/>
-      <c r="D8" s="23"/>
+      <c r="B8" s="21"/>
+      <c r="D8" s="21"/>
     </row>
     <row r="9" spans="1:4">
-      <c r="B9" s="23"/>
-      <c r="D9" s="23"/>
+      <c r="B9" s="21"/>
+      <c r="D9" s="21"/>
     </row>
     <row r="10" spans="1:4">
-      <c r="B10" s="23"/>
-      <c r="D10" s="23"/>
+      <c r="B10" s="21"/>
+      <c r="D10" s="21"/>
     </row>
     <row r="11" spans="1:4">
-      <c r="B11" s="23"/>
-      <c r="D11" s="23"/>
+      <c r="B11" s="21"/>
+      <c r="D11" s="21"/>
     </row>
     <row r="12" spans="1:4">
-      <c r="B12" s="23"/>
-      <c r="D12" s="23"/>
+      <c r="B12" s="21"/>
+      <c r="D12" s="21"/>
     </row>
     <row r="13" spans="1:4">
-      <c r="B13" s="23"/>
-      <c r="D13" s="23"/>
+      <c r="B13" s="21"/>
+      <c r="D13" s="21"/>
     </row>
     <row r="14" spans="1:4">
-      <c r="B14" s="23"/>
-      <c r="D14" s="23"/>
+      <c r="B14" s="21"/>
+      <c r="D14" s="21"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -1906,113 +5230,119 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A41FB531-20B2-41BA-83FF-D38C4F8DED83}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E16C6CB3-AB72-4C57-B773-B0F82B0D9C2B}">
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="7.5546875" style="23" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="97" style="21" customWidth="1"/>
-    <col min="3" max="3" width="7.88671875" style="23" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.88671875" style="21"/>
+    <col min="1" max="1" width="7.5546875" style="21" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="97" style="19" customWidth="1"/>
+    <col min="3" max="3" width="7.88671875" style="21" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.88671875" style="19"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="C1" s="18" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="18">
+    <row r="2" spans="1:3" ht="31.2">
+      <c r="A2" s="16">
         <v>1</v>
       </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="20"/>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="18">
+      <c r="B2" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="C2" s="18"/>
+    </row>
+    <row r="3" spans="1:3" ht="31.2">
+      <c r="A3" s="16">
         <v>2</v>
       </c>
-      <c r="B3" s="22"/>
-      <c r="C3" s="20"/>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="18">
+      <c r="B3" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="C3" s="18"/>
+    </row>
+    <row r="4" spans="1:3" ht="31.2">
+      <c r="A4" s="16">
         <v>3</v>
       </c>
-      <c r="B4" s="22"/>
-      <c r="C4" s="20"/>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="18">
+      <c r="B4" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="C4" s="18"/>
+    </row>
+    <row r="5" spans="1:3" ht="31.2">
+      <c r="A5" s="16">
         <v>4</v>
       </c>
-      <c r="B5" s="22"/>
-      <c r="C5" s="20"/>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="18">
+      <c r="B5" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="C5" s="18"/>
+    </row>
+    <row r="6" spans="1:3" ht="31.2">
+      <c r="A6" s="16">
         <v>5</v>
       </c>
-      <c r="B6" s="22"/>
-      <c r="C6" s="20"/>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="18">
+      <c r="B6" s="20" t="s">
+        <v>79</v>
+      </c>
+      <c r="C6" s="18"/>
+    </row>
+    <row r="7" spans="1:3" ht="31.2">
+      <c r="A7" s="16">
         <v>6</v>
       </c>
-      <c r="B7" s="22"/>
-      <c r="C7" s="20"/>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="18">
+      <c r="B7" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="C7" s="18"/>
+    </row>
+    <row r="8" spans="1:3" ht="31.2">
+      <c r="A8" s="16">
         <v>7</v>
       </c>
-      <c r="B8" s="22"/>
-      <c r="C8" s="20"/>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="18">
+      <c r="B8" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="C8" s="18"/>
+    </row>
+    <row r="9" spans="1:3" ht="46.8">
+      <c r="A9" s="16">
         <v>8</v>
       </c>
-      <c r="B9" s="22"/>
-      <c r="C9" s="20"/>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="18">
+      <c r="B9" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="C9" s="18"/>
+    </row>
+    <row r="10" spans="1:3" ht="31.2">
+      <c r="A10" s="16">
         <v>9</v>
       </c>
-      <c r="B10" s="22"/>
-      <c r="C10" s="20"/>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="18">
+      <c r="B10" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="C10" s="18"/>
+    </row>
+    <row r="11" spans="1:3" ht="31.2">
+      <c r="A11" s="16">
         <v>10</v>
       </c>
-      <c r="B11" s="22"/>
-      <c r="C11" s="20"/>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="18">
-        <v>11</v>
-      </c>
-      <c r="B12" s="22"/>
-      <c r="C12" s="20"/>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="18">
-        <v>12</v>
-      </c>
-      <c r="B13" s="22"/>
-      <c r="C13" s="20"/>
+      <c r="B11" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="C11" s="18"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -2020,7 +5350,7 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" showInputMessage="1" showErrorMessage="1" xr:uid="{B39E6D02-B52F-41F2-B192-27651BF65DED}">
+        <x14:dataValidation type="list" showInputMessage="1" showErrorMessage="1" xr:uid="{A899F993-9B55-4798-A1F8-A94D417A964F}">
           <x14:formula1>
             <xm:f>TB_Check!$A:$A</xm:f>
           </x14:formula1>
@@ -2033,25 +5363,1289 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B93460E-9148-431A-9979-64DD88E80E79}">
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15.6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{030DFC05-9135-487F-8F69-4B4A0E200EC8}">
+  <sheetPr>
+    <tabColor rgb="FFFFFF00"/>
+  </sheetPr>
+  <dimension ref="A1:O63"/>
+  <sheetFormatPr defaultRowHeight="21"/>
   <cols>
-    <col min="1" max="16384" width="8.88671875" style="7"/>
+    <col min="1" max="1" width="7.33203125" style="21" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.77734375" style="19" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.21875" style="19" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.6640625" style="19" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="37.44140625" style="19" customWidth="1"/>
+    <col min="6" max="6" width="19.5546875" style="19" customWidth="1"/>
+    <col min="7" max="7" width="10.6640625" style="19" customWidth="1"/>
+    <col min="8" max="8" width="28.21875" style="19" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.44140625" style="19" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.88671875" style="34" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="25.44140625" style="34" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="30.44140625" style="19" customWidth="1"/>
+    <col min="13" max="13" width="10.44140625" style="19" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.88671875" style="19"/>
+    <col min="15" max="15" width="7.77734375" style="21" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="8.88671875" style="19"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="10" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1">
-      <c r="A2" s="10" t="s">
-        <v>26</v>
-      </c>
+    <row r="1" spans="1:15" ht="62.4">
+      <c r="A1" s="31" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="31" t="s">
+        <v>89</v>
+      </c>
+      <c r="C1" s="31" t="s">
+        <v>90</v>
+      </c>
+      <c r="D1" s="31" t="s">
+        <v>91</v>
+      </c>
+      <c r="E1" s="31" t="s">
+        <v>113</v>
+      </c>
+      <c r="F1" s="31" t="s">
+        <v>114</v>
+      </c>
+      <c r="G1" s="35" t="s">
+        <v>118</v>
+      </c>
+      <c r="H1" s="32" t="s">
+        <v>93</v>
+      </c>
+      <c r="I1" s="32" t="s">
+        <v>107</v>
+      </c>
+      <c r="J1" s="32" t="s">
+        <v>152</v>
+      </c>
+      <c r="K1" s="32" t="s">
+        <v>96</v>
+      </c>
+      <c r="L1" s="32" t="s">
+        <v>94</v>
+      </c>
+      <c r="M1" s="32" t="s">
+        <v>95</v>
+      </c>
+      <c r="N1" s="50" t="s">
+        <v>155</v>
+      </c>
+      <c r="O1" s="18" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" ht="31.2">
+      <c r="A2" s="16">
+        <v>1</v>
+      </c>
+      <c r="B2" s="30" t="s">
+        <v>109</v>
+      </c>
+      <c r="C2" s="30" t="s">
+        <v>110</v>
+      </c>
+      <c r="D2" s="30" t="s">
+        <v>111</v>
+      </c>
+      <c r="E2" s="30" t="s">
+        <v>112</v>
+      </c>
+      <c r="F2" s="30" t="s">
+        <v>115</v>
+      </c>
+      <c r="G2" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="H2" s="30" t="s">
+        <v>128</v>
+      </c>
+      <c r="I2" s="30" t="s">
+        <v>104</v>
+      </c>
+      <c r="J2" s="33" t="s">
+        <v>100</v>
+      </c>
+      <c r="K2" s="33" t="s">
+        <v>97</v>
+      </c>
+      <c r="L2" s="30" t="s">
+        <v>116</v>
+      </c>
+      <c r="M2" s="30" t="s">
+        <v>117</v>
+      </c>
+      <c r="N2" s="49"/>
+      <c r="O2" s="18"/>
+    </row>
+    <row r="3" spans="1:15" ht="46.8">
+      <c r="A3" s="16">
+        <v>2</v>
+      </c>
+      <c r="B3" s="30" t="s">
+        <v>109</v>
+      </c>
+      <c r="C3" s="30" t="s">
+        <v>110</v>
+      </c>
+      <c r="D3" s="30" t="s">
+        <v>111</v>
+      </c>
+      <c r="E3" s="30" t="s">
+        <v>129</v>
+      </c>
+      <c r="F3" s="30" t="s">
+        <v>130</v>
+      </c>
+      <c r="G3" s="30" t="s">
+        <v>125</v>
+      </c>
+      <c r="H3" s="30" t="s">
+        <v>128</v>
+      </c>
+      <c r="I3" s="30" t="s">
+        <v>104</v>
+      </c>
+      <c r="J3" s="33" t="s">
+        <v>100</v>
+      </c>
+      <c r="K3" s="33" t="s">
+        <v>97</v>
+      </c>
+      <c r="L3" s="30" t="s">
+        <v>102</v>
+      </c>
+      <c r="M3" s="38" t="s">
+        <v>149</v>
+      </c>
+      <c r="N3" s="49"/>
+      <c r="O3" s="18"/>
+    </row>
+    <row r="4" spans="1:15" ht="31.2">
+      <c r="A4" s="16">
+        <v>3</v>
+      </c>
+      <c r="B4" s="30" t="s">
+        <v>109</v>
+      </c>
+      <c r="C4" s="30" t="s">
+        <v>110</v>
+      </c>
+      <c r="D4" s="30" t="s">
+        <v>142</v>
+      </c>
+      <c r="E4" s="30" t="s">
+        <v>143</v>
+      </c>
+      <c r="F4" s="30" t="s">
+        <v>146</v>
+      </c>
+      <c r="G4" s="30" t="s">
+        <v>119</v>
+      </c>
+      <c r="H4" s="30" t="s">
+        <v>147</v>
+      </c>
+      <c r="I4" s="30" t="s">
+        <v>104</v>
+      </c>
+      <c r="J4" s="33" t="s">
+        <v>100</v>
+      </c>
+      <c r="K4" s="33" t="s">
+        <v>100</v>
+      </c>
+      <c r="L4" s="30" t="s">
+        <v>148</v>
+      </c>
+      <c r="M4" s="30" t="s">
+        <v>150</v>
+      </c>
+      <c r="N4" s="49"/>
+      <c r="O4" s="18"/>
+    </row>
+    <row r="5" spans="1:15" ht="31.2">
+      <c r="A5" s="16">
+        <v>4</v>
+      </c>
+      <c r="B5" s="30" t="s">
+        <v>109</v>
+      </c>
+      <c r="C5" s="30" t="s">
+        <v>110</v>
+      </c>
+      <c r="D5" s="30" t="s">
+        <v>142</v>
+      </c>
+      <c r="E5" s="30" t="s">
+        <v>151</v>
+      </c>
+      <c r="F5" s="30" t="s">
+        <v>146</v>
+      </c>
+      <c r="G5" s="30" t="s">
+        <v>119</v>
+      </c>
+      <c r="H5" s="30" t="s">
+        <v>147</v>
+      </c>
+      <c r="I5" s="30" t="s">
+        <v>104</v>
+      </c>
+      <c r="J5" s="33" t="s">
+        <v>100</v>
+      </c>
+      <c r="K5" s="33" t="s">
+        <v>100</v>
+      </c>
+      <c r="L5" s="30" t="s">
+        <v>148</v>
+      </c>
+      <c r="M5" s="30" t="s">
+        <v>150</v>
+      </c>
+      <c r="N5" s="49"/>
+      <c r="O5" s="18"/>
+    </row>
+    <row r="6" spans="1:15">
+      <c r="A6" s="16"/>
+      <c r="B6" s="30"/>
+      <c r="C6" s="30"/>
+      <c r="D6" s="30"/>
+      <c r="E6" s="30"/>
+      <c r="F6" s="30"/>
+      <c r="G6" s="30"/>
+      <c r="H6" s="30"/>
+      <c r="I6" s="30"/>
+      <c r="J6" s="33"/>
+      <c r="K6" s="33"/>
+      <c r="L6" s="30"/>
+      <c r="M6" s="30"/>
+      <c r="N6" s="49"/>
+      <c r="O6" s="18"/>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="A7" s="16"/>
+      <c r="B7" s="30"/>
+      <c r="C7" s="30"/>
+      <c r="D7" s="30"/>
+      <c r="E7" s="30"/>
+      <c r="F7" s="30"/>
+      <c r="G7" s="30"/>
+      <c r="H7" s="30"/>
+      <c r="I7" s="30"/>
+      <c r="J7" s="33"/>
+      <c r="K7" s="33"/>
+      <c r="L7" s="30"/>
+      <c r="M7" s="30"/>
+      <c r="N7" s="49"/>
+      <c r="O7" s="18"/>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="A8" s="16"/>
+      <c r="B8" s="30"/>
+      <c r="C8" s="30"/>
+      <c r="D8" s="30"/>
+      <c r="E8" s="30"/>
+      <c r="F8" s="30"/>
+      <c r="G8" s="30"/>
+      <c r="H8" s="30"/>
+      <c r="I8" s="30"/>
+      <c r="J8" s="33"/>
+      <c r="K8" s="33"/>
+      <c r="L8" s="30"/>
+      <c r="M8" s="30"/>
+      <c r="N8" s="49"/>
+      <c r="O8" s="18"/>
+    </row>
+    <row r="9" spans="1:15">
+      <c r="A9" s="16"/>
+      <c r="B9" s="30"/>
+      <c r="C9" s="30"/>
+      <c r="D9" s="30"/>
+      <c r="E9" s="30"/>
+      <c r="F9" s="30"/>
+      <c r="G9" s="30"/>
+      <c r="H9" s="30"/>
+      <c r="I9" s="30"/>
+      <c r="J9" s="33"/>
+      <c r="K9" s="33"/>
+      <c r="L9" s="30"/>
+      <c r="M9" s="30"/>
+      <c r="N9" s="49"/>
+      <c r="O9" s="18"/>
+    </row>
+    <row r="10" spans="1:15">
+      <c r="A10" s="16"/>
+      <c r="B10" s="30"/>
+      <c r="C10" s="30"/>
+      <c r="D10" s="30"/>
+      <c r="E10" s="30"/>
+      <c r="F10" s="30"/>
+      <c r="G10" s="30"/>
+      <c r="H10" s="30"/>
+      <c r="I10" s="30"/>
+      <c r="J10" s="33"/>
+      <c r="K10" s="33"/>
+      <c r="L10" s="30"/>
+      <c r="M10" s="30"/>
+      <c r="N10" s="49"/>
+      <c r="O10" s="18"/>
+    </row>
+    <row r="11" spans="1:15">
+      <c r="A11" s="16"/>
+      <c r="B11" s="30"/>
+      <c r="C11" s="30"/>
+      <c r="D11" s="30"/>
+      <c r="E11" s="30"/>
+      <c r="F11" s="30"/>
+      <c r="G11" s="30"/>
+      <c r="H11" s="30"/>
+      <c r="I11" s="30"/>
+      <c r="J11" s="33"/>
+      <c r="K11" s="33"/>
+      <c r="L11" s="30"/>
+      <c r="M11" s="30"/>
+      <c r="N11" s="49"/>
+      <c r="O11" s="18"/>
+    </row>
+    <row r="12" spans="1:15">
+      <c r="A12" s="16"/>
+      <c r="B12" s="30"/>
+      <c r="C12" s="30"/>
+      <c r="D12" s="30"/>
+      <c r="E12" s="30"/>
+      <c r="F12" s="30"/>
+      <c r="G12" s="30"/>
+      <c r="H12" s="30"/>
+      <c r="I12" s="30"/>
+      <c r="J12" s="33"/>
+      <c r="K12" s="33"/>
+      <c r="L12" s="30"/>
+      <c r="M12" s="30"/>
+      <c r="N12" s="49"/>
+      <c r="O12" s="18"/>
+    </row>
+    <row r="13" spans="1:15">
+      <c r="A13" s="16"/>
+      <c r="B13" s="30"/>
+      <c r="C13" s="30"/>
+      <c r="D13" s="30"/>
+      <c r="E13" s="30"/>
+      <c r="F13" s="30"/>
+      <c r="G13" s="30"/>
+      <c r="H13" s="30"/>
+      <c r="I13" s="30"/>
+      <c r="J13" s="33"/>
+      <c r="K13" s="33"/>
+      <c r="L13" s="30"/>
+      <c r="M13" s="30"/>
+      <c r="N13" s="49"/>
+      <c r="O13" s="18"/>
+    </row>
+    <row r="14" spans="1:15">
+      <c r="A14" s="16"/>
+      <c r="B14" s="30"/>
+      <c r="C14" s="30"/>
+      <c r="D14" s="30"/>
+      <c r="E14" s="30"/>
+      <c r="F14" s="30"/>
+      <c r="G14" s="30"/>
+      <c r="H14" s="30"/>
+      <c r="I14" s="30"/>
+      <c r="J14" s="33"/>
+      <c r="K14" s="33"/>
+      <c r="L14" s="30"/>
+      <c r="M14" s="30"/>
+      <c r="N14" s="49"/>
+      <c r="O14" s="18"/>
+    </row>
+    <row r="15" spans="1:15">
+      <c r="A15" s="16"/>
+      <c r="B15" s="30"/>
+      <c r="C15" s="30"/>
+      <c r="D15" s="30"/>
+      <c r="E15" s="30"/>
+      <c r="F15" s="30"/>
+      <c r="G15" s="30"/>
+      <c r="H15" s="30"/>
+      <c r="I15" s="30"/>
+      <c r="J15" s="33"/>
+      <c r="K15" s="33"/>
+      <c r="L15" s="30"/>
+      <c r="M15" s="30"/>
+      <c r="N15" s="49"/>
+      <c r="O15" s="18"/>
+    </row>
+    <row r="16" spans="1:15">
+      <c r="A16" s="16"/>
+      <c r="B16" s="30"/>
+      <c r="C16" s="30"/>
+      <c r="D16" s="30"/>
+      <c r="E16" s="30"/>
+      <c r="F16" s="30"/>
+      <c r="G16" s="30"/>
+      <c r="H16" s="30"/>
+      <c r="I16" s="30"/>
+      <c r="J16" s="33"/>
+      <c r="K16" s="33"/>
+      <c r="L16" s="30"/>
+      <c r="M16" s="30"/>
+      <c r="N16" s="49"/>
+      <c r="O16" s="18"/>
+    </row>
+    <row r="17" spans="1:15">
+      <c r="A17" s="16"/>
+      <c r="B17" s="30"/>
+      <c r="C17" s="30"/>
+      <c r="D17" s="30"/>
+      <c r="E17" s="30"/>
+      <c r="F17" s="30"/>
+      <c r="G17" s="30"/>
+      <c r="H17" s="30"/>
+      <c r="I17" s="30"/>
+      <c r="J17" s="33"/>
+      <c r="K17" s="33"/>
+      <c r="L17" s="30"/>
+      <c r="M17" s="30"/>
+      <c r="N17" s="49"/>
+      <c r="O17" s="18"/>
+    </row>
+    <row r="18" spans="1:15">
+      <c r="A18" s="16"/>
+      <c r="B18" s="30"/>
+      <c r="C18" s="30"/>
+      <c r="D18" s="30"/>
+      <c r="E18" s="30"/>
+      <c r="F18" s="30"/>
+      <c r="G18" s="30"/>
+      <c r="H18" s="30"/>
+      <c r="I18" s="30"/>
+      <c r="J18" s="33"/>
+      <c r="K18" s="33"/>
+      <c r="L18" s="30"/>
+      <c r="M18" s="30"/>
+      <c r="N18" s="49"/>
+      <c r="O18" s="18"/>
+    </row>
+    <row r="19" spans="1:15">
+      <c r="A19" s="16"/>
+      <c r="B19" s="30"/>
+      <c r="C19" s="30"/>
+      <c r="D19" s="30"/>
+      <c r="E19" s="30"/>
+      <c r="F19" s="30"/>
+      <c r="G19" s="30"/>
+      <c r="H19" s="30"/>
+      <c r="I19" s="30"/>
+      <c r="J19" s="33"/>
+      <c r="K19" s="33"/>
+      <c r="L19" s="30"/>
+      <c r="M19" s="30"/>
+      <c r="N19" s="49"/>
+      <c r="O19" s="18"/>
+    </row>
+    <row r="20" spans="1:15">
+      <c r="A20" s="16"/>
+      <c r="B20" s="30"/>
+      <c r="C20" s="30"/>
+      <c r="D20" s="30"/>
+      <c r="E20" s="30"/>
+      <c r="F20" s="30"/>
+      <c r="G20" s="30"/>
+      <c r="H20" s="30"/>
+      <c r="I20" s="30"/>
+      <c r="J20" s="33"/>
+      <c r="K20" s="33"/>
+      <c r="L20" s="30"/>
+      <c r="M20" s="30"/>
+      <c r="N20" s="49"/>
+      <c r="O20" s="18"/>
+    </row>
+    <row r="21" spans="1:15">
+      <c r="A21" s="16"/>
+      <c r="B21" s="30"/>
+      <c r="C21" s="30"/>
+      <c r="D21" s="30"/>
+      <c r="E21" s="30"/>
+      <c r="F21" s="30"/>
+      <c r="G21" s="30"/>
+      <c r="H21" s="30"/>
+      <c r="I21" s="30"/>
+      <c r="J21" s="33"/>
+      <c r="K21" s="33"/>
+      <c r="L21" s="30"/>
+      <c r="M21" s="30"/>
+      <c r="N21" s="49"/>
+      <c r="O21" s="18"/>
+    </row>
+    <row r="22" spans="1:15">
+      <c r="A22" s="16"/>
+      <c r="B22" s="30"/>
+      <c r="C22" s="30"/>
+      <c r="D22" s="30"/>
+      <c r="E22" s="30"/>
+      <c r="F22" s="30"/>
+      <c r="G22" s="30"/>
+      <c r="H22" s="30"/>
+      <c r="I22" s="30"/>
+      <c r="J22" s="33"/>
+      <c r="K22" s="33"/>
+      <c r="L22" s="30"/>
+      <c r="M22" s="30"/>
+      <c r="N22" s="49"/>
+      <c r="O22" s="18"/>
+    </row>
+    <row r="23" spans="1:15">
+      <c r="A23" s="16"/>
+      <c r="B23" s="30"/>
+      <c r="C23" s="30"/>
+      <c r="D23" s="30"/>
+      <c r="E23" s="30"/>
+      <c r="F23" s="30"/>
+      <c r="G23" s="30"/>
+      <c r="H23" s="30"/>
+      <c r="I23" s="30"/>
+      <c r="J23" s="33"/>
+      <c r="K23" s="33"/>
+      <c r="L23" s="30"/>
+      <c r="M23" s="30"/>
+      <c r="N23" s="49"/>
+      <c r="O23" s="18"/>
+    </row>
+    <row r="24" spans="1:15">
+      <c r="A24" s="16"/>
+      <c r="B24" s="30"/>
+      <c r="C24" s="30"/>
+      <c r="D24" s="30"/>
+      <c r="E24" s="30"/>
+      <c r="F24" s="30"/>
+      <c r="G24" s="30"/>
+      <c r="H24" s="30"/>
+      <c r="I24" s="30"/>
+      <c r="J24" s="33"/>
+      <c r="K24" s="33"/>
+      <c r="L24" s="30"/>
+      <c r="M24" s="30"/>
+      <c r="N24" s="49"/>
+      <c r="O24" s="18"/>
+    </row>
+    <row r="25" spans="1:15">
+      <c r="A25" s="16"/>
+      <c r="B25" s="30"/>
+      <c r="C25" s="30"/>
+      <c r="D25" s="30"/>
+      <c r="E25" s="30"/>
+      <c r="F25" s="30"/>
+      <c r="G25" s="30"/>
+      <c r="H25" s="30"/>
+      <c r="I25" s="30"/>
+      <c r="J25" s="33"/>
+      <c r="K25" s="33"/>
+      <c r="L25" s="30"/>
+      <c r="M25" s="30"/>
+      <c r="N25" s="49"/>
+      <c r="O25" s="18"/>
+    </row>
+    <row r="26" spans="1:15">
+      <c r="A26" s="16"/>
+      <c r="B26" s="30"/>
+      <c r="C26" s="30"/>
+      <c r="D26" s="30"/>
+      <c r="E26" s="30"/>
+      <c r="F26" s="30"/>
+      <c r="G26" s="30"/>
+      <c r="H26" s="30"/>
+      <c r="I26" s="30"/>
+      <c r="J26" s="33"/>
+      <c r="K26" s="33"/>
+      <c r="L26" s="30"/>
+      <c r="M26" s="30"/>
+      <c r="N26" s="49"/>
+      <c r="O26" s="18"/>
+    </row>
+    <row r="27" spans="1:15">
+      <c r="A27" s="16"/>
+      <c r="B27" s="30"/>
+      <c r="C27" s="30"/>
+      <c r="D27" s="30"/>
+      <c r="E27" s="30"/>
+      <c r="F27" s="30"/>
+      <c r="G27" s="30"/>
+      <c r="H27" s="30"/>
+      <c r="I27" s="30"/>
+      <c r="J27" s="33"/>
+      <c r="K27" s="33"/>
+      <c r="L27" s="30"/>
+      <c r="M27" s="30"/>
+      <c r="N27" s="49"/>
+      <c r="O27" s="18"/>
+    </row>
+    <row r="28" spans="1:15">
+      <c r="A28" s="16"/>
+      <c r="B28" s="30"/>
+      <c r="C28" s="30"/>
+      <c r="D28" s="30"/>
+      <c r="E28" s="30"/>
+      <c r="F28" s="30"/>
+      <c r="G28" s="30"/>
+      <c r="H28" s="30"/>
+      <c r="I28" s="30"/>
+      <c r="J28" s="33"/>
+      <c r="K28" s="33"/>
+      <c r="L28" s="30"/>
+      <c r="M28" s="30"/>
+      <c r="N28" s="49"/>
+      <c r="O28" s="18"/>
+    </row>
+    <row r="29" spans="1:15">
+      <c r="A29" s="16"/>
+      <c r="B29" s="30"/>
+      <c r="C29" s="30"/>
+      <c r="D29" s="30"/>
+      <c r="E29" s="30"/>
+      <c r="F29" s="30"/>
+      <c r="G29" s="30"/>
+      <c r="H29" s="30"/>
+      <c r="I29" s="30"/>
+      <c r="J29" s="33"/>
+      <c r="K29" s="33"/>
+      <c r="L29" s="30"/>
+      <c r="M29" s="30"/>
+      <c r="N29" s="49"/>
+      <c r="O29" s="18"/>
+    </row>
+    <row r="30" spans="1:15">
+      <c r="A30" s="16"/>
+      <c r="B30" s="30"/>
+      <c r="C30" s="30"/>
+      <c r="D30" s="30"/>
+      <c r="E30" s="30"/>
+      <c r="F30" s="30"/>
+      <c r="G30" s="30"/>
+      <c r="H30" s="30"/>
+      <c r="I30" s="30"/>
+      <c r="J30" s="33"/>
+      <c r="K30" s="33"/>
+      <c r="L30" s="30"/>
+      <c r="M30" s="30"/>
+      <c r="N30" s="49"/>
+      <c r="O30" s="18"/>
+    </row>
+    <row r="31" spans="1:15">
+      <c r="A31" s="16"/>
+      <c r="B31" s="30"/>
+      <c r="C31" s="30"/>
+      <c r="D31" s="30"/>
+      <c r="E31" s="30"/>
+      <c r="F31" s="30"/>
+      <c r="G31" s="30"/>
+      <c r="H31" s="30"/>
+      <c r="I31" s="30"/>
+      <c r="J31" s="33"/>
+      <c r="K31" s="33"/>
+      <c r="L31" s="30"/>
+      <c r="M31" s="30"/>
+      <c r="N31" s="49"/>
+      <c r="O31" s="18"/>
+    </row>
+    <row r="32" spans="1:15">
+      <c r="A32" s="16"/>
+      <c r="B32" s="30"/>
+      <c r="C32" s="30"/>
+      <c r="D32" s="30"/>
+      <c r="E32" s="30"/>
+      <c r="F32" s="30"/>
+      <c r="G32" s="30"/>
+      <c r="H32" s="30"/>
+      <c r="I32" s="30"/>
+      <c r="J32" s="33"/>
+      <c r="K32" s="33"/>
+      <c r="L32" s="30"/>
+      <c r="M32" s="30"/>
+      <c r="N32" s="49"/>
+      <c r="O32" s="18"/>
+    </row>
+    <row r="33" spans="1:15">
+      <c r="A33" s="16"/>
+      <c r="B33" s="30"/>
+      <c r="C33" s="30"/>
+      <c r="D33" s="30"/>
+      <c r="E33" s="30"/>
+      <c r="F33" s="30"/>
+      <c r="G33" s="30"/>
+      <c r="H33" s="30"/>
+      <c r="I33" s="30"/>
+      <c r="J33" s="33"/>
+      <c r="K33" s="33"/>
+      <c r="L33" s="30"/>
+      <c r="M33" s="30"/>
+      <c r="N33" s="49"/>
+      <c r="O33" s="18"/>
+    </row>
+    <row r="34" spans="1:15">
+      <c r="A34" s="16"/>
+      <c r="B34" s="30"/>
+      <c r="C34" s="30"/>
+      <c r="D34" s="30"/>
+      <c r="E34" s="30"/>
+      <c r="F34" s="30"/>
+      <c r="G34" s="30"/>
+      <c r="H34" s="30"/>
+      <c r="I34" s="30"/>
+      <c r="J34" s="33"/>
+      <c r="K34" s="33"/>
+      <c r="L34" s="30"/>
+      <c r="M34" s="30"/>
+      <c r="N34" s="49"/>
+      <c r="O34" s="18"/>
+    </row>
+    <row r="35" spans="1:15">
+      <c r="A35" s="16"/>
+      <c r="B35" s="30"/>
+      <c r="C35" s="30"/>
+      <c r="D35" s="30"/>
+      <c r="E35" s="30"/>
+      <c r="F35" s="30"/>
+      <c r="G35" s="30"/>
+      <c r="H35" s="30"/>
+      <c r="I35" s="30"/>
+      <c r="J35" s="33"/>
+      <c r="K35" s="33"/>
+      <c r="L35" s="30"/>
+      <c r="M35" s="30"/>
+      <c r="N35" s="49"/>
+      <c r="O35" s="18"/>
+    </row>
+    <row r="36" spans="1:15">
+      <c r="A36" s="16"/>
+      <c r="B36" s="30"/>
+      <c r="C36" s="30"/>
+      <c r="D36" s="30"/>
+      <c r="E36" s="30"/>
+      <c r="F36" s="30"/>
+      <c r="G36" s="30"/>
+      <c r="H36" s="30"/>
+      <c r="I36" s="30"/>
+      <c r="J36" s="33"/>
+      <c r="K36" s="33"/>
+      <c r="L36" s="30"/>
+      <c r="M36" s="30"/>
+      <c r="N36" s="49"/>
+      <c r="O36" s="18"/>
+    </row>
+    <row r="37" spans="1:15">
+      <c r="A37" s="16"/>
+      <c r="B37" s="30"/>
+      <c r="C37" s="30"/>
+      <c r="D37" s="30"/>
+      <c r="E37" s="30"/>
+      <c r="F37" s="30"/>
+      <c r="G37" s="30"/>
+      <c r="H37" s="30"/>
+      <c r="I37" s="30"/>
+      <c r="J37" s="33"/>
+      <c r="K37" s="33"/>
+      <c r="L37" s="30"/>
+      <c r="M37" s="30"/>
+      <c r="N37" s="49"/>
+      <c r="O37" s="18"/>
+    </row>
+    <row r="38" spans="1:15">
+      <c r="A38" s="16"/>
+      <c r="B38" s="30"/>
+      <c r="C38" s="30"/>
+      <c r="D38" s="30"/>
+      <c r="E38" s="30"/>
+      <c r="F38" s="30"/>
+      <c r="G38" s="30"/>
+      <c r="H38" s="30"/>
+      <c r="I38" s="30"/>
+      <c r="J38" s="33"/>
+      <c r="K38" s="33"/>
+      <c r="L38" s="30"/>
+      <c r="M38" s="30"/>
+      <c r="N38" s="49"/>
+      <c r="O38" s="18"/>
+    </row>
+    <row r="39" spans="1:15">
+      <c r="A39" s="16"/>
+      <c r="B39" s="30"/>
+      <c r="C39" s="30"/>
+      <c r="D39" s="30"/>
+      <c r="E39" s="30"/>
+      <c r="F39" s="30"/>
+      <c r="G39" s="30"/>
+      <c r="H39" s="30"/>
+      <c r="I39" s="30"/>
+      <c r="J39" s="33"/>
+      <c r="K39" s="33"/>
+      <c r="L39" s="30"/>
+      <c r="M39" s="30"/>
+      <c r="N39" s="49"/>
+      <c r="O39" s="18"/>
+    </row>
+    <row r="40" spans="1:15">
+      <c r="A40" s="16"/>
+      <c r="B40" s="30"/>
+      <c r="C40" s="30"/>
+      <c r="D40" s="30"/>
+      <c r="E40" s="30"/>
+      <c r="F40" s="30"/>
+      <c r="G40" s="30"/>
+      <c r="H40" s="30"/>
+      <c r="I40" s="30"/>
+      <c r="J40" s="33"/>
+      <c r="K40" s="33"/>
+      <c r="L40" s="30"/>
+      <c r="M40" s="30"/>
+      <c r="N40" s="49"/>
+      <c r="O40" s="18"/>
+    </row>
+    <row r="41" spans="1:15">
+      <c r="A41" s="16"/>
+      <c r="B41" s="30"/>
+      <c r="C41" s="30"/>
+      <c r="D41" s="30"/>
+      <c r="E41" s="30"/>
+      <c r="F41" s="30"/>
+      <c r="G41" s="30"/>
+      <c r="H41" s="30"/>
+      <c r="I41" s="30"/>
+      <c r="J41" s="33"/>
+      <c r="K41" s="33"/>
+      <c r="L41" s="30"/>
+      <c r="M41" s="30"/>
+      <c r="N41" s="49"/>
+      <c r="O41" s="18"/>
+    </row>
+    <row r="42" spans="1:15">
+      <c r="A42" s="16"/>
+      <c r="B42" s="30"/>
+      <c r="C42" s="30"/>
+      <c r="D42" s="30"/>
+      <c r="E42" s="30"/>
+      <c r="F42" s="30"/>
+      <c r="G42" s="30"/>
+      <c r="H42" s="30"/>
+      <c r="I42" s="30"/>
+      <c r="J42" s="33"/>
+      <c r="K42" s="33"/>
+      <c r="L42" s="30"/>
+      <c r="M42" s="30"/>
+      <c r="N42" s="49"/>
+      <c r="O42" s="18"/>
+    </row>
+    <row r="43" spans="1:15">
+      <c r="A43" s="16"/>
+      <c r="B43" s="30"/>
+      <c r="C43" s="30"/>
+      <c r="D43" s="30"/>
+      <c r="E43" s="30"/>
+      <c r="F43" s="30"/>
+      <c r="G43" s="30"/>
+      <c r="H43" s="30"/>
+      <c r="I43" s="30"/>
+      <c r="J43" s="33"/>
+      <c r="K43" s="33"/>
+      <c r="L43" s="30"/>
+      <c r="M43" s="30"/>
+      <c r="N43" s="49"/>
+      <c r="O43" s="18"/>
+    </row>
+    <row r="44" spans="1:15">
+      <c r="A44" s="16"/>
+      <c r="B44" s="30"/>
+      <c r="C44" s="30"/>
+      <c r="D44" s="30"/>
+      <c r="E44" s="30"/>
+      <c r="F44" s="30"/>
+      <c r="G44" s="30"/>
+      <c r="H44" s="30"/>
+      <c r="I44" s="30"/>
+      <c r="J44" s="33"/>
+      <c r="K44" s="33"/>
+      <c r="L44" s="30"/>
+      <c r="M44" s="30"/>
+      <c r="N44" s="49"/>
+      <c r="O44" s="18"/>
+    </row>
+    <row r="45" spans="1:15">
+      <c r="A45" s="16"/>
+      <c r="B45" s="30"/>
+      <c r="C45" s="30"/>
+      <c r="D45" s="30"/>
+      <c r="E45" s="30"/>
+      <c r="F45" s="30"/>
+      <c r="G45" s="30"/>
+      <c r="H45" s="30"/>
+      <c r="I45" s="30"/>
+      <c r="J45" s="33"/>
+      <c r="K45" s="33"/>
+      <c r="L45" s="30"/>
+      <c r="M45" s="30"/>
+      <c r="N45" s="49"/>
+      <c r="O45" s="18"/>
+    </row>
+    <row r="46" spans="1:15">
+      <c r="A46" s="16"/>
+      <c r="B46" s="30"/>
+      <c r="C46" s="30"/>
+      <c r="D46" s="30"/>
+      <c r="E46" s="30"/>
+      <c r="F46" s="30"/>
+      <c r="G46" s="30"/>
+      <c r="H46" s="30"/>
+      <c r="I46" s="30"/>
+      <c r="J46" s="33"/>
+      <c r="K46" s="33"/>
+      <c r="L46" s="30"/>
+      <c r="M46" s="30"/>
+      <c r="N46" s="49"/>
+      <c r="O46" s="18"/>
+    </row>
+    <row r="47" spans="1:15">
+      <c r="A47" s="16"/>
+      <c r="B47" s="30"/>
+      <c r="C47" s="30"/>
+      <c r="D47" s="30"/>
+      <c r="E47" s="30"/>
+      <c r="F47" s="30"/>
+      <c r="G47" s="30"/>
+      <c r="H47" s="30"/>
+      <c r="I47" s="30"/>
+      <c r="J47" s="33"/>
+      <c r="K47" s="33"/>
+      <c r="L47" s="30"/>
+      <c r="M47" s="30"/>
+      <c r="N47" s="49"/>
+      <c r="O47" s="18"/>
+    </row>
+    <row r="48" spans="1:15">
+      <c r="A48" s="16"/>
+      <c r="B48" s="30"/>
+      <c r="C48" s="30"/>
+      <c r="D48" s="30"/>
+      <c r="E48" s="30"/>
+      <c r="F48" s="30"/>
+      <c r="G48" s="30"/>
+      <c r="H48" s="30"/>
+      <c r="I48" s="30"/>
+      <c r="J48" s="33"/>
+      <c r="K48" s="33"/>
+      <c r="L48" s="30"/>
+      <c r="M48" s="30"/>
+      <c r="N48" s="49"/>
+      <c r="O48" s="18"/>
+    </row>
+    <row r="49" spans="1:15">
+      <c r="A49" s="16"/>
+      <c r="B49" s="30"/>
+      <c r="C49" s="30"/>
+      <c r="D49" s="30"/>
+      <c r="E49" s="30"/>
+      <c r="F49" s="30"/>
+      <c r="G49" s="30"/>
+      <c r="H49" s="30"/>
+      <c r="I49" s="30"/>
+      <c r="J49" s="33"/>
+      <c r="K49" s="33"/>
+      <c r="L49" s="30"/>
+      <c r="M49" s="30"/>
+      <c r="N49" s="49"/>
+      <c r="O49" s="18"/>
+    </row>
+    <row r="50" spans="1:15">
+      <c r="A50" s="16"/>
+      <c r="B50" s="30"/>
+      <c r="C50" s="30"/>
+      <c r="D50" s="30"/>
+      <c r="E50" s="30"/>
+      <c r="F50" s="30"/>
+      <c r="G50" s="30"/>
+      <c r="H50" s="30"/>
+      <c r="I50" s="30"/>
+      <c r="J50" s="33"/>
+      <c r="K50" s="33"/>
+      <c r="L50" s="30"/>
+      <c r="M50" s="30"/>
+      <c r="N50" s="49"/>
+      <c r="O50" s="18"/>
+    </row>
+    <row r="51" spans="1:15">
+      <c r="A51" s="16"/>
+      <c r="B51" s="30"/>
+      <c r="C51" s="30"/>
+      <c r="D51" s="30"/>
+      <c r="E51" s="30"/>
+      <c r="F51" s="30"/>
+      <c r="G51" s="30"/>
+      <c r="H51" s="30"/>
+      <c r="I51" s="30"/>
+      <c r="J51" s="33"/>
+      <c r="K51" s="33"/>
+      <c r="L51" s="30"/>
+      <c r="M51" s="30"/>
+      <c r="N51" s="49"/>
+      <c r="O51" s="18"/>
+    </row>
+    <row r="52" spans="1:15">
+      <c r="A52" s="16"/>
+      <c r="B52" s="30"/>
+      <c r="C52" s="30"/>
+      <c r="D52" s="30"/>
+      <c r="E52" s="30"/>
+      <c r="F52" s="30"/>
+      <c r="G52" s="30"/>
+      <c r="H52" s="30"/>
+      <c r="I52" s="30"/>
+      <c r="J52" s="33"/>
+      <c r="K52" s="33"/>
+      <c r="L52" s="30"/>
+      <c r="M52" s="30"/>
+      <c r="N52" s="49"/>
+      <c r="O52" s="18"/>
+    </row>
+    <row r="53" spans="1:15">
+      <c r="A53" s="16"/>
+      <c r="B53" s="30"/>
+      <c r="C53" s="30"/>
+      <c r="D53" s="30"/>
+      <c r="E53" s="30"/>
+      <c r="F53" s="30"/>
+      <c r="G53" s="30"/>
+      <c r="H53" s="30"/>
+      <c r="I53" s="30"/>
+      <c r="J53" s="33"/>
+      <c r="K53" s="33"/>
+      <c r="L53" s="30"/>
+      <c r="M53" s="30"/>
+      <c r="N53" s="49"/>
+      <c r="O53" s="18"/>
+    </row>
+    <row r="54" spans="1:15">
+      <c r="A54" s="16"/>
+      <c r="B54" s="30"/>
+      <c r="C54" s="30"/>
+      <c r="D54" s="30"/>
+      <c r="E54" s="30"/>
+      <c r="F54" s="30"/>
+      <c r="G54" s="30"/>
+      <c r="H54" s="30"/>
+      <c r="I54" s="30"/>
+      <c r="J54" s="33"/>
+      <c r="K54" s="33"/>
+      <c r="L54" s="30"/>
+      <c r="M54" s="30"/>
+      <c r="N54" s="49"/>
+      <c r="O54" s="18"/>
+    </row>
+    <row r="55" spans="1:15">
+      <c r="A55" s="16"/>
+      <c r="B55" s="30"/>
+      <c r="C55" s="30"/>
+      <c r="D55" s="30"/>
+      <c r="E55" s="30"/>
+      <c r="F55" s="30"/>
+      <c r="G55" s="30"/>
+      <c r="H55" s="30"/>
+      <c r="I55" s="30"/>
+      <c r="J55" s="33"/>
+      <c r="K55" s="33"/>
+      <c r="L55" s="30"/>
+      <c r="M55" s="30"/>
+      <c r="N55" s="49"/>
+      <c r="O55" s="18"/>
+    </row>
+    <row r="56" spans="1:15">
+      <c r="A56" s="16"/>
+      <c r="B56" s="30"/>
+      <c r="C56" s="30"/>
+      <c r="D56" s="30"/>
+      <c r="E56" s="30"/>
+      <c r="F56" s="30"/>
+      <c r="G56" s="30"/>
+      <c r="H56" s="30"/>
+      <c r="I56" s="30"/>
+      <c r="J56" s="33"/>
+      <c r="K56" s="33"/>
+      <c r="L56" s="30"/>
+      <c r="M56" s="30"/>
+      <c r="N56" s="49"/>
+      <c r="O56" s="18"/>
+    </row>
+    <row r="57" spans="1:15">
+      <c r="A57" s="16"/>
+      <c r="B57" s="30"/>
+      <c r="C57" s="30"/>
+      <c r="D57" s="30"/>
+      <c r="E57" s="30"/>
+      <c r="F57" s="30"/>
+      <c r="G57" s="30"/>
+      <c r="H57" s="30"/>
+      <c r="I57" s="30"/>
+      <c r="J57" s="33"/>
+      <c r="K57" s="33"/>
+      <c r="L57" s="30"/>
+      <c r="M57" s="30"/>
+      <c r="N57" s="49"/>
+      <c r="O57" s="18"/>
+    </row>
+    <row r="58" spans="1:15">
+      <c r="A58" s="16"/>
+      <c r="B58" s="30"/>
+      <c r="C58" s="30"/>
+      <c r="D58" s="30"/>
+      <c r="E58" s="30"/>
+      <c r="F58" s="30"/>
+      <c r="G58" s="30"/>
+      <c r="H58" s="30"/>
+      <c r="I58" s="30"/>
+      <c r="J58" s="33"/>
+      <c r="K58" s="33"/>
+      <c r="L58" s="30"/>
+      <c r="M58" s="30"/>
+      <c r="N58" s="49"/>
+      <c r="O58" s="18"/>
+    </row>
+    <row r="59" spans="1:15">
+      <c r="A59" s="16"/>
+      <c r="B59" s="30"/>
+      <c r="C59" s="30"/>
+      <c r="D59" s="30"/>
+      <c r="E59" s="30"/>
+      <c r="F59" s="30"/>
+      <c r="G59" s="30"/>
+      <c r="H59" s="30"/>
+      <c r="I59" s="30"/>
+      <c r="J59" s="33"/>
+      <c r="K59" s="33"/>
+      <c r="L59" s="30"/>
+      <c r="M59" s="30"/>
+      <c r="N59" s="49"/>
+      <c r="O59" s="18"/>
+    </row>
+    <row r="60" spans="1:15">
+      <c r="A60" s="16"/>
+      <c r="B60" s="30"/>
+      <c r="C60" s="30"/>
+      <c r="D60" s="30"/>
+      <c r="E60" s="30"/>
+      <c r="F60" s="30"/>
+      <c r="G60" s="30"/>
+      <c r="H60" s="30"/>
+      <c r="I60" s="30"/>
+      <c r="J60" s="33"/>
+      <c r="K60" s="33"/>
+      <c r="L60" s="30"/>
+      <c r="M60" s="30"/>
+      <c r="N60" s="49"/>
+      <c r="O60" s="18"/>
+    </row>
+    <row r="61" spans="1:15">
+      <c r="A61" s="16"/>
+      <c r="B61" s="30"/>
+      <c r="C61" s="30"/>
+      <c r="D61" s="30"/>
+      <c r="E61" s="30"/>
+      <c r="F61" s="30"/>
+      <c r="G61" s="30"/>
+      <c r="H61" s="30"/>
+      <c r="I61" s="30"/>
+      <c r="J61" s="33"/>
+      <c r="K61" s="33"/>
+      <c r="L61" s="30"/>
+      <c r="M61" s="30"/>
+      <c r="N61" s="49"/>
+      <c r="O61" s="18"/>
+    </row>
+    <row r="62" spans="1:15">
+      <c r="A62" s="16"/>
+      <c r="B62" s="30"/>
+      <c r="C62" s="30"/>
+      <c r="D62" s="30"/>
+      <c r="E62" s="30"/>
+      <c r="F62" s="30"/>
+      <c r="G62" s="30"/>
+      <c r="H62" s="30"/>
+      <c r="I62" s="30"/>
+      <c r="J62" s="33"/>
+      <c r="K62" s="33"/>
+      <c r="L62" s="30"/>
+      <c r="M62" s="30"/>
+      <c r="N62" s="49"/>
+      <c r="O62" s="18"/>
+    </row>
+    <row r="63" spans="1:15">
+      <c r="A63" s="16"/>
+      <c r="B63" s="30"/>
+      <c r="C63" s="30"/>
+      <c r="D63" s="30"/>
+      <c r="E63" s="30"/>
+      <c r="F63" s="30"/>
+      <c r="G63" s="30"/>
+      <c r="H63" s="30"/>
+      <c r="I63" s="30"/>
+      <c r="J63" s="33"/>
+      <c r="K63" s="33"/>
+      <c r="L63" s="30"/>
+      <c r="M63" s="30"/>
+      <c r="N63" s="49"/>
+      <c r="O63" s="18"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="J1:K1048576">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+      <formula>"高"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+      <formula>"中"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
+      <formula>"低"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" sqref="L1:M1048576" xr:uid="{A6774F23-E5C1-48B7-8180-B3FCAC7AF0E3}"/>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="5">
+        <x14:dataValidation type="list" showInputMessage="1" showErrorMessage="1" xr:uid="{7BF47E39-1372-499A-9383-FC233EFA4C0B}">
+          <x14:formula1>
+            <xm:f>TB_Check!$A:$A</xm:f>
+          </x14:formula1>
+          <xm:sqref>O1:O1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" showInputMessage="1" showErrorMessage="1" xr:uid="{719C3576-4BC1-4CA0-BAED-0E0E9E3A3D53}">
+          <x14:formula1>
+            <xm:f>TB_製程動作分析盤點!$A:$A</xm:f>
+          </x14:formula1>
+          <xm:sqref>I1:I1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{1272C6FD-708E-4F88-ADBD-9B9D2ED7ED91}">
+          <x14:formula1>
+            <xm:f>TB_製程動作分析盤點!$B:$B</xm:f>
+          </x14:formula1>
+          <xm:sqref>J2:J1048576 K1:K1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{AD511F84-635D-4B61-AE1A-99431E67F372}">
+          <x14:formula1>
+            <xm:f>TB_製程動作分析盤點!$D:$D</xm:f>
+          </x14:formula1>
+          <xm:sqref>G1:G1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" showInputMessage="1" showErrorMessage="1" xr:uid="{75ECCEE9-3C94-4CBD-A26A-087430734E6D}">
+          <x14:formula1>
+            <xm:f>TB_製程動作分析盤點!$E:$E</xm:f>
+          </x14:formula1>
+          <xm:sqref>F1:F1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
--- a/01_組織工作盤查.xlsx
+++ b/01_組織工作盤查.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Development\LeaderMethodology\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53DBD9E0-C381-4615-96AA-A612115E9028}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19992562-7BB7-4864-B0E9-8C7FECEA3FB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" activeTab="1" xr2:uid="{6274A289-9C1F-4174-8A94-9BA38FCDDB48}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{6274A289-9C1F-4174-8A94-9BA38FCDDB48}"/>
   </bookViews>
   <sheets>
     <sheet name="Guide" sheetId="1" r:id="rId1"/>
@@ -23,9 +23,11 @@
     <sheet name="B.製造 CIM" sheetId="10" r:id="rId8"/>
     <sheet name="C.製程動作分析盤點" sheetId="11" r:id="rId9"/>
     <sheet name="C.Chart" sheetId="14" r:id="rId10"/>
-    <sheet name="X.Sample" sheetId="7" r:id="rId11"/>
-    <sheet name="TB_Check" sheetId="4" r:id="rId12"/>
-    <sheet name="TB_製程動作分析盤點" sheetId="12" r:id="rId13"/>
+    <sheet name="D.新產品及機台導入" sheetId="15" r:id="rId11"/>
+    <sheet name="D.Automation" sheetId="16" r:id="rId12"/>
+    <sheet name="X.Sample" sheetId="7" r:id="rId13"/>
+    <sheet name="TB_Check" sheetId="4" r:id="rId14"/>
+    <sheet name="TB_製程動作分析盤點" sheetId="12" r:id="rId15"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -57,25 +59,13 @@
       <text>
         <r>
           <rPr>
-            <b/>
             <sz val="20"/>
             <color indexed="81"/>
             <rFont val="微軟正黑體"/>
             <family val="2"/>
             <charset val="136"/>
           </rPr>
-          <t>Cheng Ting Tsai:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="20"/>
-            <color indexed="81"/>
-            <rFont val="微軟正黑體"/>
-            <family val="2"/>
-            <charset val="136"/>
-          </rPr>
-          <t xml:space="preserve">
-1.請拆解成單一動作
+          <t>1.請拆解成單一動作
 2.請在Note欄位說明及提供:目前生產中做常遇到的瓶頸</t>
         </r>
       </text>
@@ -85,7 +75,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="204">
   <si>
     <t>文件名稱/Document</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -160,10 +150,6 @@
   </si>
   <si>
     <t>Iteam</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Data</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -230,11 +216,6 @@
   <si>
     <t>請說明及提供:產品與市場的發展
 (包含產品的演進歷程、關鍵競爭優勢及未來發展方向)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>請說明及提供:目前生產中做常遇到的瓶頸
-(包含站點、異常項目、發生時機、紀錄)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -328,10 +309,6 @@
       </rPr>
       <t>)</t>
     </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>動作分析</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1032,12 +1009,210 @@
     <t>Note</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>時常忘記，導致確認換班或OEE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Type</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Function</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>機台</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>機台功能?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>機台命名規則?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>機台名稱?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>此機台前後有哪些站點?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>站點不同，產品會有那些差異?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>機台負責人?
+(設備、產品)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自動化功能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SECS/GEM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>須提供機台所有 ECID
+ECID (Equipment constant ID) List</t>
+  </si>
+  <si>
+    <t>設定機台參數(例如:LifeTime&amp;耗材名稱&amp;參數上下限)
+Set Machine parameter</t>
+  </si>
+  <si>
+    <t>Command</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S1F13</t>
+  </si>
+  <si>
+    <t>S2F31</t>
+  </si>
+  <si>
+    <t>S1F3</t>
+  </si>
+  <si>
+    <t>S5F1</t>
+  </si>
+  <si>
+    <t>S6F11
+S2F33、S2F35、S2F37</t>
+  </si>
+  <si>
+    <t>SVID List</t>
+  </si>
+  <si>
+    <t>CEID List</t>
+  </si>
+  <si>
+    <t>ECID List</t>
+  </si>
+  <si>
+    <t>S7Fy</t>
+  </si>
+  <si>
+    <t>S2F41</t>
+  </si>
+  <si>
+    <t>S10F1、S10F5</t>
+  </si>
+  <si>
+    <t>S14F1、S14F2</t>
+  </si>
+  <si>
+    <t>S2F13</t>
+  </si>
+  <si>
+    <t>定義/解除報告，設置回報的綁定的CEID、SVID
+Define/Undefine Report，Setting Replay Bounding CEID, SVID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S2F33、S2F35、S2F37</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>List</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>機台時間 Clock 設定</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>機台所有 ALCD &amp; ALID &amp; ALTX</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自動回報機況、燈號、工單、此批作業數量、累積作業數量、進料口狀態、出料口狀態、耗材使用量、UPH、Alarm Count.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>須提供機台所有參數的SVID (操作畫面上有的、感測器量測數值、作業參數數值等)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>須提供機台所有 CEID
+CEID(Collection event ID) List</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S2F41</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>控制機台執行 PP-SELECT、LotStart、LotEnd、Stop、Lock，須提供機台所有 RCMD 清單.
+當Host端發出 Lock，機台端需有特殊權限者才能解除鎖定.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>以上項目廠商必須提供SECS/GEM通訊手冊給我方評估自動化能力，若能提供內部測試的SECS Log會更完整.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>須提供入料及出料 StripMap 格式及內容.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>須提供入料容器及出料容器條碼清單.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>機台程式上傳/下載/比對/現在是否可以設置</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>建立連線
+Offline、Online、Local、Remote</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>查詢機台資訊，指定 SVID(機況、燈號、Recipe、Qty)並回覆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>機故發生/清除 (Alarm Notification)，回報資訊包括 Alarm ID、Message.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>控制機台開始作業，例如：當一批貨放到進料口後，機台感應到並讀取條碼或RFID，回報Host端批號等資訊，Host確認相關資訊無誤後，會回覆機台正確，機台才能開始作業或執行下一步動作；
+而當 Host 沒有收到機台送來的資訊，機台不可執行任何動作，直到 Timeout 並發出警示訊息；當 Host 回覆機台錯誤，機台必須停止並發出警示訊息.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>客製化訊息，由 Host 端發出訊息給機台，顯示在機台的螢幕上及警報音以提醒作業人員.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>請參閱"D.Automation"Sheet</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>機台前後站點</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>是否為串線?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18">
+  <fonts count="17">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1152,14 +1327,6 @@
       <charset val="136"/>
     </font>
     <font>
-      <b/>
-      <sz val="20"/>
-      <color indexed="81"/>
-      <name val="微軟正黑體"/>
-      <family val="2"/>
-      <charset val="136"/>
-    </font>
-    <font>
       <sz val="20"/>
       <color indexed="81"/>
       <name val="微軟正黑體"/>
@@ -1205,7 +1372,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -1228,13 +1395,50 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1307,15 +1511,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
@@ -1361,16 +1556,22 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="14" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1382,11 +1583,32 @@
     <xf numFmtId="0" fontId="15" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3922,13 +4144,13 @@
   <dimension ref="A1:AC14"/>
   <sheetFormatPr defaultColWidth="3.6640625" defaultRowHeight="21"/>
   <cols>
-    <col min="1" max="1" width="7.77734375" style="39" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.77734375" style="36" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="3.5546875" style="22" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.44140625" style="22" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="3.5546875" style="39" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.44140625" style="40" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="3.5546875" style="40" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.44140625" style="40" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="3.5546875" style="36" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.44140625" style="37" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="3.5546875" style="37" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.21875" style="37" customWidth="1"/>
     <col min="8" max="8" width="3.5546875" style="22" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12.44140625" style="22" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="3.5546875" style="22" bestFit="1" customWidth="1"/>
@@ -3939,111 +4161,111 @@
     <col min="15" max="24" width="3.6640625" style="22"/>
     <col min="25" max="25" width="11.6640625" style="22" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="25.109375" style="22" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="3.5546875" style="39" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="12.44140625" style="40" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="3.5546875" style="36" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="12.44140625" style="37" bestFit="1" customWidth="1"/>
     <col min="29" max="16384" width="3.6640625" style="22"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="66.599999999999994" customHeight="1">
-      <c r="A1" s="42" t="s">
-        <v>92</v>
-      </c>
-      <c r="B1" s="43" t="s">
-        <v>154</v>
-      </c>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-      <c r="F1" s="43"/>
-      <c r="G1" s="43"/>
-      <c r="H1" s="43" t="s">
-        <v>153</v>
-      </c>
-      <c r="I1" s="43"/>
-      <c r="J1" s="43"/>
-      <c r="K1" s="43"/>
-      <c r="L1" s="43"/>
-      <c r="M1" s="43"/>
+      <c r="A1" s="44" t="s">
+        <v>89</v>
+      </c>
+      <c r="B1" s="48" t="s">
+        <v>151</v>
+      </c>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="48"/>
+      <c r="G1" s="48"/>
+      <c r="H1" s="48" t="s">
+        <v>150</v>
+      </c>
+      <c r="I1" s="48"/>
+      <c r="J1" s="48"/>
+      <c r="K1" s="48"/>
+      <c r="L1" s="48"/>
+      <c r="M1" s="48"/>
     </row>
     <row r="2" spans="1:29" ht="15.6">
-      <c r="A2" s="42"/>
-      <c r="B2" s="46" t="s">
+      <c r="A2" s="44"/>
+      <c r="B2" s="45" t="s">
+        <v>95</v>
+      </c>
+      <c r="C2" s="45"/>
+      <c r="D2" s="46" t="s">
+        <v>96</v>
+      </c>
+      <c r="E2" s="46"/>
+      <c r="F2" s="47" t="s">
         <v>98</v>
       </c>
-      <c r="C2" s="46"/>
-      <c r="D2" s="47" t="s">
-        <v>99</v>
-      </c>
-      <c r="E2" s="47"/>
-      <c r="F2" s="48" t="s">
-        <v>101</v>
-      </c>
-      <c r="G2" s="48"/>
-      <c r="H2" s="46" t="s">
+      <c r="G2" s="47"/>
+      <c r="H2" s="45" t="s">
+        <v>95</v>
+      </c>
+      <c r="I2" s="45"/>
+      <c r="J2" s="46" t="s">
+        <v>96</v>
+      </c>
+      <c r="K2" s="46"/>
+      <c r="L2" s="47" t="s">
         <v>98</v>
       </c>
-      <c r="I2" s="46"/>
-      <c r="J2" s="47" t="s">
-        <v>99</v>
-      </c>
-      <c r="K2" s="47"/>
-      <c r="L2" s="48" t="s">
-        <v>101</v>
-      </c>
-      <c r="M2" s="48"/>
+      <c r="M2" s="47"/>
       <c r="AA2" s="22"/>
       <c r="AB2" s="22"/>
     </row>
     <row r="3" spans="1:29">
-      <c r="A3" s="44">
+      <c r="A3" s="39">
         <f>COUNT('C.製程動作分析盤點'!A:A)</f>
         <v>4</v>
       </c>
-      <c r="B3" s="44">
+      <c r="B3" s="39">
         <f>COUNTIF('C.製程動作分析盤點'!J:J,"高")</f>
         <v>0</v>
       </c>
-      <c r="C3" s="45">
+      <c r="C3" s="40">
         <f>B3/$A$3</f>
         <v>0</v>
       </c>
-      <c r="D3" s="44">
+      <c r="D3" s="39">
         <f>COUNTIF('C.製程動作分析盤點'!J:J,"中")</f>
         <v>0</v>
       </c>
-      <c r="E3" s="45">
+      <c r="E3" s="40">
         <f>D3/$A$3</f>
         <v>0</v>
       </c>
-      <c r="F3" s="44">
+      <c r="F3" s="39">
         <f>COUNTIF('C.製程動作分析盤點'!J:J,"低")</f>
         <v>4</v>
       </c>
-      <c r="G3" s="45">
+      <c r="G3" s="40">
         <f>F3/$A$3</f>
         <v>1</v>
       </c>
-      <c r="H3" s="44">
+      <c r="H3" s="39">
         <f>COUNTIF('C.製程動作分析盤點'!K:K,"高")</f>
         <v>2</v>
       </c>
-      <c r="I3" s="45">
+      <c r="I3" s="40">
         <f>H3/$A$3</f>
         <v>0.5</v>
       </c>
-      <c r="J3" s="44">
+      <c r="J3" s="39">
         <f>COUNTIF('C.製程動作分析盤點'!K:K,"中")</f>
         <v>0</v>
       </c>
-      <c r="K3" s="45">
+      <c r="K3" s="40">
         <f>J3/$A$3</f>
         <v>0</v>
       </c>
-      <c r="L3" s="44">
+      <c r="L3" s="39">
         <f>COUNTIF('C.製程動作分析盤點'!K:K,"低")</f>
         <v>2</v>
       </c>
-      <c r="M3" s="45">
+      <c r="M3" s="40">
         <f>L3/$A$3</f>
         <v>0.5</v>
       </c>
@@ -4051,40 +4273,40 @@
       <c r="AB3" s="22"/>
     </row>
     <row r="4" spans="1:29">
-      <c r="B4" s="41"/>
-      <c r="C4" s="41"/>
-      <c r="F4" s="39"/>
-      <c r="G4" s="39"/>
+      <c r="B4" s="38"/>
+      <c r="C4" s="38"/>
+      <c r="F4" s="36"/>
+      <c r="G4" s="36"/>
       <c r="AA4" s="22"/>
       <c r="AB4" s="22"/>
     </row>
     <row r="5" spans="1:29">
-      <c r="B5" s="41"/>
-      <c r="C5" s="41"/>
-      <c r="F5" s="39"/>
-      <c r="G5" s="39"/>
+      <c r="B5" s="38"/>
+      <c r="C5" s="38"/>
+      <c r="F5" s="36"/>
+      <c r="G5" s="36"/>
       <c r="AA5" s="22"/>
       <c r="AB5" s="22"/>
     </row>
     <row r="6" spans="1:29">
-      <c r="B6" s="39"/>
-      <c r="C6" s="39"/>
-      <c r="E6" s="39"/>
-      <c r="F6" s="39"/>
-      <c r="G6" s="39"/>
+      <c r="B6" s="36"/>
+      <c r="C6" s="36"/>
+      <c r="E6" s="36"/>
+      <c r="F6" s="36"/>
+      <c r="G6" s="36"/>
       <c r="AA6" s="22"/>
       <c r="AB6" s="22"/>
     </row>
     <row r="7" spans="1:29">
-      <c r="B7" s="39"/>
-      <c r="C7" s="39"/>
-      <c r="E7" s="39"/>
-      <c r="F7" s="39"/>
-      <c r="G7" s="39"/>
-      <c r="Y7" s="39"/>
-      <c r="Z7" s="39"/>
-      <c r="AB7" s="39"/>
-      <c r="AC7" s="39"/>
+      <c r="B7" s="36"/>
+      <c r="C7" s="36"/>
+      <c r="E7" s="36"/>
+      <c r="F7" s="36"/>
+      <c r="G7" s="36"/>
+      <c r="Y7" s="36"/>
+      <c r="Z7" s="36"/>
+      <c r="AB7" s="36"/>
+      <c r="AC7" s="36"/>
     </row>
     <row r="11" spans="1:29">
       <c r="F11" s="22"/>
@@ -4121,6 +4343,468 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A4CC354-BFD0-41BE-9F77-989F437BAD38}">
+  <sheetPr>
+    <tabColor rgb="FFFFFF00"/>
+  </sheetPr>
+  <dimension ref="A1:D13"/>
+  <sheetFormatPr defaultRowHeight="15.6"/>
+  <cols>
+    <col min="1" max="1" width="7.21875" style="21" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.88671875" style="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.33203125" style="19" customWidth="1"/>
+    <col min="4" max="4" width="7.77734375" style="21" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="8.88671875" style="19"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="16" t="s">
+        <v>154</v>
+      </c>
+      <c r="C1" s="17" t="s">
+        <v>155</v>
+      </c>
+      <c r="D1" s="18" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="16">
+        <v>1</v>
+      </c>
+      <c r="B2" s="50" t="s">
+        <v>156</v>
+      </c>
+      <c r="C2" s="20" t="s">
+        <v>159</v>
+      </c>
+      <c r="D2" s="18"/>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="16">
+        <v>2</v>
+      </c>
+      <c r="B3" s="51"/>
+      <c r="C3" s="20" t="s">
+        <v>158</v>
+      </c>
+      <c r="D3" s="18"/>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="16">
+        <v>3</v>
+      </c>
+      <c r="B4" s="51"/>
+      <c r="C4" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="D4" s="18"/>
+    </row>
+    <row r="5" spans="1:4" ht="31.2">
+      <c r="A5" s="16">
+        <v>4</v>
+      </c>
+      <c r="B5" s="51"/>
+      <c r="C5" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="D5" s="18"/>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="16">
+        <v>5</v>
+      </c>
+      <c r="B6" s="53" t="s">
+        <v>163</v>
+      </c>
+      <c r="C6" s="20" t="s">
+        <v>201</v>
+      </c>
+      <c r="D6" s="18"/>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="16">
+        <v>6</v>
+      </c>
+      <c r="B7" s="16"/>
+      <c r="C7" s="20"/>
+      <c r="D7" s="18"/>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="16">
+        <v>7</v>
+      </c>
+      <c r="B8" s="16"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="18"/>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="16">
+        <v>8</v>
+      </c>
+      <c r="B9" s="50" t="s">
+        <v>202</v>
+      </c>
+      <c r="C9" s="20" t="s">
+        <v>203</v>
+      </c>
+      <c r="D9" s="18"/>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="16">
+        <v>9</v>
+      </c>
+      <c r="B10" s="51"/>
+      <c r="C10" s="20" t="s">
+        <v>160</v>
+      </c>
+      <c r="D10" s="18"/>
+    </row>
+    <row r="11" spans="1:4" ht="31.2">
+      <c r="A11" s="16">
+        <v>10</v>
+      </c>
+      <c r="B11" s="52"/>
+      <c r="C11" s="20" t="s">
+        <v>161</v>
+      </c>
+      <c r="D11" s="18"/>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="16">
+        <v>11</v>
+      </c>
+      <c r="B12" s="16"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="18"/>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="16">
+        <v>12</v>
+      </c>
+      <c r="B13" s="16"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="18"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:B5"/>
+    <mergeCell ref="B9:B11"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" showInputMessage="1" showErrorMessage="1" xr:uid="{35370D83-DF03-4DFA-ABDC-F812A7B2B8C3}">
+          <x14:formula1>
+            <xm:f>TB_Check!$A:$A</xm:f>
+          </x14:formula1>
+          <xm:sqref>D1:D1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{310231CE-E806-4AF8-8EB1-B75DCA94EB47}">
+  <sheetPr>
+    <tabColor rgb="FFFFFF00"/>
+  </sheetPr>
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr defaultRowHeight="15.6"/>
+  <cols>
+    <col min="1" max="1" width="7.33203125" style="21" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.33203125" style="19" customWidth="1"/>
+    <col min="3" max="3" width="255.77734375" style="19" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="255.77734375" style="19" customWidth="1"/>
+    <col min="5" max="5" width="7.77734375" style="21" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="8.88671875" style="19"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>155</v>
+      </c>
+      <c r="C1" s="17" t="s">
+        <v>164</v>
+      </c>
+      <c r="D1" s="17" t="s">
+        <v>168</v>
+      </c>
+      <c r="E1" s="18" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="31.2">
+      <c r="A2" s="16">
+        <v>1</v>
+      </c>
+      <c r="B2" s="54" t="s">
+        <v>165</v>
+      </c>
+      <c r="C2" s="20" t="s">
+        <v>196</v>
+      </c>
+      <c r="D2" s="20" t="s">
+        <v>169</v>
+      </c>
+      <c r="E2" s="18"/>
+    </row>
+    <row r="3" spans="1:5" ht="31.2">
+      <c r="A3" s="16">
+        <v>2</v>
+      </c>
+      <c r="B3" s="55"/>
+      <c r="C3" s="20" t="s">
+        <v>182</v>
+      </c>
+      <c r="D3" s="20" t="s">
+        <v>183</v>
+      </c>
+      <c r="E3" s="18"/>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="16">
+        <v>3</v>
+      </c>
+      <c r="B4" s="55"/>
+      <c r="C4" s="20" t="s">
+        <v>185</v>
+      </c>
+      <c r="D4" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="E4" s="18"/>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="16">
+        <v>4</v>
+      </c>
+      <c r="B5" s="55"/>
+      <c r="C5" s="20" t="s">
+        <v>197</v>
+      </c>
+      <c r="D5" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="E5" s="18"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="16">
+        <v>5</v>
+      </c>
+      <c r="B6" s="55"/>
+      <c r="C6" s="20" t="s">
+        <v>186</v>
+      </c>
+      <c r="D6" s="20" t="s">
+        <v>184</v>
+      </c>
+      <c r="E6" s="18"/>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="16">
+        <v>6</v>
+      </c>
+      <c r="B7" s="55"/>
+      <c r="C7" s="20" t="s">
+        <v>198</v>
+      </c>
+      <c r="D7" s="20" t="s">
+        <v>172</v>
+      </c>
+      <c r="E7" s="18"/>
+    </row>
+    <row r="8" spans="1:5" ht="31.2">
+      <c r="A8" s="16">
+        <v>7</v>
+      </c>
+      <c r="B8" s="55"/>
+      <c r="C8" s="20" t="s">
+        <v>187</v>
+      </c>
+      <c r="D8" s="20" t="s">
+        <v>173</v>
+      </c>
+      <c r="E8" s="18"/>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="16">
+        <v>8</v>
+      </c>
+      <c r="B9" s="55"/>
+      <c r="C9" s="20" t="s">
+        <v>188</v>
+      </c>
+      <c r="D9" s="20" t="s">
+        <v>174</v>
+      </c>
+      <c r="E9" s="18"/>
+    </row>
+    <row r="10" spans="1:5" ht="31.2">
+      <c r="A10" s="16">
+        <v>9</v>
+      </c>
+      <c r="B10" s="55"/>
+      <c r="C10" s="20" t="s">
+        <v>189</v>
+      </c>
+      <c r="D10" s="20" t="s">
+        <v>175</v>
+      </c>
+      <c r="E10" s="18"/>
+    </row>
+    <row r="11" spans="1:5" ht="31.2">
+      <c r="A11" s="16">
+        <v>10</v>
+      </c>
+      <c r="B11" s="55"/>
+      <c r="C11" s="20" t="s">
+        <v>166</v>
+      </c>
+      <c r="D11" s="20" t="s">
+        <v>176</v>
+      </c>
+      <c r="E11" s="18"/>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="16">
+        <v>11</v>
+      </c>
+      <c r="B12" s="55"/>
+      <c r="C12" s="20" t="s">
+        <v>195</v>
+      </c>
+      <c r="D12" s="20" t="s">
+        <v>177</v>
+      </c>
+      <c r="E12" s="18"/>
+    </row>
+    <row r="13" spans="1:5" ht="31.2">
+      <c r="A13" s="16">
+        <v>12</v>
+      </c>
+      <c r="B13" s="55"/>
+      <c r="C13" s="20" t="s">
+        <v>191</v>
+      </c>
+      <c r="D13" s="17" t="s">
+        <v>178</v>
+      </c>
+      <c r="E13" s="16"/>
+    </row>
+    <row r="14" spans="1:5" ht="31.2">
+      <c r="A14" s="16">
+        <v>13</v>
+      </c>
+      <c r="B14" s="55"/>
+      <c r="C14" s="20" t="s">
+        <v>199</v>
+      </c>
+      <c r="D14" s="20" t="s">
+        <v>190</v>
+      </c>
+      <c r="E14" s="18"/>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="16">
+        <v>14</v>
+      </c>
+      <c r="B15" s="55"/>
+      <c r="C15" s="17" t="s">
+        <v>200</v>
+      </c>
+      <c r="D15" s="17" t="s">
+        <v>179</v>
+      </c>
+      <c r="E15" s="16"/>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="16">
+        <v>15</v>
+      </c>
+      <c r="B16" s="55"/>
+      <c r="C16" s="17" t="s">
+        <v>193</v>
+      </c>
+      <c r="D16" s="17" t="s">
+        <v>180</v>
+      </c>
+      <c r="E16" s="16"/>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="16">
+        <v>16</v>
+      </c>
+      <c r="B17" s="55"/>
+      <c r="C17" s="17" t="s">
+        <v>194</v>
+      </c>
+      <c r="D17" s="17"/>
+      <c r="E17" s="16"/>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="16">
+        <v>17</v>
+      </c>
+      <c r="B18" s="55"/>
+      <c r="C18" s="17" t="s">
+        <v>167</v>
+      </c>
+      <c r="D18" s="17" t="s">
+        <v>181</v>
+      </c>
+      <c r="E18" s="16"/>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="16">
+        <v>18</v>
+      </c>
+      <c r="B19" s="56"/>
+      <c r="C19" s="17" t="s">
+        <v>192</v>
+      </c>
+      <c r="D19" s="17"/>
+      <c r="E19" s="16"/>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="16"/>
+      <c r="B20" s="17"/>
+      <c r="C20" s="17"/>
+      <c r="D20" s="17"/>
+      <c r="E20" s="16"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:B19"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" showInputMessage="1" showErrorMessage="1" xr:uid="{9E9A501F-8084-4F0F-85CB-8F04A62BDCA4}">
+          <x14:formula1>
+            <xm:f>TB_Check!$A:$A</xm:f>
+          </x14:formula1>
+          <xm:sqref>E1:E1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A41FB531-20B2-41BA-83FF-D38C4F8DED83}">
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
@@ -4139,10 +4823,10 @@
         <v>18</v>
       </c>
       <c r="B1" s="17" t="s">
+        <v>155</v>
+      </c>
+      <c r="C1" s="18" t="s">
         <v>19</v>
-      </c>
-      <c r="C1" s="18" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -4247,7 +4931,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B93460E-9148-431A-9979-64DD88E80E79}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15.6"/>
@@ -4257,12 +4941,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -4271,7 +4955,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7838456F-A1DD-4730-9800-D417F66E90E7}">
   <dimension ref="A1:J14"/>
   <sheetFormatPr defaultRowHeight="15.6"/>
@@ -4287,116 +4971,116 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="26" t="s">
+        <v>100</v>
+      </c>
+      <c r="B1" s="24" t="s">
+        <v>95</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="D1" s="24" t="s">
+        <v>117</v>
+      </c>
+      <c r="E1" s="26" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="26" t="s">
         <v>103</v>
       </c>
-      <c r="B1" s="27" t="s">
+      <c r="B2" s="24" t="s">
+        <v>96</v>
+      </c>
+      <c r="D2" s="24" t="s">
+        <v>124</v>
+      </c>
+      <c r="E2" s="33" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="26" t="s">
+        <v>102</v>
+      </c>
+      <c r="B3" s="24" t="s">
         <v>98</v>
       </c>
-      <c r="C1" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="D1" s="27" t="s">
+      <c r="D3" s="24" t="s">
+        <v>123</v>
+      </c>
+      <c r="E3" s="33" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="26" t="s">
+        <v>105</v>
+      </c>
+      <c r="D4" s="24" t="s">
+        <v>119</v>
+      </c>
+      <c r="E4" s="26" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="D5" s="24" t="s">
         <v>120</v>
       </c>
-      <c r="E1" s="29" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="29" t="s">
-        <v>106</v>
-      </c>
-      <c r="B2" s="27" t="s">
-        <v>99</v>
-      </c>
-      <c r="D2" s="27" t="s">
-        <v>127</v>
-      </c>
-      <c r="E2" s="36" t="s">
+      <c r="E5" s="33" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="D6" s="24" t="s">
+        <v>121</v>
+      </c>
+      <c r="E6" s="26" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="29" t="s">
-        <v>105</v>
-      </c>
-      <c r="B3" s="27" t="s">
-        <v>101</v>
-      </c>
-      <c r="D3" s="27" t="s">
-        <v>126</v>
-      </c>
-      <c r="E3" s="36" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="29" t="s">
-        <v>108</v>
-      </c>
-      <c r="D4" s="27" t="s">
-        <v>122</v>
-      </c>
-      <c r="E4" s="29" t="s">
+    <row r="7" spans="1:10">
+      <c r="E7" s="24" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
-      <c r="D5" s="27" t="s">
-        <v>123</v>
-      </c>
-      <c r="E5" s="36" t="s">
+    <row r="8" spans="1:10">
+      <c r="E8" s="24" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
-      <c r="D6" s="27" t="s">
-        <v>124</v>
-      </c>
-      <c r="E6" s="29" t="s">
+    <row r="9" spans="1:10">
+      <c r="E9" s="24" t="s">
         <v>135</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="E7" s="27" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="E8" s="27" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="E9" s="27" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="E10" s="8" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="16.2">
-      <c r="E11" s="37" t="s">
-        <v>140</v>
-      </c>
-      <c r="J11" s="28"/>
+      <c r="E11" s="34" t="s">
+        <v>137</v>
+      </c>
+      <c r="J11" s="25"/>
     </row>
     <row r="12" spans="1:10">
-      <c r="E12" s="27" t="s">
+      <c r="E12" s="24" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="E13" s="34" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
-      <c r="E13" s="37" t="s">
-        <v>144</v>
-      </c>
-    </row>
     <row r="14" spans="1:10" ht="16.2">
-      <c r="E14" s="36" t="s">
-        <v>145</v>
+      <c r="E14" s="33" t="s">
+        <v>142</v>
       </c>
     </row>
   </sheetData>
@@ -4424,71 +5108,71 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="33" customHeight="1">
-      <c r="A1" s="26" t="s">
-        <v>58</v>
-      </c>
-      <c r="B1" s="24" t="s">
-        <v>76</v>
-      </c>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
+      <c r="A1" s="43" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1" s="41" t="s">
+        <v>73</v>
+      </c>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="26"/>
+      <c r="A2" s="43"/>
       <c r="B2" s="6" t="s">
         <v>18</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D2" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>21</v>
-      </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="26"/>
+      <c r="A3" s="43"/>
       <c r="B3" s="6">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D3" s="5"/>
       <c r="E3" s="1"/>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="26"/>
+      <c r="A4" s="43"/>
       <c r="B4" s="6">
         <v>2</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D4" s="5"/>
       <c r="E4" s="1"/>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="26"/>
+      <c r="A5" s="43"/>
       <c r="B5" s="6">
         <v>3</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D5" s="5"/>
       <c r="E5" s="1"/>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="26"/>
+      <c r="A6" s="43"/>
       <c r="B6" s="6">
         <v>4</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D6" s="5"/>
       <c r="E6" s="1"/>
@@ -4497,88 +5181,88 @@
       <c r="B7" s="9"/>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="26" t="s">
-        <v>59</v>
-      </c>
-      <c r="B8" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" s="25"/>
-      <c r="D8" s="25"/>
-      <c r="E8" s="25"/>
+      <c r="A8" s="43" t="s">
+        <v>56</v>
+      </c>
+      <c r="B8" s="41" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="42"/>
+      <c r="D8" s="42"/>
+      <c r="E8" s="42"/>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="26"/>
+      <c r="A9" s="43"/>
       <c r="B9" s="6" t="s">
         <v>18</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D9" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="1" t="s">
-        <v>21</v>
-      </c>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="26"/>
+      <c r="A10" s="43"/>
       <c r="B10" s="6" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D10" s="5"/>
       <c r="E10" s="1"/>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="26"/>
+      <c r="A11" s="43"/>
       <c r="B11" s="6" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D11" s="5"/>
       <c r="E11" s="1"/>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="26"/>
+      <c r="A12" s="43"/>
       <c r="B12" s="6" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D12" s="5"/>
       <c r="E12" s="1"/>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="26"/>
+      <c r="A13" s="43"/>
       <c r="B13" s="6" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C13" s="23" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D13" s="5"/>
       <c r="E13" s="1"/>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="26"/>
+      <c r="A14" s="43"/>
       <c r="B14" s="6" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="5"/>
       <c r="E14" s="1"/>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="26"/>
+      <c r="A15" s="43"/>
       <c r="B15" s="6" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="5"/>
@@ -4627,10 +5311,10 @@
         <v>18</v>
       </c>
       <c r="B1" s="17" t="s">
+        <v>155</v>
+      </c>
+      <c r="C1" s="18" t="s">
         <v>19</v>
-      </c>
-      <c r="C1" s="18" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="31.2">
@@ -4638,7 +5322,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="20" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C2" s="18"/>
     </row>
@@ -4647,7 +5331,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C3" s="18"/>
     </row>
@@ -4656,7 +5340,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C4" s="18"/>
     </row>
@@ -4665,7 +5349,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C5" s="18"/>
     </row>
@@ -4674,7 +5358,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C6" s="18"/>
     </row>
@@ -4683,7 +5367,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C7" s="18"/>
     </row>
@@ -4692,7 +5376,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C8" s="18"/>
     </row>
@@ -4701,7 +5385,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="20" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C9" s="18"/>
     </row>
@@ -4710,7 +5394,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="20" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C10" s="18"/>
     </row>
@@ -4719,7 +5403,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="20" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C11" s="18"/>
     </row>
@@ -4728,7 +5412,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="20" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C12" s="18"/>
     </row>
@@ -4737,7 +5421,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="20" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C13" s="18"/>
     </row>
@@ -4764,7 +5448,7 @@
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="7.5546875" style="15" bestFit="1" customWidth="1"/>
@@ -4778,10 +5462,10 @@
         <v>18</v>
       </c>
       <c r="B1" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="C1" s="12" t="s">
         <v>19</v>
-      </c>
-      <c r="C1" s="12" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="31.2">
@@ -4789,7 +5473,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C2" s="12"/>
     </row>
@@ -4798,7 +5482,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C3" s="12"/>
     </row>
@@ -4807,7 +5491,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C4" s="12"/>
     </row>
@@ -4816,7 +5500,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C5" s="12"/>
     </row>
@@ -4825,7 +5509,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C6" s="12"/>
     </row>
@@ -4834,7 +5518,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C7" s="12"/>
     </row>
@@ -4843,7 +5527,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C8" s="12"/>
     </row>
@@ -4852,7 +5536,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C9" s="12"/>
     </row>
@@ -4879,16 +5563,6 @@
     <row r="15" spans="1:3">
       <c r="A15" s="13"/>
       <c r="C15" s="13"/>
-    </row>
-    <row r="17" spans="2:2" ht="31.2">
-      <c r="B17" s="14" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="18" spans="2:2">
-      <c r="B18" s="13" t="s">
-        <v>52</v>
-      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -4913,7 +5587,7 @@
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="7.5546875" style="21" bestFit="1" customWidth="1"/>
@@ -4927,10 +5601,10 @@
         <v>18</v>
       </c>
       <c r="B1" s="17" t="s">
+        <v>155</v>
+      </c>
+      <c r="C1" s="18" t="s">
         <v>19</v>
-      </c>
-      <c r="C1" s="18" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -4938,7 +5612,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="20" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C2" s="18"/>
     </row>
@@ -4947,7 +5621,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C3" s="18"/>
     </row>
@@ -4956,7 +5630,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C4" s="18"/>
     </row>
@@ -4965,7 +5639,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C5" s="18"/>
     </row>
@@ -4974,19 +5648,9 @@
         <v>5</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C6" s="18"/>
-    </row>
-    <row r="9" spans="1:3" ht="31.2">
-      <c r="B9" s="14" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="B10" s="13" t="s">
-        <v>52</v>
-      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -5025,10 +5689,10 @@
         <v>18</v>
       </c>
       <c r="B1" s="17" t="s">
+        <v>155</v>
+      </c>
+      <c r="C1" s="18" t="s">
         <v>19</v>
-      </c>
-      <c r="C1" s="18" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="31.2">
@@ -5036,7 +5700,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="20" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C2" s="18"/>
     </row>
@@ -5045,7 +5709,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C3" s="18"/>
     </row>
@@ -5054,7 +5718,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C4" s="18"/>
     </row>
@@ -5063,7 +5727,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C5" s="18"/>
     </row>
@@ -5128,10 +5792,10 @@
         <v>18</v>
       </c>
       <c r="B1" s="17" t="s">
+        <v>155</v>
+      </c>
+      <c r="C1" s="18" t="s">
         <v>19</v>
-      </c>
-      <c r="C1" s="18" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="46.8">
@@ -5139,7 +5803,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="20" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C2" s="18"/>
     </row>
@@ -5148,7 +5812,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C3" s="18"/>
     </row>
@@ -5157,7 +5821,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C4" s="18"/>
     </row>
@@ -5166,7 +5830,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C5" s="18"/>
     </row>
@@ -5175,7 +5839,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C6" s="18"/>
     </row>
@@ -5248,10 +5912,10 @@
         <v>18</v>
       </c>
       <c r="B1" s="17" t="s">
+        <v>155</v>
+      </c>
+      <c r="C1" s="18" t="s">
         <v>19</v>
-      </c>
-      <c r="C1" s="18" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="31.2">
@@ -5259,7 +5923,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="20" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C2" s="18"/>
     </row>
@@ -5268,7 +5932,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C3" s="18"/>
     </row>
@@ -5277,7 +5941,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C4" s="18"/>
     </row>
@@ -5286,7 +5950,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C5" s="18"/>
     </row>
@@ -5295,7 +5959,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C6" s="18"/>
     </row>
@@ -5304,7 +5968,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C7" s="18"/>
     </row>
@@ -5313,7 +5977,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C8" s="18"/>
     </row>
@@ -5322,7 +5986,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="20" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C9" s="18"/>
     </row>
@@ -5331,7 +5995,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="20" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C10" s="18"/>
     </row>
@@ -5340,7 +6004,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="20" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C11" s="18"/>
     </row>
@@ -5379,1218 +6043,1222 @@
     <col min="7" max="7" width="10.6640625" style="19" customWidth="1"/>
     <col min="8" max="8" width="28.21875" style="19" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="19.44140625" style="19" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21.88671875" style="34" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="25.44140625" style="34" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.88671875" style="31" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="25.44140625" style="31" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="30.44140625" style="19" customWidth="1"/>
     <col min="13" max="13" width="10.44140625" style="19" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.88671875" style="19"/>
+    <col min="14" max="14" width="26.5546875" style="49" customWidth="1"/>
     <col min="15" max="15" width="7.77734375" style="21" bestFit="1" customWidth="1"/>
     <col min="16" max="16384" width="8.88671875" style="19"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="62.4">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="31" t="s">
-        <v>89</v>
-      </c>
-      <c r="C1" s="31" t="s">
+      <c r="B1" s="28" t="s">
+        <v>86</v>
+      </c>
+      <c r="C1" s="28" t="s">
+        <v>87</v>
+      </c>
+      <c r="D1" s="28" t="s">
+        <v>88</v>
+      </c>
+      <c r="E1" s="28" t="s">
+        <v>110</v>
+      </c>
+      <c r="F1" s="28" t="s">
+        <v>111</v>
+      </c>
+      <c r="G1" s="32" t="s">
+        <v>115</v>
+      </c>
+      <c r="H1" s="29" t="s">
         <v>90</v>
       </c>
-      <c r="D1" s="31" t="s">
+      <c r="I1" s="29" t="s">
+        <v>104</v>
+      </c>
+      <c r="J1" s="29" t="s">
+        <v>149</v>
+      </c>
+      <c r="K1" s="29" t="s">
+        <v>93</v>
+      </c>
+      <c r="L1" s="29" t="s">
         <v>91</v>
       </c>
-      <c r="E1" s="31" t="s">
-        <v>113</v>
-      </c>
-      <c r="F1" s="31" t="s">
-        <v>114</v>
-      </c>
-      <c r="G1" s="35" t="s">
-        <v>118</v>
-      </c>
-      <c r="H1" s="32" t="s">
-        <v>93</v>
-      </c>
-      <c r="I1" s="32" t="s">
-        <v>107</v>
-      </c>
-      <c r="J1" s="32" t="s">
+      <c r="M1" s="29" t="s">
+        <v>92</v>
+      </c>
+      <c r="N1" s="29" t="s">
         <v>152</v>
       </c>
-      <c r="K1" s="32" t="s">
-        <v>96</v>
-      </c>
-      <c r="L1" s="32" t="s">
-        <v>94</v>
-      </c>
-      <c r="M1" s="32" t="s">
-        <v>95</v>
-      </c>
-      <c r="N1" s="50" t="s">
-        <v>155</v>
-      </c>
       <c r="O1" s="18" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="31.2">
       <c r="A2" s="16">
         <v>1</v>
       </c>
-      <c r="B2" s="30" t="s">
+      <c r="B2" s="27" t="s">
+        <v>106</v>
+      </c>
+      <c r="C2" s="27" t="s">
+        <v>107</v>
+      </c>
+      <c r="D2" s="27" t="s">
+        <v>108</v>
+      </c>
+      <c r="E2" s="27" t="s">
         <v>109</v>
       </c>
-      <c r="C2" s="30" t="s">
-        <v>110</v>
-      </c>
-      <c r="D2" s="30" t="s">
-        <v>111</v>
-      </c>
-      <c r="E2" s="30" t="s">
+      <c r="F2" s="27" t="s">
         <v>112</v>
       </c>
-      <c r="F2" s="30" t="s">
-        <v>115</v>
-      </c>
-      <c r="G2" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="H2" s="30" t="s">
-        <v>128</v>
-      </c>
-      <c r="I2" s="30" t="s">
-        <v>104</v>
-      </c>
-      <c r="J2" s="33" t="s">
-        <v>100</v>
-      </c>
-      <c r="K2" s="33" t="s">
+      <c r="G2" s="27" t="s">
+        <v>118</v>
+      </c>
+      <c r="H2" s="27" t="s">
+        <v>125</v>
+      </c>
+      <c r="I2" s="27" t="s">
+        <v>101</v>
+      </c>
+      <c r="J2" s="30" t="s">
         <v>97</v>
       </c>
-      <c r="L2" s="30" t="s">
-        <v>116</v>
-      </c>
-      <c r="M2" s="30" t="s">
-        <v>117</v>
-      </c>
-      <c r="N2" s="49"/>
+      <c r="K2" s="30" t="s">
+        <v>94</v>
+      </c>
+      <c r="L2" s="27" t="s">
+        <v>113</v>
+      </c>
+      <c r="M2" s="27" t="s">
+        <v>114</v>
+      </c>
+      <c r="N2" s="27"/>
       <c r="O2" s="18"/>
     </row>
     <row r="3" spans="1:15" ht="46.8">
       <c r="A3" s="16">
         <v>2</v>
       </c>
-      <c r="B3" s="30" t="s">
-        <v>109</v>
-      </c>
-      <c r="C3" s="30" t="s">
-        <v>110</v>
-      </c>
-      <c r="D3" s="30" t="s">
-        <v>111</v>
-      </c>
-      <c r="E3" s="30" t="s">
-        <v>129</v>
-      </c>
-      <c r="F3" s="30" t="s">
-        <v>130</v>
-      </c>
-      <c r="G3" s="30" t="s">
+      <c r="B3" s="27" t="s">
+        <v>106</v>
+      </c>
+      <c r="C3" s="27" t="s">
+        <v>107</v>
+      </c>
+      <c r="D3" s="27" t="s">
+        <v>108</v>
+      </c>
+      <c r="E3" s="27" t="s">
+        <v>126</v>
+      </c>
+      <c r="F3" s="27" t="s">
+        <v>127</v>
+      </c>
+      <c r="G3" s="27" t="s">
+        <v>122</v>
+      </c>
+      <c r="H3" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="H3" s="30" t="s">
-        <v>128</v>
-      </c>
-      <c r="I3" s="30" t="s">
-        <v>104</v>
-      </c>
-      <c r="J3" s="33" t="s">
-        <v>100</v>
-      </c>
-      <c r="K3" s="33" t="s">
+      <c r="I3" s="27" t="s">
+        <v>101</v>
+      </c>
+      <c r="J3" s="30" t="s">
         <v>97</v>
       </c>
-      <c r="L3" s="30" t="s">
-        <v>102</v>
-      </c>
-      <c r="M3" s="38" t="s">
-        <v>149</v>
-      </c>
-      <c r="N3" s="49"/>
+      <c r="K3" s="30" t="s">
+        <v>94</v>
+      </c>
+      <c r="L3" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="M3" s="35" t="s">
+        <v>146</v>
+      </c>
+      <c r="N3" s="27"/>
       <c r="O3" s="18"/>
     </row>
     <row r="4" spans="1:15" ht="31.2">
       <c r="A4" s="16">
         <v>3</v>
       </c>
-      <c r="B4" s="30" t="s">
-        <v>109</v>
-      </c>
-      <c r="C4" s="30" t="s">
-        <v>110</v>
-      </c>
-      <c r="D4" s="30" t="s">
-        <v>142</v>
-      </c>
-      <c r="E4" s="30" t="s">
+      <c r="B4" s="27" t="s">
+        <v>106</v>
+      </c>
+      <c r="C4" s="27" t="s">
+        <v>107</v>
+      </c>
+      <c r="D4" s="27" t="s">
+        <v>139</v>
+      </c>
+      <c r="E4" s="27" t="s">
+        <v>140</v>
+      </c>
+      <c r="F4" s="27" t="s">
         <v>143</v>
       </c>
-      <c r="F4" s="30" t="s">
-        <v>146</v>
-      </c>
-      <c r="G4" s="30" t="s">
-        <v>119</v>
-      </c>
-      <c r="H4" s="30" t="s">
+      <c r="G4" s="27" t="s">
+        <v>116</v>
+      </c>
+      <c r="H4" s="27" t="s">
+        <v>144</v>
+      </c>
+      <c r="I4" s="27" t="s">
+        <v>101</v>
+      </c>
+      <c r="J4" s="30" t="s">
+        <v>97</v>
+      </c>
+      <c r="K4" s="30" t="s">
+        <v>97</v>
+      </c>
+      <c r="L4" s="27" t="s">
+        <v>145</v>
+      </c>
+      <c r="M4" s="27" t="s">
         <v>147</v>
       </c>
-      <c r="I4" s="30" t="s">
-        <v>104</v>
-      </c>
-      <c r="J4" s="33" t="s">
-        <v>100</v>
-      </c>
-      <c r="K4" s="33" t="s">
-        <v>100</v>
-      </c>
-      <c r="L4" s="30" t="s">
-        <v>148</v>
-      </c>
-      <c r="M4" s="30" t="s">
-        <v>150</v>
-      </c>
-      <c r="N4" s="49"/>
+      <c r="N4" s="27" t="s">
+        <v>153</v>
+      </c>
       <c r="O4" s="18"/>
     </row>
     <row r="5" spans="1:15" ht="31.2">
       <c r="A5" s="16">
         <v>4</v>
       </c>
-      <c r="B5" s="30" t="s">
-        <v>109</v>
-      </c>
-      <c r="C5" s="30" t="s">
-        <v>110</v>
-      </c>
-      <c r="D5" s="30" t="s">
-        <v>142</v>
-      </c>
-      <c r="E5" s="30" t="s">
-        <v>151</v>
-      </c>
-      <c r="F5" s="30" t="s">
-        <v>146</v>
-      </c>
-      <c r="G5" s="30" t="s">
-        <v>119</v>
-      </c>
-      <c r="H5" s="30" t="s">
+      <c r="B5" s="27" t="s">
+        <v>106</v>
+      </c>
+      <c r="C5" s="27" t="s">
+        <v>107</v>
+      </c>
+      <c r="D5" s="27" t="s">
+        <v>139</v>
+      </c>
+      <c r="E5" s="27" t="s">
+        <v>148</v>
+      </c>
+      <c r="F5" s="27" t="s">
+        <v>143</v>
+      </c>
+      <c r="G5" s="27" t="s">
+        <v>116</v>
+      </c>
+      <c r="H5" s="27" t="s">
+        <v>144</v>
+      </c>
+      <c r="I5" s="27" t="s">
+        <v>101</v>
+      </c>
+      <c r="J5" s="30" t="s">
+        <v>97</v>
+      </c>
+      <c r="K5" s="30" t="s">
+        <v>97</v>
+      </c>
+      <c r="L5" s="27" t="s">
+        <v>145</v>
+      </c>
+      <c r="M5" s="27" t="s">
         <v>147</v>
       </c>
-      <c r="I5" s="30" t="s">
-        <v>104</v>
-      </c>
-      <c r="J5" s="33" t="s">
-        <v>100</v>
-      </c>
-      <c r="K5" s="33" t="s">
-        <v>100</v>
-      </c>
-      <c r="L5" s="30" t="s">
-        <v>148</v>
-      </c>
-      <c r="M5" s="30" t="s">
-        <v>150</v>
-      </c>
-      <c r="N5" s="49"/>
+      <c r="N5" s="27" t="s">
+        <v>153</v>
+      </c>
       <c r="O5" s="18"/>
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="16"/>
-      <c r="B6" s="30"/>
-      <c r="C6" s="30"/>
-      <c r="D6" s="30"/>
-      <c r="E6" s="30"/>
-      <c r="F6" s="30"/>
-      <c r="G6" s="30"/>
-      <c r="H6" s="30"/>
-      <c r="I6" s="30"/>
-      <c r="J6" s="33"/>
-      <c r="K6" s="33"/>
-      <c r="L6" s="30"/>
-      <c r="M6" s="30"/>
-      <c r="N6" s="49"/>
+      <c r="B6" s="27"/>
+      <c r="C6" s="27"/>
+      <c r="D6" s="27"/>
+      <c r="E6" s="27"/>
+      <c r="F6" s="27"/>
+      <c r="G6" s="27"/>
+      <c r="H6" s="27"/>
+      <c r="I6" s="27"/>
+      <c r="J6" s="30"/>
+      <c r="K6" s="30"/>
+      <c r="L6" s="27"/>
+      <c r="M6" s="27"/>
+      <c r="N6" s="27"/>
       <c r="O6" s="18"/>
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="16"/>
-      <c r="B7" s="30"/>
-      <c r="C7" s="30"/>
-      <c r="D7" s="30"/>
-      <c r="E7" s="30"/>
-      <c r="F7" s="30"/>
-      <c r="G7" s="30"/>
-      <c r="H7" s="30"/>
-      <c r="I7" s="30"/>
-      <c r="J7" s="33"/>
-      <c r="K7" s="33"/>
-      <c r="L7" s="30"/>
-      <c r="M7" s="30"/>
-      <c r="N7" s="49"/>
+      <c r="B7" s="27"/>
+      <c r="C7" s="27"/>
+      <c r="D7" s="27"/>
+      <c r="E7" s="27"/>
+      <c r="F7" s="27"/>
+      <c r="G7" s="27"/>
+      <c r="H7" s="27"/>
+      <c r="I7" s="27"/>
+      <c r="J7" s="30"/>
+      <c r="K7" s="30"/>
+      <c r="L7" s="27"/>
+      <c r="M7" s="27"/>
+      <c r="N7" s="27"/>
       <c r="O7" s="18"/>
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="16"/>
-      <c r="B8" s="30"/>
-      <c r="C8" s="30"/>
-      <c r="D8" s="30"/>
-      <c r="E8" s="30"/>
-      <c r="F8" s="30"/>
-      <c r="G8" s="30"/>
-      <c r="H8" s="30"/>
-      <c r="I8" s="30"/>
-      <c r="J8" s="33"/>
-      <c r="K8" s="33"/>
-      <c r="L8" s="30"/>
-      <c r="M8" s="30"/>
-      <c r="N8" s="49"/>
+      <c r="B8" s="27"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="27"/>
+      <c r="G8" s="27"/>
+      <c r="H8" s="27"/>
+      <c r="I8" s="27"/>
+      <c r="J8" s="30"/>
+      <c r="K8" s="30"/>
+      <c r="L8" s="27"/>
+      <c r="M8" s="27"/>
+      <c r="N8" s="27"/>
       <c r="O8" s="18"/>
     </row>
     <row r="9" spans="1:15">
       <c r="A9" s="16"/>
-      <c r="B9" s="30"/>
-      <c r="C9" s="30"/>
-      <c r="D9" s="30"/>
-      <c r="E9" s="30"/>
-      <c r="F9" s="30"/>
-      <c r="G9" s="30"/>
-      <c r="H9" s="30"/>
-      <c r="I9" s="30"/>
-      <c r="J9" s="33"/>
-      <c r="K9" s="33"/>
-      <c r="L9" s="30"/>
-      <c r="M9" s="30"/>
-      <c r="N9" s="49"/>
+      <c r="B9" s="27"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="27"/>
+      <c r="F9" s="27"/>
+      <c r="G9" s="27"/>
+      <c r="H9" s="27"/>
+      <c r="I9" s="27"/>
+      <c r="J9" s="30"/>
+      <c r="K9" s="30"/>
+      <c r="L9" s="27"/>
+      <c r="M9" s="27"/>
+      <c r="N9" s="27"/>
       <c r="O9" s="18"/>
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="16"/>
-      <c r="B10" s="30"/>
-      <c r="C10" s="30"/>
-      <c r="D10" s="30"/>
-      <c r="E10" s="30"/>
-      <c r="F10" s="30"/>
-      <c r="G10" s="30"/>
-      <c r="H10" s="30"/>
-      <c r="I10" s="30"/>
-      <c r="J10" s="33"/>
-      <c r="K10" s="33"/>
-      <c r="L10" s="30"/>
-      <c r="M10" s="30"/>
-      <c r="N10" s="49"/>
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="27"/>
+      <c r="G10" s="27"/>
+      <c r="H10" s="27"/>
+      <c r="I10" s="27"/>
+      <c r="J10" s="30"/>
+      <c r="K10" s="30"/>
+      <c r="L10" s="27"/>
+      <c r="M10" s="27"/>
+      <c r="N10" s="27"/>
       <c r="O10" s="18"/>
     </row>
     <row r="11" spans="1:15">
       <c r="A11" s="16"/>
-      <c r="B11" s="30"/>
-      <c r="C11" s="30"/>
-      <c r="D11" s="30"/>
-      <c r="E11" s="30"/>
-      <c r="F11" s="30"/>
-      <c r="G11" s="30"/>
-      <c r="H11" s="30"/>
-      <c r="I11" s="30"/>
-      <c r="J11" s="33"/>
-      <c r="K11" s="33"/>
-      <c r="L11" s="30"/>
-      <c r="M11" s="30"/>
-      <c r="N11" s="49"/>
+      <c r="B11" s="27"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="27"/>
+      <c r="E11" s="27"/>
+      <c r="F11" s="27"/>
+      <c r="G11" s="27"/>
+      <c r="H11" s="27"/>
+      <c r="I11" s="27"/>
+      <c r="J11" s="30"/>
+      <c r="K11" s="30"/>
+      <c r="L11" s="27"/>
+      <c r="M11" s="27"/>
+      <c r="N11" s="27"/>
       <c r="O11" s="18"/>
     </row>
     <row r="12" spans="1:15">
       <c r="A12" s="16"/>
-      <c r="B12" s="30"/>
-      <c r="C12" s="30"/>
-      <c r="D12" s="30"/>
-      <c r="E12" s="30"/>
-      <c r="F12" s="30"/>
-      <c r="G12" s="30"/>
-      <c r="H12" s="30"/>
-      <c r="I12" s="30"/>
-      <c r="J12" s="33"/>
-      <c r="K12" s="33"/>
-      <c r="L12" s="30"/>
-      <c r="M12" s="30"/>
-      <c r="N12" s="49"/>
+      <c r="B12" s="27"/>
+      <c r="C12" s="27"/>
+      <c r="D12" s="27"/>
+      <c r="E12" s="27"/>
+      <c r="F12" s="27"/>
+      <c r="G12" s="27"/>
+      <c r="H12" s="27"/>
+      <c r="I12" s="27"/>
+      <c r="J12" s="30"/>
+      <c r="K12" s="30"/>
+      <c r="L12" s="27"/>
+      <c r="M12" s="27"/>
+      <c r="N12" s="27"/>
       <c r="O12" s="18"/>
     </row>
     <row r="13" spans="1:15">
       <c r="A13" s="16"/>
-      <c r="B13" s="30"/>
-      <c r="C13" s="30"/>
-      <c r="D13" s="30"/>
-      <c r="E13" s="30"/>
-      <c r="F13" s="30"/>
-      <c r="G13" s="30"/>
-      <c r="H13" s="30"/>
-      <c r="I13" s="30"/>
-      <c r="J13" s="33"/>
-      <c r="K13" s="33"/>
-      <c r="L13" s="30"/>
-      <c r="M13" s="30"/>
-      <c r="N13" s="49"/>
+      <c r="B13" s="27"/>
+      <c r="C13" s="27"/>
+      <c r="D13" s="27"/>
+      <c r="E13" s="27"/>
+      <c r="F13" s="27"/>
+      <c r="G13" s="27"/>
+      <c r="H13" s="27"/>
+      <c r="I13" s="27"/>
+      <c r="J13" s="30"/>
+      <c r="K13" s="30"/>
+      <c r="L13" s="27"/>
+      <c r="M13" s="27"/>
+      <c r="N13" s="27"/>
       <c r="O13" s="18"/>
     </row>
     <row r="14" spans="1:15">
       <c r="A14" s="16"/>
-      <c r="B14" s="30"/>
-      <c r="C14" s="30"/>
-      <c r="D14" s="30"/>
-      <c r="E14" s="30"/>
-      <c r="F14" s="30"/>
-      <c r="G14" s="30"/>
-      <c r="H14" s="30"/>
-      <c r="I14" s="30"/>
-      <c r="J14" s="33"/>
-      <c r="K14" s="33"/>
-      <c r="L14" s="30"/>
-      <c r="M14" s="30"/>
-      <c r="N14" s="49"/>
+      <c r="B14" s="27"/>
+      <c r="C14" s="27"/>
+      <c r="D14" s="27"/>
+      <c r="E14" s="27"/>
+      <c r="F14" s="27"/>
+      <c r="G14" s="27"/>
+      <c r="H14" s="27"/>
+      <c r="I14" s="27"/>
+      <c r="J14" s="30"/>
+      <c r="K14" s="30"/>
+      <c r="L14" s="27"/>
+      <c r="M14" s="27"/>
+      <c r="N14" s="27"/>
       <c r="O14" s="18"/>
     </row>
     <row r="15" spans="1:15">
       <c r="A15" s="16"/>
-      <c r="B15" s="30"/>
-      <c r="C15" s="30"/>
-      <c r="D15" s="30"/>
-      <c r="E15" s="30"/>
-      <c r="F15" s="30"/>
-      <c r="G15" s="30"/>
-      <c r="H15" s="30"/>
-      <c r="I15" s="30"/>
-      <c r="J15" s="33"/>
-      <c r="K15" s="33"/>
-      <c r="L15" s="30"/>
-      <c r="M15" s="30"/>
-      <c r="N15" s="49"/>
+      <c r="B15" s="27"/>
+      <c r="C15" s="27"/>
+      <c r="D15" s="27"/>
+      <c r="E15" s="27"/>
+      <c r="F15" s="27"/>
+      <c r="G15" s="27"/>
+      <c r="H15" s="27"/>
+      <c r="I15" s="27"/>
+      <c r="J15" s="30"/>
+      <c r="K15" s="30"/>
+      <c r="L15" s="27"/>
+      <c r="M15" s="27"/>
+      <c r="N15" s="27"/>
       <c r="O15" s="18"/>
     </row>
     <row r="16" spans="1:15">
       <c r="A16" s="16"/>
-      <c r="B16" s="30"/>
-      <c r="C16" s="30"/>
-      <c r="D16" s="30"/>
-      <c r="E16" s="30"/>
-      <c r="F16" s="30"/>
-      <c r="G16" s="30"/>
-      <c r="H16" s="30"/>
-      <c r="I16" s="30"/>
-      <c r="J16" s="33"/>
-      <c r="K16" s="33"/>
-      <c r="L16" s="30"/>
-      <c r="M16" s="30"/>
-      <c r="N16" s="49"/>
+      <c r="B16" s="27"/>
+      <c r="C16" s="27"/>
+      <c r="D16" s="27"/>
+      <c r="E16" s="27"/>
+      <c r="F16" s="27"/>
+      <c r="G16" s="27"/>
+      <c r="H16" s="27"/>
+      <c r="I16" s="27"/>
+      <c r="J16" s="30"/>
+      <c r="K16" s="30"/>
+      <c r="L16" s="27"/>
+      <c r="M16" s="27"/>
+      <c r="N16" s="27"/>
       <c r="O16" s="18"/>
     </row>
     <row r="17" spans="1:15">
       <c r="A17" s="16"/>
-      <c r="B17" s="30"/>
-      <c r="C17" s="30"/>
-      <c r="D17" s="30"/>
-      <c r="E17" s="30"/>
-      <c r="F17" s="30"/>
-      <c r="G17" s="30"/>
-      <c r="H17" s="30"/>
-      <c r="I17" s="30"/>
-      <c r="J17" s="33"/>
-      <c r="K17" s="33"/>
-      <c r="L17" s="30"/>
-      <c r="M17" s="30"/>
-      <c r="N17" s="49"/>
+      <c r="B17" s="27"/>
+      <c r="C17" s="27"/>
+      <c r="D17" s="27"/>
+      <c r="E17" s="27"/>
+      <c r="F17" s="27"/>
+      <c r="G17" s="27"/>
+      <c r="H17" s="27"/>
+      <c r="I17" s="27"/>
+      <c r="J17" s="30"/>
+      <c r="K17" s="30"/>
+      <c r="L17" s="27"/>
+      <c r="M17" s="27"/>
+      <c r="N17" s="27"/>
       <c r="O17" s="18"/>
     </row>
     <row r="18" spans="1:15">
       <c r="A18" s="16"/>
-      <c r="B18" s="30"/>
-      <c r="C18" s="30"/>
-      <c r="D18" s="30"/>
-      <c r="E18" s="30"/>
-      <c r="F18" s="30"/>
-      <c r="G18" s="30"/>
-      <c r="H18" s="30"/>
-      <c r="I18" s="30"/>
-      <c r="J18" s="33"/>
-      <c r="K18" s="33"/>
-      <c r="L18" s="30"/>
-      <c r="M18" s="30"/>
-      <c r="N18" s="49"/>
+      <c r="B18" s="27"/>
+      <c r="C18" s="27"/>
+      <c r="D18" s="27"/>
+      <c r="E18" s="27"/>
+      <c r="F18" s="27"/>
+      <c r="G18" s="27"/>
+      <c r="H18" s="27"/>
+      <c r="I18" s="27"/>
+      <c r="J18" s="30"/>
+      <c r="K18" s="30"/>
+      <c r="L18" s="27"/>
+      <c r="M18" s="27"/>
+      <c r="N18" s="27"/>
       <c r="O18" s="18"/>
     </row>
     <row r="19" spans="1:15">
       <c r="A19" s="16"/>
-      <c r="B19" s="30"/>
-      <c r="C19" s="30"/>
-      <c r="D19" s="30"/>
-      <c r="E19" s="30"/>
-      <c r="F19" s="30"/>
-      <c r="G19" s="30"/>
-      <c r="H19" s="30"/>
-      <c r="I19" s="30"/>
-      <c r="J19" s="33"/>
-      <c r="K19" s="33"/>
-      <c r="L19" s="30"/>
-      <c r="M19" s="30"/>
-      <c r="N19" s="49"/>
+      <c r="B19" s="27"/>
+      <c r="C19" s="27"/>
+      <c r="D19" s="27"/>
+      <c r="E19" s="27"/>
+      <c r="F19" s="27"/>
+      <c r="G19" s="27"/>
+      <c r="H19" s="27"/>
+      <c r="I19" s="27"/>
+      <c r="J19" s="30"/>
+      <c r="K19" s="30"/>
+      <c r="L19" s="27"/>
+      <c r="M19" s="27"/>
+      <c r="N19" s="27"/>
       <c r="O19" s="18"/>
     </row>
     <row r="20" spans="1:15">
       <c r="A20" s="16"/>
-      <c r="B20" s="30"/>
-      <c r="C20" s="30"/>
-      <c r="D20" s="30"/>
-      <c r="E20" s="30"/>
-      <c r="F20" s="30"/>
-      <c r="G20" s="30"/>
-      <c r="H20" s="30"/>
-      <c r="I20" s="30"/>
-      <c r="J20" s="33"/>
-      <c r="K20" s="33"/>
-      <c r="L20" s="30"/>
-      <c r="M20" s="30"/>
-      <c r="N20" s="49"/>
+      <c r="B20" s="27"/>
+      <c r="C20" s="27"/>
+      <c r="D20" s="27"/>
+      <c r="E20" s="27"/>
+      <c r="F20" s="27"/>
+      <c r="G20" s="27"/>
+      <c r="H20" s="27"/>
+      <c r="I20" s="27"/>
+      <c r="J20" s="30"/>
+      <c r="K20" s="30"/>
+      <c r="L20" s="27"/>
+      <c r="M20" s="27"/>
+      <c r="N20" s="27"/>
       <c r="O20" s="18"/>
     </row>
     <row r="21" spans="1:15">
       <c r="A21" s="16"/>
-      <c r="B21" s="30"/>
-      <c r="C21" s="30"/>
-      <c r="D21" s="30"/>
-      <c r="E21" s="30"/>
-      <c r="F21" s="30"/>
-      <c r="G21" s="30"/>
-      <c r="H21" s="30"/>
-      <c r="I21" s="30"/>
-      <c r="J21" s="33"/>
-      <c r="K21" s="33"/>
-      <c r="L21" s="30"/>
-      <c r="M21" s="30"/>
-      <c r="N21" s="49"/>
+      <c r="B21" s="27"/>
+      <c r="C21" s="27"/>
+      <c r="D21" s="27"/>
+      <c r="E21" s="27"/>
+      <c r="F21" s="27"/>
+      <c r="G21" s="27"/>
+      <c r="H21" s="27"/>
+      <c r="I21" s="27"/>
+      <c r="J21" s="30"/>
+      <c r="K21" s="30"/>
+      <c r="L21" s="27"/>
+      <c r="M21" s="27"/>
+      <c r="N21" s="27"/>
       <c r="O21" s="18"/>
     </row>
     <row r="22" spans="1:15">
       <c r="A22" s="16"/>
-      <c r="B22" s="30"/>
-      <c r="C22" s="30"/>
-      <c r="D22" s="30"/>
-      <c r="E22" s="30"/>
-      <c r="F22" s="30"/>
-      <c r="G22" s="30"/>
-      <c r="H22" s="30"/>
-      <c r="I22" s="30"/>
-      <c r="J22" s="33"/>
-      <c r="K22" s="33"/>
-      <c r="L22" s="30"/>
-      <c r="M22" s="30"/>
-      <c r="N22" s="49"/>
+      <c r="B22" s="27"/>
+      <c r="C22" s="27"/>
+      <c r="D22" s="27"/>
+      <c r="E22" s="27"/>
+      <c r="F22" s="27"/>
+      <c r="G22" s="27"/>
+      <c r="H22" s="27"/>
+      <c r="I22" s="27"/>
+      <c r="J22" s="30"/>
+      <c r="K22" s="30"/>
+      <c r="L22" s="27"/>
+      <c r="M22" s="27"/>
+      <c r="N22" s="27"/>
       <c r="O22" s="18"/>
     </row>
     <row r="23" spans="1:15">
       <c r="A23" s="16"/>
-      <c r="B23" s="30"/>
-      <c r="C23" s="30"/>
-      <c r="D23" s="30"/>
-      <c r="E23" s="30"/>
-      <c r="F23" s="30"/>
-      <c r="G23" s="30"/>
-      <c r="H23" s="30"/>
-      <c r="I23" s="30"/>
-      <c r="J23" s="33"/>
-      <c r="K23" s="33"/>
-      <c r="L23" s="30"/>
-      <c r="M23" s="30"/>
-      <c r="N23" s="49"/>
+      <c r="B23" s="27"/>
+      <c r="C23" s="27"/>
+      <c r="D23" s="27"/>
+      <c r="E23" s="27"/>
+      <c r="F23" s="27"/>
+      <c r="G23" s="27"/>
+      <c r="H23" s="27"/>
+      <c r="I23" s="27"/>
+      <c r="J23" s="30"/>
+      <c r="K23" s="30"/>
+      <c r="L23" s="27"/>
+      <c r="M23" s="27"/>
+      <c r="N23" s="27"/>
       <c r="O23" s="18"/>
     </row>
     <row r="24" spans="1:15">
       <c r="A24" s="16"/>
-      <c r="B24" s="30"/>
-      <c r="C24" s="30"/>
-      <c r="D24" s="30"/>
-      <c r="E24" s="30"/>
-      <c r="F24" s="30"/>
-      <c r="G24" s="30"/>
-      <c r="H24" s="30"/>
-      <c r="I24" s="30"/>
-      <c r="J24" s="33"/>
-      <c r="K24" s="33"/>
-      <c r="L24" s="30"/>
-      <c r="M24" s="30"/>
-      <c r="N24" s="49"/>
+      <c r="B24" s="27"/>
+      <c r="C24" s="27"/>
+      <c r="D24" s="27"/>
+      <c r="E24" s="27"/>
+      <c r="F24" s="27"/>
+      <c r="G24" s="27"/>
+      <c r="H24" s="27"/>
+      <c r="I24" s="27"/>
+      <c r="J24" s="30"/>
+      <c r="K24" s="30"/>
+      <c r="L24" s="27"/>
+      <c r="M24" s="27"/>
+      <c r="N24" s="27"/>
       <c r="O24" s="18"/>
     </row>
     <row r="25" spans="1:15">
       <c r="A25" s="16"/>
-      <c r="B25" s="30"/>
-      <c r="C25" s="30"/>
-      <c r="D25" s="30"/>
-      <c r="E25" s="30"/>
-      <c r="F25" s="30"/>
-      <c r="G25" s="30"/>
-      <c r="H25" s="30"/>
-      <c r="I25" s="30"/>
-      <c r="J25" s="33"/>
-      <c r="K25" s="33"/>
-      <c r="L25" s="30"/>
-      <c r="M25" s="30"/>
-      <c r="N25" s="49"/>
+      <c r="B25" s="27"/>
+      <c r="C25" s="27"/>
+      <c r="D25" s="27"/>
+      <c r="E25" s="27"/>
+      <c r="F25" s="27"/>
+      <c r="G25" s="27"/>
+      <c r="H25" s="27"/>
+      <c r="I25" s="27"/>
+      <c r="J25" s="30"/>
+      <c r="K25" s="30"/>
+      <c r="L25" s="27"/>
+      <c r="M25" s="27"/>
+      <c r="N25" s="27"/>
       <c r="O25" s="18"/>
     </row>
     <row r="26" spans="1:15">
       <c r="A26" s="16"/>
-      <c r="B26" s="30"/>
-      <c r="C26" s="30"/>
-      <c r="D26" s="30"/>
-      <c r="E26" s="30"/>
-      <c r="F26" s="30"/>
-      <c r="G26" s="30"/>
-      <c r="H26" s="30"/>
-      <c r="I26" s="30"/>
-      <c r="J26" s="33"/>
-      <c r="K26" s="33"/>
-      <c r="L26" s="30"/>
-      <c r="M26" s="30"/>
-      <c r="N26" s="49"/>
+      <c r="B26" s="27"/>
+      <c r="C26" s="27"/>
+      <c r="D26" s="27"/>
+      <c r="E26" s="27"/>
+      <c r="F26" s="27"/>
+      <c r="G26" s="27"/>
+      <c r="H26" s="27"/>
+      <c r="I26" s="27"/>
+      <c r="J26" s="30"/>
+      <c r="K26" s="30"/>
+      <c r="L26" s="27"/>
+      <c r="M26" s="27"/>
+      <c r="N26" s="27"/>
       <c r="O26" s="18"/>
     </row>
     <row r="27" spans="1:15">
       <c r="A27" s="16"/>
-      <c r="B27" s="30"/>
-      <c r="C27" s="30"/>
-      <c r="D27" s="30"/>
-      <c r="E27" s="30"/>
-      <c r="F27" s="30"/>
-      <c r="G27" s="30"/>
-      <c r="H27" s="30"/>
-      <c r="I27" s="30"/>
-      <c r="J27" s="33"/>
-      <c r="K27" s="33"/>
-      <c r="L27" s="30"/>
-      <c r="M27" s="30"/>
-      <c r="N27" s="49"/>
+      <c r="B27" s="27"/>
+      <c r="C27" s="27"/>
+      <c r="D27" s="27"/>
+      <c r="E27" s="27"/>
+      <c r="F27" s="27"/>
+      <c r="G27" s="27"/>
+      <c r="H27" s="27"/>
+      <c r="I27" s="27"/>
+      <c r="J27" s="30"/>
+      <c r="K27" s="30"/>
+      <c r="L27" s="27"/>
+      <c r="M27" s="27"/>
+      <c r="N27" s="27"/>
       <c r="O27" s="18"/>
     </row>
     <row r="28" spans="1:15">
       <c r="A28" s="16"/>
-      <c r="B28" s="30"/>
-      <c r="C28" s="30"/>
-      <c r="D28" s="30"/>
-      <c r="E28" s="30"/>
-      <c r="F28" s="30"/>
-      <c r="G28" s="30"/>
-      <c r="H28" s="30"/>
-      <c r="I28" s="30"/>
-      <c r="J28" s="33"/>
-      <c r="K28" s="33"/>
-      <c r="L28" s="30"/>
-      <c r="M28" s="30"/>
-      <c r="N28" s="49"/>
+      <c r="B28" s="27"/>
+      <c r="C28" s="27"/>
+      <c r="D28" s="27"/>
+      <c r="E28" s="27"/>
+      <c r="F28" s="27"/>
+      <c r="G28" s="27"/>
+      <c r="H28" s="27"/>
+      <c r="I28" s="27"/>
+      <c r="J28" s="30"/>
+      <c r="K28" s="30"/>
+      <c r="L28" s="27"/>
+      <c r="M28" s="27"/>
+      <c r="N28" s="27"/>
       <c r="O28" s="18"/>
     </row>
     <row r="29" spans="1:15">
       <c r="A29" s="16"/>
-      <c r="B29" s="30"/>
-      <c r="C29" s="30"/>
-      <c r="D29" s="30"/>
-      <c r="E29" s="30"/>
-      <c r="F29" s="30"/>
-      <c r="G29" s="30"/>
-      <c r="H29" s="30"/>
-      <c r="I29" s="30"/>
-      <c r="J29" s="33"/>
-      <c r="K29" s="33"/>
-      <c r="L29" s="30"/>
-      <c r="M29" s="30"/>
-      <c r="N29" s="49"/>
+      <c r="B29" s="27"/>
+      <c r="C29" s="27"/>
+      <c r="D29" s="27"/>
+      <c r="E29" s="27"/>
+      <c r="F29" s="27"/>
+      <c r="G29" s="27"/>
+      <c r="H29" s="27"/>
+      <c r="I29" s="27"/>
+      <c r="J29" s="30"/>
+      <c r="K29" s="30"/>
+      <c r="L29" s="27"/>
+      <c r="M29" s="27"/>
+      <c r="N29" s="27"/>
       <c r="O29" s="18"/>
     </row>
     <row r="30" spans="1:15">
       <c r="A30" s="16"/>
-      <c r="B30" s="30"/>
-      <c r="C30" s="30"/>
-      <c r="D30" s="30"/>
-      <c r="E30" s="30"/>
-      <c r="F30" s="30"/>
-      <c r="G30" s="30"/>
-      <c r="H30" s="30"/>
-      <c r="I30" s="30"/>
-      <c r="J30" s="33"/>
-      <c r="K30" s="33"/>
-      <c r="L30" s="30"/>
-      <c r="M30" s="30"/>
-      <c r="N30" s="49"/>
+      <c r="B30" s="27"/>
+      <c r="C30" s="27"/>
+      <c r="D30" s="27"/>
+      <c r="E30" s="27"/>
+      <c r="F30" s="27"/>
+      <c r="G30" s="27"/>
+      <c r="H30" s="27"/>
+      <c r="I30" s="27"/>
+      <c r="J30" s="30"/>
+      <c r="K30" s="30"/>
+      <c r="L30" s="27"/>
+      <c r="M30" s="27"/>
+      <c r="N30" s="27"/>
       <c r="O30" s="18"/>
     </row>
     <row r="31" spans="1:15">
       <c r="A31" s="16"/>
-      <c r="B31" s="30"/>
-      <c r="C31" s="30"/>
-      <c r="D31" s="30"/>
-      <c r="E31" s="30"/>
-      <c r="F31" s="30"/>
-      <c r="G31" s="30"/>
-      <c r="H31" s="30"/>
-      <c r="I31" s="30"/>
-      <c r="J31" s="33"/>
-      <c r="K31" s="33"/>
-      <c r="L31" s="30"/>
-      <c r="M31" s="30"/>
-      <c r="N31" s="49"/>
+      <c r="B31" s="27"/>
+      <c r="C31" s="27"/>
+      <c r="D31" s="27"/>
+      <c r="E31" s="27"/>
+      <c r="F31" s="27"/>
+      <c r="G31" s="27"/>
+      <c r="H31" s="27"/>
+      <c r="I31" s="27"/>
+      <c r="J31" s="30"/>
+      <c r="K31" s="30"/>
+      <c r="L31" s="27"/>
+      <c r="M31" s="27"/>
+      <c r="N31" s="27"/>
       <c r="O31" s="18"/>
     </row>
     <row r="32" spans="1:15">
       <c r="A32" s="16"/>
-      <c r="B32" s="30"/>
-      <c r="C32" s="30"/>
-      <c r="D32" s="30"/>
-      <c r="E32" s="30"/>
-      <c r="F32" s="30"/>
-      <c r="G32" s="30"/>
-      <c r="H32" s="30"/>
-      <c r="I32" s="30"/>
-      <c r="J32" s="33"/>
-      <c r="K32" s="33"/>
-      <c r="L32" s="30"/>
-      <c r="M32" s="30"/>
-      <c r="N32" s="49"/>
+      <c r="B32" s="27"/>
+      <c r="C32" s="27"/>
+      <c r="D32" s="27"/>
+      <c r="E32" s="27"/>
+      <c r="F32" s="27"/>
+      <c r="G32" s="27"/>
+      <c r="H32" s="27"/>
+      <c r="I32" s="27"/>
+      <c r="J32" s="30"/>
+      <c r="K32" s="30"/>
+      <c r="L32" s="27"/>
+      <c r="M32" s="27"/>
+      <c r="N32" s="27"/>
       <c r="O32" s="18"/>
     </row>
     <row r="33" spans="1:15">
       <c r="A33" s="16"/>
-      <c r="B33" s="30"/>
-      <c r="C33" s="30"/>
-      <c r="D33" s="30"/>
-      <c r="E33" s="30"/>
-      <c r="F33" s="30"/>
-      <c r="G33" s="30"/>
-      <c r="H33" s="30"/>
-      <c r="I33" s="30"/>
-      <c r="J33" s="33"/>
-      <c r="K33" s="33"/>
-      <c r="L33" s="30"/>
-      <c r="M33" s="30"/>
-      <c r="N33" s="49"/>
+      <c r="B33" s="27"/>
+      <c r="C33" s="27"/>
+      <c r="D33" s="27"/>
+      <c r="E33" s="27"/>
+      <c r="F33" s="27"/>
+      <c r="G33" s="27"/>
+      <c r="H33" s="27"/>
+      <c r="I33" s="27"/>
+      <c r="J33" s="30"/>
+      <c r="K33" s="30"/>
+      <c r="L33" s="27"/>
+      <c r="M33" s="27"/>
+      <c r="N33" s="27"/>
       <c r="O33" s="18"/>
     </row>
     <row r="34" spans="1:15">
       <c r="A34" s="16"/>
-      <c r="B34" s="30"/>
-      <c r="C34" s="30"/>
-      <c r="D34" s="30"/>
-      <c r="E34" s="30"/>
-      <c r="F34" s="30"/>
-      <c r="G34" s="30"/>
-      <c r="H34" s="30"/>
-      <c r="I34" s="30"/>
-      <c r="J34" s="33"/>
-      <c r="K34" s="33"/>
-      <c r="L34" s="30"/>
-      <c r="M34" s="30"/>
-      <c r="N34" s="49"/>
+      <c r="B34" s="27"/>
+      <c r="C34" s="27"/>
+      <c r="D34" s="27"/>
+      <c r="E34" s="27"/>
+      <c r="F34" s="27"/>
+      <c r="G34" s="27"/>
+      <c r="H34" s="27"/>
+      <c r="I34" s="27"/>
+      <c r="J34" s="30"/>
+      <c r="K34" s="30"/>
+      <c r="L34" s="27"/>
+      <c r="M34" s="27"/>
+      <c r="N34" s="27"/>
       <c r="O34" s="18"/>
     </row>
     <row r="35" spans="1:15">
       <c r="A35" s="16"/>
-      <c r="B35" s="30"/>
-      <c r="C35" s="30"/>
-      <c r="D35" s="30"/>
-      <c r="E35" s="30"/>
-      <c r="F35" s="30"/>
-      <c r="G35" s="30"/>
-      <c r="H35" s="30"/>
-      <c r="I35" s="30"/>
-      <c r="J35" s="33"/>
-      <c r="K35" s="33"/>
-      <c r="L35" s="30"/>
-      <c r="M35" s="30"/>
-      <c r="N35" s="49"/>
+      <c r="B35" s="27"/>
+      <c r="C35" s="27"/>
+      <c r="D35" s="27"/>
+      <c r="E35" s="27"/>
+      <c r="F35" s="27"/>
+      <c r="G35" s="27"/>
+      <c r="H35" s="27"/>
+      <c r="I35" s="27"/>
+      <c r="J35" s="30"/>
+      <c r="K35" s="30"/>
+      <c r="L35" s="27"/>
+      <c r="M35" s="27"/>
+      <c r="N35" s="27"/>
       <c r="O35" s="18"/>
     </row>
     <row r="36" spans="1:15">
       <c r="A36" s="16"/>
-      <c r="B36" s="30"/>
-      <c r="C36" s="30"/>
-      <c r="D36" s="30"/>
-      <c r="E36" s="30"/>
-      <c r="F36" s="30"/>
-      <c r="G36" s="30"/>
-      <c r="H36" s="30"/>
-      <c r="I36" s="30"/>
-      <c r="J36" s="33"/>
-      <c r="K36" s="33"/>
-      <c r="L36" s="30"/>
-      <c r="M36" s="30"/>
-      <c r="N36" s="49"/>
+      <c r="B36" s="27"/>
+      <c r="C36" s="27"/>
+      <c r="D36" s="27"/>
+      <c r="E36" s="27"/>
+      <c r="F36" s="27"/>
+      <c r="G36" s="27"/>
+      <c r="H36" s="27"/>
+      <c r="I36" s="27"/>
+      <c r="J36" s="30"/>
+      <c r="K36" s="30"/>
+      <c r="L36" s="27"/>
+      <c r="M36" s="27"/>
+      <c r="N36" s="27"/>
       <c r="O36" s="18"/>
     </row>
     <row r="37" spans="1:15">
       <c r="A37" s="16"/>
-      <c r="B37" s="30"/>
-      <c r="C37" s="30"/>
-      <c r="D37" s="30"/>
-      <c r="E37" s="30"/>
-      <c r="F37" s="30"/>
-      <c r="G37" s="30"/>
-      <c r="H37" s="30"/>
-      <c r="I37" s="30"/>
-      <c r="J37" s="33"/>
-      <c r="K37" s="33"/>
-      <c r="L37" s="30"/>
-      <c r="M37" s="30"/>
-      <c r="N37" s="49"/>
+      <c r="B37" s="27"/>
+      <c r="C37" s="27"/>
+      <c r="D37" s="27"/>
+      <c r="E37" s="27"/>
+      <c r="F37" s="27"/>
+      <c r="G37" s="27"/>
+      <c r="H37" s="27"/>
+      <c r="I37" s="27"/>
+      <c r="J37" s="30"/>
+      <c r="K37" s="30"/>
+      <c r="L37" s="27"/>
+      <c r="M37" s="27"/>
+      <c r="N37" s="27"/>
       <c r="O37" s="18"/>
     </row>
     <row r="38" spans="1:15">
       <c r="A38" s="16"/>
-      <c r="B38" s="30"/>
-      <c r="C38" s="30"/>
-      <c r="D38" s="30"/>
-      <c r="E38" s="30"/>
-      <c r="F38" s="30"/>
-      <c r="G38" s="30"/>
-      <c r="H38" s="30"/>
-      <c r="I38" s="30"/>
-      <c r="J38" s="33"/>
-      <c r="K38" s="33"/>
-      <c r="L38" s="30"/>
-      <c r="M38" s="30"/>
-      <c r="N38" s="49"/>
+      <c r="B38" s="27"/>
+      <c r="C38" s="27"/>
+      <c r="D38" s="27"/>
+      <c r="E38" s="27"/>
+      <c r="F38" s="27"/>
+      <c r="G38" s="27"/>
+      <c r="H38" s="27"/>
+      <c r="I38" s="27"/>
+      <c r="J38" s="30"/>
+      <c r="K38" s="30"/>
+      <c r="L38" s="27"/>
+      <c r="M38" s="27"/>
+      <c r="N38" s="27"/>
       <c r="O38" s="18"/>
     </row>
     <row r="39" spans="1:15">
       <c r="A39" s="16"/>
-      <c r="B39" s="30"/>
-      <c r="C39" s="30"/>
-      <c r="D39" s="30"/>
-      <c r="E39" s="30"/>
-      <c r="F39" s="30"/>
-      <c r="G39" s="30"/>
-      <c r="H39" s="30"/>
-      <c r="I39" s="30"/>
-      <c r="J39" s="33"/>
-      <c r="K39" s="33"/>
-      <c r="L39" s="30"/>
-      <c r="M39" s="30"/>
-      <c r="N39" s="49"/>
+      <c r="B39" s="27"/>
+      <c r="C39" s="27"/>
+      <c r="D39" s="27"/>
+      <c r="E39" s="27"/>
+      <c r="F39" s="27"/>
+      <c r="G39" s="27"/>
+      <c r="H39" s="27"/>
+      <c r="I39" s="27"/>
+      <c r="J39" s="30"/>
+      <c r="K39" s="30"/>
+      <c r="L39" s="27"/>
+      <c r="M39" s="27"/>
+      <c r="N39" s="27"/>
       <c r="O39" s="18"/>
     </row>
     <row r="40" spans="1:15">
       <c r="A40" s="16"/>
-      <c r="B40" s="30"/>
-      <c r="C40" s="30"/>
-      <c r="D40" s="30"/>
-      <c r="E40" s="30"/>
-      <c r="F40" s="30"/>
-      <c r="G40" s="30"/>
-      <c r="H40" s="30"/>
-      <c r="I40" s="30"/>
-      <c r="J40" s="33"/>
-      <c r="K40" s="33"/>
-      <c r="L40" s="30"/>
-      <c r="M40" s="30"/>
-      <c r="N40" s="49"/>
+      <c r="B40" s="27"/>
+      <c r="C40" s="27"/>
+      <c r="D40" s="27"/>
+      <c r="E40" s="27"/>
+      <c r="F40" s="27"/>
+      <c r="G40" s="27"/>
+      <c r="H40" s="27"/>
+      <c r="I40" s="27"/>
+      <c r="J40" s="30"/>
+      <c r="K40" s="30"/>
+      <c r="L40" s="27"/>
+      <c r="M40" s="27"/>
+      <c r="N40" s="27"/>
       <c r="O40" s="18"/>
     </row>
     <row r="41" spans="1:15">
       <c r="A41" s="16"/>
-      <c r="B41" s="30"/>
-      <c r="C41" s="30"/>
-      <c r="D41" s="30"/>
-      <c r="E41" s="30"/>
-      <c r="F41" s="30"/>
-      <c r="G41" s="30"/>
-      <c r="H41" s="30"/>
-      <c r="I41" s="30"/>
-      <c r="J41" s="33"/>
-      <c r="K41" s="33"/>
-      <c r="L41" s="30"/>
-      <c r="M41" s="30"/>
-      <c r="N41" s="49"/>
+      <c r="B41" s="27"/>
+      <c r="C41" s="27"/>
+      <c r="D41" s="27"/>
+      <c r="E41" s="27"/>
+      <c r="F41" s="27"/>
+      <c r="G41" s="27"/>
+      <c r="H41" s="27"/>
+      <c r="I41" s="27"/>
+      <c r="J41" s="30"/>
+      <c r="K41" s="30"/>
+      <c r="L41" s="27"/>
+      <c r="M41" s="27"/>
+      <c r="N41" s="27"/>
       <c r="O41" s="18"/>
     </row>
     <row r="42" spans="1:15">
       <c r="A42" s="16"/>
-      <c r="B42" s="30"/>
-      <c r="C42" s="30"/>
-      <c r="D42" s="30"/>
-      <c r="E42" s="30"/>
-      <c r="F42" s="30"/>
-      <c r="G42" s="30"/>
-      <c r="H42" s="30"/>
-      <c r="I42" s="30"/>
-      <c r="J42" s="33"/>
-      <c r="K42" s="33"/>
-      <c r="L42" s="30"/>
-      <c r="M42" s="30"/>
-      <c r="N42" s="49"/>
+      <c r="B42" s="27"/>
+      <c r="C42" s="27"/>
+      <c r="D42" s="27"/>
+      <c r="E42" s="27"/>
+      <c r="F42" s="27"/>
+      <c r="G42" s="27"/>
+      <c r="H42" s="27"/>
+      <c r="I42" s="27"/>
+      <c r="J42" s="30"/>
+      <c r="K42" s="30"/>
+      <c r="L42" s="27"/>
+      <c r="M42" s="27"/>
+      <c r="N42" s="27"/>
       <c r="O42" s="18"/>
     </row>
     <row r="43" spans="1:15">
       <c r="A43" s="16"/>
-      <c r="B43" s="30"/>
-      <c r="C43" s="30"/>
-      <c r="D43" s="30"/>
-      <c r="E43" s="30"/>
-      <c r="F43" s="30"/>
-      <c r="G43" s="30"/>
-      <c r="H43" s="30"/>
-      <c r="I43" s="30"/>
-      <c r="J43" s="33"/>
-      <c r="K43" s="33"/>
-      <c r="L43" s="30"/>
-      <c r="M43" s="30"/>
-      <c r="N43" s="49"/>
+      <c r="B43" s="27"/>
+      <c r="C43" s="27"/>
+      <c r="D43" s="27"/>
+      <c r="E43" s="27"/>
+      <c r="F43" s="27"/>
+      <c r="G43" s="27"/>
+      <c r="H43" s="27"/>
+      <c r="I43" s="27"/>
+      <c r="J43" s="30"/>
+      <c r="K43" s="30"/>
+      <c r="L43" s="27"/>
+      <c r="M43" s="27"/>
+      <c r="N43" s="27"/>
       <c r="O43" s="18"/>
     </row>
     <row r="44" spans="1:15">
       <c r="A44" s="16"/>
-      <c r="B44" s="30"/>
-      <c r="C44" s="30"/>
-      <c r="D44" s="30"/>
-      <c r="E44" s="30"/>
-      <c r="F44" s="30"/>
-      <c r="G44" s="30"/>
-      <c r="H44" s="30"/>
-      <c r="I44" s="30"/>
-      <c r="J44" s="33"/>
-      <c r="K44" s="33"/>
-      <c r="L44" s="30"/>
-      <c r="M44" s="30"/>
-      <c r="N44" s="49"/>
+      <c r="B44" s="27"/>
+      <c r="C44" s="27"/>
+      <c r="D44" s="27"/>
+      <c r="E44" s="27"/>
+      <c r="F44" s="27"/>
+      <c r="G44" s="27"/>
+      <c r="H44" s="27"/>
+      <c r="I44" s="27"/>
+      <c r="J44" s="30"/>
+      <c r="K44" s="30"/>
+      <c r="L44" s="27"/>
+      <c r="M44" s="27"/>
+      <c r="N44" s="27"/>
       <c r="O44" s="18"/>
     </row>
     <row r="45" spans="1:15">
       <c r="A45" s="16"/>
-      <c r="B45" s="30"/>
-      <c r="C45" s="30"/>
-      <c r="D45" s="30"/>
-      <c r="E45" s="30"/>
-      <c r="F45" s="30"/>
-      <c r="G45" s="30"/>
-      <c r="H45" s="30"/>
-      <c r="I45" s="30"/>
-      <c r="J45" s="33"/>
-      <c r="K45" s="33"/>
-      <c r="L45" s="30"/>
-      <c r="M45" s="30"/>
-      <c r="N45" s="49"/>
+      <c r="B45" s="27"/>
+      <c r="C45" s="27"/>
+      <c r="D45" s="27"/>
+      <c r="E45" s="27"/>
+      <c r="F45" s="27"/>
+      <c r="G45" s="27"/>
+      <c r="H45" s="27"/>
+      <c r="I45" s="27"/>
+      <c r="J45" s="30"/>
+      <c r="K45" s="30"/>
+      <c r="L45" s="27"/>
+      <c r="M45" s="27"/>
+      <c r="N45" s="27"/>
       <c r="O45" s="18"/>
     </row>
     <row r="46" spans="1:15">
       <c r="A46" s="16"/>
-      <c r="B46" s="30"/>
-      <c r="C46" s="30"/>
-      <c r="D46" s="30"/>
-      <c r="E46" s="30"/>
-      <c r="F46" s="30"/>
-      <c r="G46" s="30"/>
-      <c r="H46" s="30"/>
-      <c r="I46" s="30"/>
-      <c r="J46" s="33"/>
-      <c r="K46" s="33"/>
-      <c r="L46" s="30"/>
-      <c r="M46" s="30"/>
-      <c r="N46" s="49"/>
+      <c r="B46" s="27"/>
+      <c r="C46" s="27"/>
+      <c r="D46" s="27"/>
+      <c r="E46" s="27"/>
+      <c r="F46" s="27"/>
+      <c r="G46" s="27"/>
+      <c r="H46" s="27"/>
+      <c r="I46" s="27"/>
+      <c r="J46" s="30"/>
+      <c r="K46" s="30"/>
+      <c r="L46" s="27"/>
+      <c r="M46" s="27"/>
+      <c r="N46" s="27"/>
       <c r="O46" s="18"/>
     </row>
     <row r="47" spans="1:15">
       <c r="A47" s="16"/>
-      <c r="B47" s="30"/>
-      <c r="C47" s="30"/>
-      <c r="D47" s="30"/>
-      <c r="E47" s="30"/>
-      <c r="F47" s="30"/>
-      <c r="G47" s="30"/>
-      <c r="H47" s="30"/>
-      <c r="I47" s="30"/>
-      <c r="J47" s="33"/>
-      <c r="K47" s="33"/>
-      <c r="L47" s="30"/>
-      <c r="M47" s="30"/>
-      <c r="N47" s="49"/>
+      <c r="B47" s="27"/>
+      <c r="C47" s="27"/>
+      <c r="D47" s="27"/>
+      <c r="E47" s="27"/>
+      <c r="F47" s="27"/>
+      <c r="G47" s="27"/>
+      <c r="H47" s="27"/>
+      <c r="I47" s="27"/>
+      <c r="J47" s="30"/>
+      <c r="K47" s="30"/>
+      <c r="L47" s="27"/>
+      <c r="M47" s="27"/>
+      <c r="N47" s="27"/>
       <c r="O47" s="18"/>
     </row>
     <row r="48" spans="1:15">
       <c r="A48" s="16"/>
-      <c r="B48" s="30"/>
-      <c r="C48" s="30"/>
-      <c r="D48" s="30"/>
-      <c r="E48" s="30"/>
-      <c r="F48" s="30"/>
-      <c r="G48" s="30"/>
-      <c r="H48" s="30"/>
-      <c r="I48" s="30"/>
-      <c r="J48" s="33"/>
-      <c r="K48" s="33"/>
-      <c r="L48" s="30"/>
-      <c r="M48" s="30"/>
-      <c r="N48" s="49"/>
+      <c r="B48" s="27"/>
+      <c r="C48" s="27"/>
+      <c r="D48" s="27"/>
+      <c r="E48" s="27"/>
+      <c r="F48" s="27"/>
+      <c r="G48" s="27"/>
+      <c r="H48" s="27"/>
+      <c r="I48" s="27"/>
+      <c r="J48" s="30"/>
+      <c r="K48" s="30"/>
+      <c r="L48" s="27"/>
+      <c r="M48" s="27"/>
+      <c r="N48" s="27"/>
       <c r="O48" s="18"/>
     </row>
     <row r="49" spans="1:15">
       <c r="A49" s="16"/>
-      <c r="B49" s="30"/>
-      <c r="C49" s="30"/>
-      <c r="D49" s="30"/>
-      <c r="E49" s="30"/>
-      <c r="F49" s="30"/>
-      <c r="G49" s="30"/>
-      <c r="H49" s="30"/>
-      <c r="I49" s="30"/>
-      <c r="J49" s="33"/>
-      <c r="K49" s="33"/>
-      <c r="L49" s="30"/>
-      <c r="M49" s="30"/>
-      <c r="N49" s="49"/>
+      <c r="B49" s="27"/>
+      <c r="C49" s="27"/>
+      <c r="D49" s="27"/>
+      <c r="E49" s="27"/>
+      <c r="F49" s="27"/>
+      <c r="G49" s="27"/>
+      <c r="H49" s="27"/>
+      <c r="I49" s="27"/>
+      <c r="J49" s="30"/>
+      <c r="K49" s="30"/>
+      <c r="L49" s="27"/>
+      <c r="M49" s="27"/>
+      <c r="N49" s="27"/>
       <c r="O49" s="18"/>
     </row>
     <row r="50" spans="1:15">
       <c r="A50" s="16"/>
-      <c r="B50" s="30"/>
-      <c r="C50" s="30"/>
-      <c r="D50" s="30"/>
-      <c r="E50" s="30"/>
-      <c r="F50" s="30"/>
-      <c r="G50" s="30"/>
-      <c r="H50" s="30"/>
-      <c r="I50" s="30"/>
-      <c r="J50" s="33"/>
-      <c r="K50" s="33"/>
-      <c r="L50" s="30"/>
-      <c r="M50" s="30"/>
-      <c r="N50" s="49"/>
+      <c r="B50" s="27"/>
+      <c r="C50" s="27"/>
+      <c r="D50" s="27"/>
+      <c r="E50" s="27"/>
+      <c r="F50" s="27"/>
+      <c r="G50" s="27"/>
+      <c r="H50" s="27"/>
+      <c r="I50" s="27"/>
+      <c r="J50" s="30"/>
+      <c r="K50" s="30"/>
+      <c r="L50" s="27"/>
+      <c r="M50" s="27"/>
+      <c r="N50" s="27"/>
       <c r="O50" s="18"/>
     </row>
     <row r="51" spans="1:15">
       <c r="A51" s="16"/>
-      <c r="B51" s="30"/>
-      <c r="C51" s="30"/>
-      <c r="D51" s="30"/>
-      <c r="E51" s="30"/>
-      <c r="F51" s="30"/>
-      <c r="G51" s="30"/>
-      <c r="H51" s="30"/>
-      <c r="I51" s="30"/>
-      <c r="J51" s="33"/>
-      <c r="K51" s="33"/>
-      <c r="L51" s="30"/>
-      <c r="M51" s="30"/>
-      <c r="N51" s="49"/>
+      <c r="B51" s="27"/>
+      <c r="C51" s="27"/>
+      <c r="D51" s="27"/>
+      <c r="E51" s="27"/>
+      <c r="F51" s="27"/>
+      <c r="G51" s="27"/>
+      <c r="H51" s="27"/>
+      <c r="I51" s="27"/>
+      <c r="J51" s="30"/>
+      <c r="K51" s="30"/>
+      <c r="L51" s="27"/>
+      <c r="M51" s="27"/>
+      <c r="N51" s="27"/>
       <c r="O51" s="18"/>
     </row>
     <row r="52" spans="1:15">
       <c r="A52" s="16"/>
-      <c r="B52" s="30"/>
-      <c r="C52" s="30"/>
-      <c r="D52" s="30"/>
-      <c r="E52" s="30"/>
-      <c r="F52" s="30"/>
-      <c r="G52" s="30"/>
-      <c r="H52" s="30"/>
-      <c r="I52" s="30"/>
-      <c r="J52" s="33"/>
-      <c r="K52" s="33"/>
-      <c r="L52" s="30"/>
-      <c r="M52" s="30"/>
-      <c r="N52" s="49"/>
+      <c r="B52" s="27"/>
+      <c r="C52" s="27"/>
+      <c r="D52" s="27"/>
+      <c r="E52" s="27"/>
+      <c r="F52" s="27"/>
+      <c r="G52" s="27"/>
+      <c r="H52" s="27"/>
+      <c r="I52" s="27"/>
+      <c r="J52" s="30"/>
+      <c r="K52" s="30"/>
+      <c r="L52" s="27"/>
+      <c r="M52" s="27"/>
+      <c r="N52" s="27"/>
       <c r="O52" s="18"/>
     </row>
     <row r="53" spans="1:15">
       <c r="A53" s="16"/>
-      <c r="B53" s="30"/>
-      <c r="C53" s="30"/>
-      <c r="D53" s="30"/>
-      <c r="E53" s="30"/>
-      <c r="F53" s="30"/>
-      <c r="G53" s="30"/>
-      <c r="H53" s="30"/>
-      <c r="I53" s="30"/>
-      <c r="J53" s="33"/>
-      <c r="K53" s="33"/>
-      <c r="L53" s="30"/>
-      <c r="M53" s="30"/>
-      <c r="N53" s="49"/>
+      <c r="B53" s="27"/>
+      <c r="C53" s="27"/>
+      <c r="D53" s="27"/>
+      <c r="E53" s="27"/>
+      <c r="F53" s="27"/>
+      <c r="G53" s="27"/>
+      <c r="H53" s="27"/>
+      <c r="I53" s="27"/>
+      <c r="J53" s="30"/>
+      <c r="K53" s="30"/>
+      <c r="L53" s="27"/>
+      <c r="M53" s="27"/>
+      <c r="N53" s="27"/>
       <c r="O53" s="18"/>
     </row>
     <row r="54" spans="1:15">
       <c r="A54" s="16"/>
-      <c r="B54" s="30"/>
-      <c r="C54" s="30"/>
-      <c r="D54" s="30"/>
-      <c r="E54" s="30"/>
-      <c r="F54" s="30"/>
-      <c r="G54" s="30"/>
-      <c r="H54" s="30"/>
-      <c r="I54" s="30"/>
-      <c r="J54" s="33"/>
-      <c r="K54" s="33"/>
-      <c r="L54" s="30"/>
-      <c r="M54" s="30"/>
-      <c r="N54" s="49"/>
+      <c r="B54" s="27"/>
+      <c r="C54" s="27"/>
+      <c r="D54" s="27"/>
+      <c r="E54" s="27"/>
+      <c r="F54" s="27"/>
+      <c r="G54" s="27"/>
+      <c r="H54" s="27"/>
+      <c r="I54" s="27"/>
+      <c r="J54" s="30"/>
+      <c r="K54" s="30"/>
+      <c r="L54" s="27"/>
+      <c r="M54" s="27"/>
+      <c r="N54" s="27"/>
       <c r="O54" s="18"/>
     </row>
     <row r="55" spans="1:15">
       <c r="A55" s="16"/>
-      <c r="B55" s="30"/>
-      <c r="C55" s="30"/>
-      <c r="D55" s="30"/>
-      <c r="E55" s="30"/>
-      <c r="F55" s="30"/>
-      <c r="G55" s="30"/>
-      <c r="H55" s="30"/>
-      <c r="I55" s="30"/>
-      <c r="J55" s="33"/>
-      <c r="K55" s="33"/>
-      <c r="L55" s="30"/>
-      <c r="M55" s="30"/>
-      <c r="N55" s="49"/>
+      <c r="B55" s="27"/>
+      <c r="C55" s="27"/>
+      <c r="D55" s="27"/>
+      <c r="E55" s="27"/>
+      <c r="F55" s="27"/>
+      <c r="G55" s="27"/>
+      <c r="H55" s="27"/>
+      <c r="I55" s="27"/>
+      <c r="J55" s="30"/>
+      <c r="K55" s="30"/>
+      <c r="L55" s="27"/>
+      <c r="M55" s="27"/>
+      <c r="N55" s="27"/>
       <c r="O55" s="18"/>
     </row>
     <row r="56" spans="1:15">
       <c r="A56" s="16"/>
-      <c r="B56" s="30"/>
-      <c r="C56" s="30"/>
-      <c r="D56" s="30"/>
-      <c r="E56" s="30"/>
-      <c r="F56" s="30"/>
-      <c r="G56" s="30"/>
-      <c r="H56" s="30"/>
-      <c r="I56" s="30"/>
-      <c r="J56" s="33"/>
-      <c r="K56" s="33"/>
-      <c r="L56" s="30"/>
-      <c r="M56" s="30"/>
-      <c r="N56" s="49"/>
+      <c r="B56" s="27"/>
+      <c r="C56" s="27"/>
+      <c r="D56" s="27"/>
+      <c r="E56" s="27"/>
+      <c r="F56" s="27"/>
+      <c r="G56" s="27"/>
+      <c r="H56" s="27"/>
+      <c r="I56" s="27"/>
+      <c r="J56" s="30"/>
+      <c r="K56" s="30"/>
+      <c r="L56" s="27"/>
+      <c r="M56" s="27"/>
+      <c r="N56" s="27"/>
       <c r="O56" s="18"/>
     </row>
     <row r="57" spans="1:15">
       <c r="A57" s="16"/>
-      <c r="B57" s="30"/>
-      <c r="C57" s="30"/>
-      <c r="D57" s="30"/>
-      <c r="E57" s="30"/>
-      <c r="F57" s="30"/>
-      <c r="G57" s="30"/>
-      <c r="H57" s="30"/>
-      <c r="I57" s="30"/>
-      <c r="J57" s="33"/>
-      <c r="K57" s="33"/>
-      <c r="L57" s="30"/>
-      <c r="M57" s="30"/>
-      <c r="N57" s="49"/>
+      <c r="B57" s="27"/>
+      <c r="C57" s="27"/>
+      <c r="D57" s="27"/>
+      <c r="E57" s="27"/>
+      <c r="F57" s="27"/>
+      <c r="G57" s="27"/>
+      <c r="H57" s="27"/>
+      <c r="I57" s="27"/>
+      <c r="J57" s="30"/>
+      <c r="K57" s="30"/>
+      <c r="L57" s="27"/>
+      <c r="M57" s="27"/>
+      <c r="N57" s="27"/>
       <c r="O57" s="18"/>
     </row>
     <row r="58" spans="1:15">
       <c r="A58" s="16"/>
-      <c r="B58" s="30"/>
-      <c r="C58" s="30"/>
-      <c r="D58" s="30"/>
-      <c r="E58" s="30"/>
-      <c r="F58" s="30"/>
-      <c r="G58" s="30"/>
-      <c r="H58" s="30"/>
-      <c r="I58" s="30"/>
-      <c r="J58" s="33"/>
-      <c r="K58" s="33"/>
-      <c r="L58" s="30"/>
-      <c r="M58" s="30"/>
-      <c r="N58" s="49"/>
+      <c r="B58" s="27"/>
+      <c r="C58" s="27"/>
+      <c r="D58" s="27"/>
+      <c r="E58" s="27"/>
+      <c r="F58" s="27"/>
+      <c r="G58" s="27"/>
+      <c r="H58" s="27"/>
+      <c r="I58" s="27"/>
+      <c r="J58" s="30"/>
+      <c r="K58" s="30"/>
+      <c r="L58" s="27"/>
+      <c r="M58" s="27"/>
+      <c r="N58" s="27"/>
       <c r="O58" s="18"/>
     </row>
     <row r="59" spans="1:15">
       <c r="A59" s="16"/>
-      <c r="B59" s="30"/>
-      <c r="C59" s="30"/>
-      <c r="D59" s="30"/>
-      <c r="E59" s="30"/>
-      <c r="F59" s="30"/>
-      <c r="G59" s="30"/>
-      <c r="H59" s="30"/>
-      <c r="I59" s="30"/>
-      <c r="J59" s="33"/>
-      <c r="K59" s="33"/>
-      <c r="L59" s="30"/>
-      <c r="M59" s="30"/>
-      <c r="N59" s="49"/>
+      <c r="B59" s="27"/>
+      <c r="C59" s="27"/>
+      <c r="D59" s="27"/>
+      <c r="E59" s="27"/>
+      <c r="F59" s="27"/>
+      <c r="G59" s="27"/>
+      <c r="H59" s="27"/>
+      <c r="I59" s="27"/>
+      <c r="J59" s="30"/>
+      <c r="K59" s="30"/>
+      <c r="L59" s="27"/>
+      <c r="M59" s="27"/>
+      <c r="N59" s="27"/>
       <c r="O59" s="18"/>
     </row>
     <row r="60" spans="1:15">
       <c r="A60" s="16"/>
-      <c r="B60" s="30"/>
-      <c r="C60" s="30"/>
-      <c r="D60" s="30"/>
-      <c r="E60" s="30"/>
-      <c r="F60" s="30"/>
-      <c r="G60" s="30"/>
-      <c r="H60" s="30"/>
-      <c r="I60" s="30"/>
-      <c r="J60" s="33"/>
-      <c r="K60" s="33"/>
-      <c r="L60" s="30"/>
-      <c r="M60" s="30"/>
-      <c r="N60" s="49"/>
+      <c r="B60" s="27"/>
+      <c r="C60" s="27"/>
+      <c r="D60" s="27"/>
+      <c r="E60" s="27"/>
+      <c r="F60" s="27"/>
+      <c r="G60" s="27"/>
+      <c r="H60" s="27"/>
+      <c r="I60" s="27"/>
+      <c r="J60" s="30"/>
+      <c r="K60" s="30"/>
+      <c r="L60" s="27"/>
+      <c r="M60" s="27"/>
+      <c r="N60" s="27"/>
       <c r="O60" s="18"/>
     </row>
     <row r="61" spans="1:15">
       <c r="A61" s="16"/>
-      <c r="B61" s="30"/>
-      <c r="C61" s="30"/>
-      <c r="D61" s="30"/>
-      <c r="E61" s="30"/>
-      <c r="F61" s="30"/>
-      <c r="G61" s="30"/>
-      <c r="H61" s="30"/>
-      <c r="I61" s="30"/>
-      <c r="J61" s="33"/>
-      <c r="K61" s="33"/>
-      <c r="L61" s="30"/>
-      <c r="M61" s="30"/>
-      <c r="N61" s="49"/>
+      <c r="B61" s="27"/>
+      <c r="C61" s="27"/>
+      <c r="D61" s="27"/>
+      <c r="E61" s="27"/>
+      <c r="F61" s="27"/>
+      <c r="G61" s="27"/>
+      <c r="H61" s="27"/>
+      <c r="I61" s="27"/>
+      <c r="J61" s="30"/>
+      <c r="K61" s="30"/>
+      <c r="L61" s="27"/>
+      <c r="M61" s="27"/>
+      <c r="N61" s="27"/>
       <c r="O61" s="18"/>
     </row>
     <row r="62" spans="1:15">
       <c r="A62" s="16"/>
-      <c r="B62" s="30"/>
-      <c r="C62" s="30"/>
-      <c r="D62" s="30"/>
-      <c r="E62" s="30"/>
-      <c r="F62" s="30"/>
-      <c r="G62" s="30"/>
-      <c r="H62" s="30"/>
-      <c r="I62" s="30"/>
-      <c r="J62" s="33"/>
-      <c r="K62" s="33"/>
-      <c r="L62" s="30"/>
-      <c r="M62" s="30"/>
-      <c r="N62" s="49"/>
+      <c r="B62" s="27"/>
+      <c r="C62" s="27"/>
+      <c r="D62" s="27"/>
+      <c r="E62" s="27"/>
+      <c r="F62" s="27"/>
+      <c r="G62" s="27"/>
+      <c r="H62" s="27"/>
+      <c r="I62" s="27"/>
+      <c r="J62" s="30"/>
+      <c r="K62" s="30"/>
+      <c r="L62" s="27"/>
+      <c r="M62" s="27"/>
+      <c r="N62" s="27"/>
       <c r="O62" s="18"/>
     </row>
     <row r="63" spans="1:15">
       <c r="A63" s="16"/>
-      <c r="B63" s="30"/>
-      <c r="C63" s="30"/>
-      <c r="D63" s="30"/>
-      <c r="E63" s="30"/>
-      <c r="F63" s="30"/>
-      <c r="G63" s="30"/>
-      <c r="H63" s="30"/>
-      <c r="I63" s="30"/>
-      <c r="J63" s="33"/>
-      <c r="K63" s="33"/>
-      <c r="L63" s="30"/>
-      <c r="M63" s="30"/>
-      <c r="N63" s="49"/>
+      <c r="B63" s="27"/>
+      <c r="C63" s="27"/>
+      <c r="D63" s="27"/>
+      <c r="E63" s="27"/>
+      <c r="F63" s="27"/>
+      <c r="G63" s="27"/>
+      <c r="H63" s="27"/>
+      <c r="I63" s="27"/>
+      <c r="J63" s="30"/>
+      <c r="K63" s="30"/>
+      <c r="L63" s="27"/>
+      <c r="M63" s="27"/>
+      <c r="N63" s="27"/>
       <c r="O63" s="18"/>
     </row>
   </sheetData>

--- a/01_組織工作盤查.xlsx
+++ b/01_組織工作盤查.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Development\LeaderMethodology\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19992562-7BB7-4864-B0E9-8C7FECEA3FB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35AB0298-26D9-421C-93BC-0202C73620BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{6274A289-9C1F-4174-8A94-9BA38FCDDB48}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" activeTab="1" xr2:uid="{6274A289-9C1F-4174-8A94-9BA38FCDDB48}"/>
   </bookViews>
   <sheets>
     <sheet name="Guide" sheetId="1" r:id="rId1"/>
@@ -75,7 +75,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="213">
   <si>
     <t>文件名稱/Document</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -409,14 +409,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>E</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>F</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>請說明及提供:製造區域、辦公室、樓層、大樓之網路架構、資訊流及管理方式
 (包含每個區域的Switch、防火牆、設備、機台、管制方式、網速頻寬、權限、連線紀錄)
 有架構圖最好</t>
@@ -459,11 +451,6 @@
   </si>
   <si>
     <t>製造 CIM</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>請確認以下表格，對應 Sheet 內容
-(黃底部要調寫確認結果)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1128,19 +1115,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>機台時間 Clock 設定</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>機台所有 ALCD &amp; ALID &amp; ALTX</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>自動回報機況、燈號、工單、此批作業數量、累積作業數量、進料口狀態、出料口狀態、耗材使用量、UPH、Alarm Count.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>須提供機台所有參數的SVID (操作畫面上有的、感測器量測數值、作業參數數值等)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1205,6 +1184,77 @@
   </si>
   <si>
     <t>是否為串線?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WebServcie</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我司能介入機台機構動作(入料確認、出料確認、讀取確認、退料)及運作流程(判為良品、判為不良品)，若我司無回覆給機台結果，則機台必須等待(最久達到 Timeout)；反之機台有收到我司回覆的結果，則依照結果執行後續對應的動作。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我司能遠端控制機台開始生產、暫停、鎖定(需有特殊權限者才能解除)及燈號.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我司能指定機台 Recipe(檔案、資訊流).</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我司能遠端控制機台呈現指定的訊息及報警聲.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我司能設置機台參數(檔案、工作檔).</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>我司可主動跟機台索取或機台可在指定的時機/事件(機構動作、燈號、操作、警報)匯出或拋出 Summary、Log、工單、Recipe(檔案、參數)、UPH、目前生產數量、IndexTime、機構狀態、機台參數、燈號、AlarmCount 等.
+匯出格式、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei UI"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>資訊、時機，可由我司指定.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我司能設置機台卡控的上下限(速度、範圍、電壓、電流)、卡控時機.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>以上項目廠商必須提供 Servcie 手冊及dll給我方評估自動化能力，若能提供內部測試的 Log 及 SampleCode會更完整.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Other</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>機台時間(Clock)設定及T3/T5/T6/T7 Timeout 設定</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>須提供機台所有參數的SVID (操作畫面上有的、感測器量測數值、作業參數數值等)
+Variable Data Collection</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>能達到上述SECS/GEM 或 WebServcie 功能皆可</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>請確認以下表格，對應 Sheet 內容
+(黃底部要填寫確認結果)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1212,7 +1262,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="17">
+  <fonts count="16">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1266,14 +1316,6 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Microsoft JhengHei UI"/>
-      <family val="2"/>
-      <charset val="136"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="微軟正黑體"/>
       <family val="2"/>
       <charset val="136"/>
     </font>
@@ -1508,13 +1550,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
@@ -1529,16 +1568,16 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
@@ -1547,20 +1586,26 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="14" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="13" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1571,23 +1616,20 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1598,9 +1640,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1608,6 +1647,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4144,13 +4186,13 @@
   <dimension ref="A1:AC14"/>
   <sheetFormatPr defaultColWidth="3.6640625" defaultRowHeight="21"/>
   <cols>
-    <col min="1" max="1" width="7.77734375" style="36" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.77734375" style="35" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="3.5546875" style="22" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.44140625" style="22" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="3.5546875" style="36" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.44140625" style="37" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="3.5546875" style="37" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.21875" style="37" customWidth="1"/>
+    <col min="4" max="4" width="3.5546875" style="35" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.44140625" style="36" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="3.5546875" style="36" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.21875" style="36" customWidth="1"/>
     <col min="8" max="8" width="3.5546875" style="22" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12.44140625" style="22" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="3.5546875" style="22" bestFit="1" customWidth="1"/>
@@ -4161,111 +4203,111 @@
     <col min="15" max="24" width="3.6640625" style="22"/>
     <col min="25" max="25" width="11.6640625" style="22" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="25.109375" style="22" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="3.5546875" style="36" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="12.44140625" style="37" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="3.5546875" style="35" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="12.44140625" style="36" bestFit="1" customWidth="1"/>
     <col min="29" max="16384" width="3.6640625" style="22"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="66.599999999999994" customHeight="1">
-      <c r="A1" s="44" t="s">
-        <v>89</v>
-      </c>
-      <c r="B1" s="48" t="s">
-        <v>151</v>
-      </c>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
-      <c r="G1" s="48"/>
-      <c r="H1" s="48" t="s">
-        <v>150</v>
-      </c>
-      <c r="I1" s="48"/>
-      <c r="J1" s="48"/>
-      <c r="K1" s="48"/>
-      <c r="L1" s="48"/>
-      <c r="M1" s="48"/>
+      <c r="A1" s="45" t="s">
+        <v>86</v>
+      </c>
+      <c r="B1" s="49" t="s">
+        <v>148</v>
+      </c>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49" t="s">
+        <v>147</v>
+      </c>
+      <c r="I1" s="49"/>
+      <c r="J1" s="49"/>
+      <c r="K1" s="49"/>
+      <c r="L1" s="49"/>
+      <c r="M1" s="49"/>
     </row>
     <row r="2" spans="1:29" ht="15.6">
-      <c r="A2" s="44"/>
-      <c r="B2" s="45" t="s">
+      <c r="A2" s="45"/>
+      <c r="B2" s="46" t="s">
+        <v>92</v>
+      </c>
+      <c r="C2" s="46"/>
+      <c r="D2" s="47" t="s">
+        <v>93</v>
+      </c>
+      <c r="E2" s="47"/>
+      <c r="F2" s="48" t="s">
         <v>95</v>
       </c>
-      <c r="C2" s="45"/>
-      <c r="D2" s="46" t="s">
-        <v>96</v>
-      </c>
-      <c r="E2" s="46"/>
-      <c r="F2" s="47" t="s">
-        <v>98</v>
-      </c>
-      <c r="G2" s="47"/>
-      <c r="H2" s="45" t="s">
+      <c r="G2" s="48"/>
+      <c r="H2" s="46" t="s">
+        <v>92</v>
+      </c>
+      <c r="I2" s="46"/>
+      <c r="J2" s="47" t="s">
+        <v>93</v>
+      </c>
+      <c r="K2" s="47"/>
+      <c r="L2" s="48" t="s">
         <v>95</v>
       </c>
-      <c r="I2" s="45"/>
-      <c r="J2" s="46" t="s">
-        <v>96</v>
-      </c>
-      <c r="K2" s="46"/>
-      <c r="L2" s="47" t="s">
-        <v>98</v>
-      </c>
-      <c r="M2" s="47"/>
+      <c r="M2" s="48"/>
       <c r="AA2" s="22"/>
       <c r="AB2" s="22"/>
     </row>
     <row r="3" spans="1:29">
-      <c r="A3" s="39">
+      <c r="A3" s="38">
         <f>COUNT('C.製程動作分析盤點'!A:A)</f>
         <v>4</v>
       </c>
-      <c r="B3" s="39">
+      <c r="B3" s="38">
         <f>COUNTIF('C.製程動作分析盤點'!J:J,"高")</f>
         <v>0</v>
       </c>
-      <c r="C3" s="40">
+      <c r="C3" s="39">
         <f>B3/$A$3</f>
         <v>0</v>
       </c>
-      <c r="D3" s="39">
+      <c r="D3" s="38">
         <f>COUNTIF('C.製程動作分析盤點'!J:J,"中")</f>
         <v>0</v>
       </c>
-      <c r="E3" s="40">
+      <c r="E3" s="39">
         <f>D3/$A$3</f>
         <v>0</v>
       </c>
-      <c r="F3" s="39">
+      <c r="F3" s="38">
         <f>COUNTIF('C.製程動作分析盤點'!J:J,"低")</f>
         <v>4</v>
       </c>
-      <c r="G3" s="40">
+      <c r="G3" s="39">
         <f>F3/$A$3</f>
         <v>1</v>
       </c>
-      <c r="H3" s="39">
+      <c r="H3" s="38">
         <f>COUNTIF('C.製程動作分析盤點'!K:K,"高")</f>
         <v>2</v>
       </c>
-      <c r="I3" s="40">
+      <c r="I3" s="39">
         <f>H3/$A$3</f>
         <v>0.5</v>
       </c>
-      <c r="J3" s="39">
+      <c r="J3" s="38">
         <f>COUNTIF('C.製程動作分析盤點'!K:K,"中")</f>
         <v>0</v>
       </c>
-      <c r="K3" s="40">
+      <c r="K3" s="39">
         <f>J3/$A$3</f>
         <v>0</v>
       </c>
-      <c r="L3" s="39">
+      <c r="L3" s="38">
         <f>COUNTIF('C.製程動作分析盤點'!K:K,"低")</f>
         <v>2</v>
       </c>
-      <c r="M3" s="40">
+      <c r="M3" s="39">
         <f>L3/$A$3</f>
         <v>0.5</v>
       </c>
@@ -4273,40 +4315,40 @@
       <c r="AB3" s="22"/>
     </row>
     <row r="4" spans="1:29">
-      <c r="B4" s="38"/>
-      <c r="C4" s="38"/>
-      <c r="F4" s="36"/>
-      <c r="G4" s="36"/>
+      <c r="B4" s="37"/>
+      <c r="C4" s="37"/>
+      <c r="F4" s="35"/>
+      <c r="G4" s="35"/>
       <c r="AA4" s="22"/>
       <c r="AB4" s="22"/>
     </row>
     <row r="5" spans="1:29">
-      <c r="B5" s="38"/>
-      <c r="C5" s="38"/>
-      <c r="F5" s="36"/>
-      <c r="G5" s="36"/>
+      <c r="B5" s="37"/>
+      <c r="C5" s="37"/>
+      <c r="F5" s="35"/>
+      <c r="G5" s="35"/>
       <c r="AA5" s="22"/>
       <c r="AB5" s="22"/>
     </row>
     <row r="6" spans="1:29">
-      <c r="B6" s="36"/>
-      <c r="C6" s="36"/>
-      <c r="E6" s="36"/>
-      <c r="F6" s="36"/>
-      <c r="G6" s="36"/>
+      <c r="B6" s="35"/>
+      <c r="C6" s="35"/>
+      <c r="E6" s="35"/>
+      <c r="F6" s="35"/>
+      <c r="G6" s="35"/>
       <c r="AA6" s="22"/>
       <c r="AB6" s="22"/>
     </row>
     <row r="7" spans="1:29">
-      <c r="B7" s="36"/>
-      <c r="C7" s="36"/>
-      <c r="E7" s="36"/>
-      <c r="F7" s="36"/>
-      <c r="G7" s="36"/>
-      <c r="Y7" s="36"/>
-      <c r="Z7" s="36"/>
-      <c r="AB7" s="36"/>
-      <c r="AC7" s="36"/>
+      <c r="B7" s="35"/>
+      <c r="C7" s="35"/>
+      <c r="E7" s="35"/>
+      <c r="F7" s="35"/>
+      <c r="G7" s="35"/>
+      <c r="Y7" s="35"/>
+      <c r="Z7" s="35"/>
+      <c r="AB7" s="35"/>
+      <c r="AC7" s="35"/>
     </row>
     <row r="11" spans="1:29">
       <c r="F11" s="22"/>
@@ -4362,10 +4404,10 @@
         <v>18</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C1" s="17" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="D1" s="18" t="s">
         <v>19</v>
@@ -4376,10 +4418,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="50" t="s">
+        <v>153</v>
+      </c>
+      <c r="C2" s="20" t="s">
         <v>156</v>
-      </c>
-      <c r="C2" s="20" t="s">
-        <v>159</v>
       </c>
       <c r="D2" s="18"/>
     </row>
@@ -4389,7 +4431,7 @@
       </c>
       <c r="B3" s="51"/>
       <c r="C3" s="20" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="D3" s="18"/>
     </row>
@@ -4399,7 +4441,7 @@
       </c>
       <c r="B4" s="51"/>
       <c r="C4" s="20" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="D4" s="18"/>
     </row>
@@ -4409,7 +4451,7 @@
       </c>
       <c r="B5" s="51"/>
       <c r="C5" s="20" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="D5" s="18"/>
     </row>
@@ -4417,11 +4459,11 @@
       <c r="A6" s="16">
         <v>5</v>
       </c>
-      <c r="B6" s="53" t="s">
-        <v>163</v>
+      <c r="B6" s="41" t="s">
+        <v>160</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="D6" s="18"/>
     </row>
@@ -4446,10 +4488,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="50" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="C9" s="20" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="D9" s="18"/>
     </row>
@@ -4459,7 +4501,7 @@
       </c>
       <c r="B10" s="51"/>
       <c r="C10" s="20" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="D10" s="18"/>
     </row>
@@ -4469,7 +4511,7 @@
       </c>
       <c r="B11" s="52"/>
       <c r="C11" s="20" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="D11" s="18"/>
     </row>
@@ -4516,13 +4558,13 @@
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="7.33203125" style="21" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.33203125" style="19" customWidth="1"/>
     <col min="3" max="3" width="255.77734375" style="19" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="255.77734375" style="19" customWidth="1"/>
+    <col min="4" max="4" width="27.33203125" style="19" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="7.77734375" style="21" bestFit="1" customWidth="1"/>
     <col min="6" max="16384" width="8.88671875" style="19"/>
   </cols>
@@ -4532,13 +4574,13 @@
         <v>18</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C1" s="17" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D1" s="17" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="E1" s="18" t="s">
         <v>19</v>
@@ -4548,14 +4590,14 @@
       <c r="A2" s="16">
         <v>1</v>
       </c>
-      <c r="B2" s="54" t="s">
-        <v>165</v>
+      <c r="B2" s="53" t="s">
+        <v>162</v>
       </c>
       <c r="C2" s="20" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="D2" s="20" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="E2" s="18"/>
     </row>
@@ -4563,12 +4605,12 @@
       <c r="A3" s="16">
         <v>2</v>
       </c>
-      <c r="B3" s="55"/>
+      <c r="B3" s="54"/>
       <c r="C3" s="20" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="D3" s="20" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="E3" s="18"/>
     </row>
@@ -4576,12 +4618,12 @@
       <c r="A4" s="16">
         <v>3</v>
       </c>
-      <c r="B4" s="55"/>
+      <c r="B4" s="54"/>
       <c r="C4" s="20" t="s">
-        <v>185</v>
+        <v>209</v>
       </c>
       <c r="D4" s="20" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="E4" s="18"/>
     </row>
@@ -4589,12 +4631,12 @@
       <c r="A5" s="16">
         <v>4</v>
       </c>
-      <c r="B5" s="55"/>
+      <c r="B5" s="54"/>
       <c r="C5" s="20" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="D5" s="20" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="E5" s="18"/>
     </row>
@@ -4602,12 +4644,12 @@
       <c r="A6" s="16">
         <v>5</v>
       </c>
-      <c r="B6" s="55"/>
+      <c r="B6" s="54"/>
       <c r="C6" s="20" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="D6" s="20" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="E6" s="18"/>
     </row>
@@ -4615,12 +4657,12 @@
       <c r="A7" s="16">
         <v>6</v>
       </c>
-      <c r="B7" s="55"/>
+      <c r="B7" s="54"/>
       <c r="C7" s="20" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="D7" s="20" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E7" s="18"/>
     </row>
@@ -4628,25 +4670,25 @@
       <c r="A8" s="16">
         <v>7</v>
       </c>
-      <c r="B8" s="55"/>
+      <c r="B8" s="54"/>
       <c r="C8" s="20" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="D8" s="20" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="E8" s="18"/>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" ht="31.2">
       <c r="A9" s="16">
         <v>8</v>
       </c>
-      <c r="B9" s="55"/>
+      <c r="B9" s="54"/>
       <c r="C9" s="20" t="s">
-        <v>188</v>
+        <v>210</v>
       </c>
       <c r="D9" s="20" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="E9" s="18"/>
     </row>
@@ -4654,12 +4696,12 @@
       <c r="A10" s="16">
         <v>9</v>
       </c>
-      <c r="B10" s="55"/>
+      <c r="B10" s="54"/>
       <c r="C10" s="20" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="D10" s="20" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="E10" s="18"/>
     </row>
@@ -4667,12 +4709,12 @@
       <c r="A11" s="16">
         <v>10</v>
       </c>
-      <c r="B11" s="55"/>
+      <c r="B11" s="54"/>
       <c r="C11" s="20" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D11" s="20" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="E11" s="18"/>
     </row>
@@ -4680,12 +4722,12 @@
       <c r="A12" s="16">
         <v>11</v>
       </c>
-      <c r="B12" s="55"/>
+      <c r="B12" s="54"/>
       <c r="C12" s="20" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="D12" s="20" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="E12" s="18"/>
     </row>
@@ -4693,25 +4735,25 @@
       <c r="A13" s="16">
         <v>12</v>
       </c>
-      <c r="B13" s="55"/>
+      <c r="B13" s="54"/>
       <c r="C13" s="20" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="D13" s="17" t="s">
-        <v>178</v>
-      </c>
-      <c r="E13" s="16"/>
+        <v>175</v>
+      </c>
+      <c r="E13" s="18"/>
     </row>
     <row r="14" spans="1:5" ht="31.2">
       <c r="A14" s="16">
         <v>13</v>
       </c>
-      <c r="B14" s="55"/>
+      <c r="B14" s="54"/>
       <c r="C14" s="20" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="D14" s="20" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E14" s="18"/>
     </row>
@@ -4719,73 +4761,170 @@
       <c r="A15" s="16">
         <v>14</v>
       </c>
-      <c r="B15" s="55"/>
+      <c r="B15" s="54"/>
       <c r="C15" s="17" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="D15" s="17" t="s">
-        <v>179</v>
-      </c>
-      <c r="E15" s="16"/>
+        <v>176</v>
+      </c>
+      <c r="E15" s="18"/>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="16">
         <v>15</v>
       </c>
-      <c r="B16" s="55"/>
+      <c r="B16" s="54"/>
       <c r="C16" s="17" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>180</v>
-      </c>
-      <c r="E16" s="16"/>
+        <v>177</v>
+      </c>
+      <c r="E16" s="18"/>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="16">
         <v>16</v>
       </c>
-      <c r="B17" s="55"/>
+      <c r="B17" s="54"/>
       <c r="C17" s="17" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="D17" s="17"/>
-      <c r="E17" s="16"/>
+      <c r="E17" s="18"/>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="16">
         <v>17</v>
       </c>
-      <c r="B18" s="55"/>
+      <c r="B18" s="54"/>
       <c r="C18" s="17" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>181</v>
-      </c>
-      <c r="E18" s="16"/>
+        <v>178</v>
+      </c>
+      <c r="E18" s="18"/>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="16">
         <v>18</v>
       </c>
-      <c r="B19" s="56"/>
+      <c r="B19" s="55"/>
       <c r="C19" s="17" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="D19" s="17"/>
-      <c r="E19" s="16"/>
+      <c r="E19" s="18"/>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="16"/>
-      <c r="B20" s="17"/>
-      <c r="C20" s="17"/>
+      <c r="A20" s="16">
+        <v>19</v>
+      </c>
+      <c r="B20" s="56" t="s">
+        <v>199</v>
+      </c>
+      <c r="C20" s="17" t="s">
+        <v>202</v>
+      </c>
       <c r="D20" s="17"/>
-      <c r="E20" s="16"/>
+      <c r="E20" s="18"/>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="16">
+        <v>20</v>
+      </c>
+      <c r="B21" s="56"/>
+      <c r="C21" s="17" t="s">
+        <v>204</v>
+      </c>
+      <c r="D21" s="17"/>
+      <c r="E21" s="18"/>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="16">
+        <v>21</v>
+      </c>
+      <c r="B22" s="56"/>
+      <c r="C22" s="17" t="s">
+        <v>206</v>
+      </c>
+      <c r="D22" s="17"/>
+      <c r="E22" s="18"/>
+    </row>
+    <row r="23" spans="1:5" ht="31.2">
+      <c r="A23" s="16">
+        <v>22</v>
+      </c>
+      <c r="B23" s="56"/>
+      <c r="C23" s="20" t="s">
+        <v>205</v>
+      </c>
+      <c r="D23" s="17"/>
+      <c r="E23" s="18"/>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="16">
+        <v>23</v>
+      </c>
+      <c r="B24" s="56"/>
+      <c r="C24" s="17" t="s">
+        <v>201</v>
+      </c>
+      <c r="D24" s="17"/>
+      <c r="E24" s="18"/>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="16">
+        <v>24</v>
+      </c>
+      <c r="B25" s="56"/>
+      <c r="C25" s="17" t="s">
+        <v>200</v>
+      </c>
+      <c r="D25" s="17"/>
+      <c r="E25" s="18"/>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="16">
+        <v>25</v>
+      </c>
+      <c r="B26" s="56"/>
+      <c r="C26" s="17" t="s">
+        <v>203</v>
+      </c>
+      <c r="D26" s="17"/>
+      <c r="E26" s="18"/>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="16">
+        <v>26</v>
+      </c>
+      <c r="B27" s="56"/>
+      <c r="C27" s="17" t="s">
+        <v>207</v>
+      </c>
+      <c r="D27" s="17"/>
+      <c r="E27" s="18"/>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="16">
+        <v>27</v>
+      </c>
+      <c r="B28" s="16" t="s">
+        <v>208</v>
+      </c>
+      <c r="C28" s="17" t="s">
+        <v>211</v>
+      </c>
+      <c r="D28" s="17"/>
+      <c r="E28" s="16"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="B2:B19"/>
+    <mergeCell ref="B20:B27"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4823,7 +4962,7 @@
         <v>18</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C1" s="18" t="s">
         <v>19</v>
@@ -4971,116 +5110,116 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="25" t="s">
+        <v>97</v>
+      </c>
+      <c r="B1" s="23" t="s">
+        <v>92</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="D1" s="23" t="s">
+        <v>114</v>
+      </c>
+      <c r="E1" s="25" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="25" t="s">
         <v>100</v>
       </c>
-      <c r="B1" s="24" t="s">
+      <c r="B2" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="D2" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="E2" s="32" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="25" t="s">
+        <v>99</v>
+      </c>
+      <c r="B3" s="23" t="s">
         <v>95</v>
       </c>
-      <c r="C1" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="D1" s="24" t="s">
+      <c r="D3" s="23" t="s">
+        <v>120</v>
+      </c>
+      <c r="E3" s="32" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="25" t="s">
+        <v>102</v>
+      </c>
+      <c r="D4" s="23" t="s">
+        <v>116</v>
+      </c>
+      <c r="E4" s="25" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="D5" s="23" t="s">
         <v>117</v>
       </c>
-      <c r="E1" s="26" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="26" t="s">
-        <v>103</v>
-      </c>
-      <c r="B2" s="24" t="s">
-        <v>96</v>
-      </c>
-      <c r="D2" s="24" t="s">
-        <v>124</v>
-      </c>
-      <c r="E2" s="33" t="s">
+      <c r="E5" s="32" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="D6" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="E6" s="25" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="26" t="s">
-        <v>102</v>
-      </c>
-      <c r="B3" s="24" t="s">
-        <v>98</v>
-      </c>
-      <c r="D3" s="24" t="s">
-        <v>123</v>
-      </c>
-      <c r="E3" s="33" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="26" t="s">
-        <v>105</v>
-      </c>
-      <c r="D4" s="24" t="s">
-        <v>119</v>
-      </c>
-      <c r="E4" s="26" t="s">
+    <row r="7" spans="1:10">
+      <c r="E7" s="23" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
-      <c r="D5" s="24" t="s">
-        <v>120</v>
-      </c>
-      <c r="E5" s="33" t="s">
+    <row r="8" spans="1:10">
+      <c r="E8" s="23" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
-      <c r="D6" s="24" t="s">
-        <v>121</v>
-      </c>
-      <c r="E6" s="26" t="s">
+    <row r="9" spans="1:10">
+      <c r="E9" s="23" t="s">
         <v>132</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="E7" s="24" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="E8" s="24" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="E9" s="24" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="E10" s="8" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="16.2">
-      <c r="E11" s="34" t="s">
-        <v>137</v>
-      </c>
-      <c r="J11" s="25"/>
+      <c r="E11" s="33" t="s">
+        <v>134</v>
+      </c>
+      <c r="J11" s="24"/>
     </row>
     <row r="12" spans="1:10">
-      <c r="E12" s="24" t="s">
+      <c r="E12" s="23" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="E13" s="33" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
-      <c r="E13" s="34" t="s">
-        <v>141</v>
-      </c>
-    </row>
     <row r="14" spans="1:10" ht="16.2">
-      <c r="E14" s="33" t="s">
-        <v>142</v>
+      <c r="E14" s="32" t="s">
+        <v>139</v>
       </c>
     </row>
   </sheetData>
@@ -5094,32 +5233,32 @@
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="6" style="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="7.5546875" style="22" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="65.33203125" style="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7.88671875" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15" style="9" customWidth="1"/>
+    <col min="5" max="5" width="6" style="9" bestFit="1" customWidth="1"/>
     <col min="6" max="10" width="8.88671875" style="9"/>
     <col min="11" max="11" width="10.6640625" style="9" bestFit="1" customWidth="1"/>
     <col min="12" max="16384" width="8.88671875" style="9"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="33" customHeight="1">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="44" t="s">
         <v>55</v>
       </c>
-      <c r="B1" s="41" t="s">
-        <v>73</v>
-      </c>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
+      <c r="B1" s="42" t="s">
+        <v>212</v>
+      </c>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="43"/>
+      <c r="A2" s="44"/>
       <c r="B2" s="6" t="s">
         <v>18</v>
       </c>
@@ -5134,7 +5273,7 @@
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="43"/>
+      <c r="A3" s="44"/>
       <c r="B3" s="6">
         <v>1</v>
       </c>
@@ -5145,7 +5284,7 @@
       <c r="E3" s="1"/>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="43"/>
+      <c r="A4" s="44"/>
       <c r="B4" s="6">
         <v>2</v>
       </c>
@@ -5156,7 +5295,7 @@
       <c r="E4" s="1"/>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="43"/>
+      <c r="A5" s="44"/>
       <c r="B5" s="6">
         <v>3</v>
       </c>
@@ -5167,7 +5306,7 @@
       <c r="E5" s="1"/>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="43"/>
+      <c r="A6" s="44"/>
       <c r="B6" s="6">
         <v>4</v>
       </c>
@@ -5180,19 +5319,19 @@
     <row r="7" spans="1:5">
       <c r="B7" s="9"/>
     </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="43" t="s">
+    <row r="8" spans="1:5" ht="31.8" customHeight="1">
+      <c r="A8" s="44" t="s">
         <v>56</v>
       </c>
-      <c r="B8" s="41" t="s">
+      <c r="B8" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="C8" s="42"/>
-      <c r="D8" s="42"/>
-      <c r="E8" s="42"/>
+      <c r="C8" s="43"/>
+      <c r="D8" s="43"/>
+      <c r="E8" s="43"/>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="43"/>
+      <c r="A9" s="44"/>
       <c r="B9" s="6" t="s">
         <v>18</v>
       </c>
@@ -5207,66 +5346,59 @@
       </c>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="43"/>
+      <c r="A10" s="44"/>
       <c r="B10" s="6" t="s">
         <v>58</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D10" s="5"/>
       <c r="E10" s="1"/>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="43"/>
+      <c r="A11" s="44"/>
       <c r="B11" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D11" s="5"/>
       <c r="E11" s="1"/>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="43"/>
+      <c r="A12" s="44"/>
       <c r="B12" s="6" t="s">
         <v>60</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D12" s="5"/>
       <c r="E12" s="1"/>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="43"/>
+      <c r="A13" s="44"/>
       <c r="B13" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="C13" s="23" t="s">
-        <v>74</v>
+      <c r="C13" s="1" t="s">
+        <v>71</v>
       </c>
       <c r="D13" s="5"/>
       <c r="E13" s="1"/>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="43"/>
-      <c r="B14" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="C14" s="1"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="1"/>
+      <c r="A14" s="44"/>
+      <c r="B14" s="9"/>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="43"/>
-      <c r="B15" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="C15" s="1"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="1"/>
+      <c r="A15" s="44"/>
+      <c r="B15" s="9"/>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="B16" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -5284,7 +5416,7 @@
           <x14:formula1>
             <xm:f>TB_Check!B:B</xm:f>
           </x14:formula1>
-          <xm:sqref>D8:D1048576 D1:D6</xm:sqref>
+          <xm:sqref>D1:D6 D8:D13 D17:D1048576</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -5311,7 +5443,7 @@
         <v>18</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C1" s="18" t="s">
         <v>19</v>
@@ -5462,7 +5594,7 @@
         <v>18</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C1" s="12" t="s">
         <v>19</v>
@@ -5601,7 +5733,7 @@
         <v>18</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C1" s="18" t="s">
         <v>19</v>
@@ -5689,7 +5821,7 @@
         <v>18</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C1" s="18" t="s">
         <v>19</v>
@@ -5709,7 +5841,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C3" s="18"/>
     </row>
@@ -5718,7 +5850,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C4" s="18"/>
     </row>
@@ -5792,7 +5924,7 @@
         <v>18</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C1" s="18" t="s">
         <v>19</v>
@@ -5803,7 +5935,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="20" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C2" s="18"/>
     </row>
@@ -5812,7 +5944,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C3" s="18"/>
     </row>
@@ -5821,7 +5953,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C4" s="18"/>
     </row>
@@ -5830,7 +5962,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C5" s="18"/>
     </row>
@@ -5839,7 +5971,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C6" s="18"/>
     </row>
@@ -5912,7 +6044,7 @@
         <v>18</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C1" s="18" t="s">
         <v>19</v>
@@ -5923,7 +6055,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="20" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C2" s="18"/>
     </row>
@@ -5932,7 +6064,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C3" s="18"/>
     </row>
@@ -5941,7 +6073,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C4" s="18"/>
     </row>
@@ -5950,7 +6082,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C5" s="18"/>
     </row>
@@ -5959,7 +6091,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C6" s="18"/>
     </row>
@@ -5968,7 +6100,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C7" s="18"/>
     </row>
@@ -5977,7 +6109,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C8" s="18"/>
     </row>
@@ -5986,7 +6118,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="20" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C9" s="18"/>
     </row>
@@ -5995,7 +6127,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="20" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C10" s="18"/>
     </row>
@@ -6004,7 +6136,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="20" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C11" s="18"/>
     </row>
@@ -6043,57 +6175,57 @@
     <col min="7" max="7" width="10.6640625" style="19" customWidth="1"/>
     <col min="8" max="8" width="28.21875" style="19" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="19.44140625" style="19" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21.88671875" style="31" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="25.44140625" style="31" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.88671875" style="30" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="25.44140625" style="30" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="30.44140625" style="19" customWidth="1"/>
     <col min="13" max="13" width="10.44140625" style="19" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="26.5546875" style="49" customWidth="1"/>
+    <col min="14" max="14" width="26.5546875" style="40" customWidth="1"/>
     <col min="15" max="15" width="7.77734375" style="21" bestFit="1" customWidth="1"/>
     <col min="16" max="16384" width="8.88671875" style="19"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="62.4">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="28" t="s">
-        <v>86</v>
-      </c>
-      <c r="C1" s="28" t="s">
+      <c r="B1" s="27" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1" s="27" t="s">
+        <v>84</v>
+      </c>
+      <c r="D1" s="27" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1" s="27" t="s">
+        <v>107</v>
+      </c>
+      <c r="F1" s="27" t="s">
+        <v>108</v>
+      </c>
+      <c r="G1" s="31" t="s">
+        <v>112</v>
+      </c>
+      <c r="H1" s="28" t="s">
         <v>87</v>
       </c>
-      <c r="D1" s="28" t="s">
+      <c r="I1" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="J1" s="28" t="s">
+        <v>146</v>
+      </c>
+      <c r="K1" s="28" t="s">
+        <v>90</v>
+      </c>
+      <c r="L1" s="28" t="s">
         <v>88</v>
       </c>
-      <c r="E1" s="28" t="s">
-        <v>110</v>
-      </c>
-      <c r="F1" s="28" t="s">
-        <v>111</v>
-      </c>
-      <c r="G1" s="32" t="s">
-        <v>115</v>
-      </c>
-      <c r="H1" s="29" t="s">
-        <v>90</v>
-      </c>
-      <c r="I1" s="29" t="s">
-        <v>104</v>
-      </c>
-      <c r="J1" s="29" t="s">
+      <c r="M1" s="28" t="s">
+        <v>89</v>
+      </c>
+      <c r="N1" s="28" t="s">
         <v>149</v>
-      </c>
-      <c r="K1" s="29" t="s">
-        <v>93</v>
-      </c>
-      <c r="L1" s="29" t="s">
-        <v>91</v>
-      </c>
-      <c r="M1" s="29" t="s">
-        <v>92</v>
-      </c>
-      <c r="N1" s="29" t="s">
-        <v>152</v>
       </c>
       <c r="O1" s="18" t="s">
         <v>19</v>
@@ -6103,130 +6235,130 @@
       <c r="A2" s="16">
         <v>1</v>
       </c>
-      <c r="B2" s="27" t="s">
+      <c r="B2" s="26" t="s">
+        <v>103</v>
+      </c>
+      <c r="C2" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="D2" s="26" t="s">
+        <v>105</v>
+      </c>
+      <c r="E2" s="26" t="s">
         <v>106</v>
       </c>
-      <c r="C2" s="27" t="s">
-        <v>107</v>
-      </c>
-      <c r="D2" s="27" t="s">
-        <v>108</v>
-      </c>
-      <c r="E2" s="27" t="s">
+      <c r="F2" s="26" t="s">
         <v>109</v>
       </c>
-      <c r="F2" s="27" t="s">
-        <v>112</v>
-      </c>
-      <c r="G2" s="27" t="s">
-        <v>118</v>
-      </c>
-      <c r="H2" s="27" t="s">
-        <v>125</v>
-      </c>
-      <c r="I2" s="27" t="s">
-        <v>101</v>
-      </c>
-      <c r="J2" s="30" t="s">
-        <v>97</v>
-      </c>
-      <c r="K2" s="30" t="s">
+      <c r="G2" s="26" t="s">
+        <v>115</v>
+      </c>
+      <c r="H2" s="26" t="s">
+        <v>122</v>
+      </c>
+      <c r="I2" s="26" t="s">
+        <v>98</v>
+      </c>
+      <c r="J2" s="29" t="s">
         <v>94</v>
       </c>
-      <c r="L2" s="27" t="s">
-        <v>113</v>
-      </c>
-      <c r="M2" s="27" t="s">
-        <v>114</v>
-      </c>
-      <c r="N2" s="27"/>
+      <c r="K2" s="29" t="s">
+        <v>91</v>
+      </c>
+      <c r="L2" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="M2" s="26" t="s">
+        <v>111</v>
+      </c>
+      <c r="N2" s="26"/>
       <c r="O2" s="18"/>
     </row>
     <row r="3" spans="1:15" ht="46.8">
       <c r="A3" s="16">
         <v>2</v>
       </c>
-      <c r="B3" s="27" t="s">
-        <v>106</v>
-      </c>
-      <c r="C3" s="27" t="s">
-        <v>107</v>
-      </c>
-      <c r="D3" s="27" t="s">
-        <v>108</v>
-      </c>
-      <c r="E3" s="27" t="s">
-        <v>126</v>
-      </c>
-      <c r="F3" s="27" t="s">
-        <v>127</v>
-      </c>
-      <c r="G3" s="27" t="s">
+      <c r="B3" s="26" t="s">
+        <v>103</v>
+      </c>
+      <c r="C3" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="D3" s="26" t="s">
+        <v>105</v>
+      </c>
+      <c r="E3" s="26" t="s">
+        <v>123</v>
+      </c>
+      <c r="F3" s="26" t="s">
+        <v>124</v>
+      </c>
+      <c r="G3" s="26" t="s">
+        <v>119</v>
+      </c>
+      <c r="H3" s="26" t="s">
         <v>122</v>
       </c>
-      <c r="H3" s="27" t="s">
-        <v>125</v>
-      </c>
-      <c r="I3" s="27" t="s">
-        <v>101</v>
-      </c>
-      <c r="J3" s="30" t="s">
-        <v>97</v>
-      </c>
-      <c r="K3" s="30" t="s">
+      <c r="I3" s="26" t="s">
+        <v>98</v>
+      </c>
+      <c r="J3" s="29" t="s">
         <v>94</v>
       </c>
-      <c r="L3" s="27" t="s">
-        <v>99</v>
-      </c>
-      <c r="M3" s="35" t="s">
-        <v>146</v>
-      </c>
-      <c r="N3" s="27"/>
+      <c r="K3" s="29" t="s">
+        <v>91</v>
+      </c>
+      <c r="L3" s="26" t="s">
+        <v>96</v>
+      </c>
+      <c r="M3" s="34" t="s">
+        <v>143</v>
+      </c>
+      <c r="N3" s="26"/>
       <c r="O3" s="18"/>
     </row>
     <row r="4" spans="1:15" ht="31.2">
       <c r="A4" s="16">
         <v>3</v>
       </c>
-      <c r="B4" s="27" t="s">
-        <v>106</v>
-      </c>
-      <c r="C4" s="27" t="s">
-        <v>107</v>
-      </c>
-      <c r="D4" s="27" t="s">
-        <v>139</v>
-      </c>
-      <c r="E4" s="27" t="s">
+      <c r="B4" s="26" t="s">
+        <v>103</v>
+      </c>
+      <c r="C4" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="D4" s="26" t="s">
+        <v>136</v>
+      </c>
+      <c r="E4" s="26" t="s">
+        <v>137</v>
+      </c>
+      <c r="F4" s="26" t="s">
         <v>140</v>
       </c>
-      <c r="F4" s="27" t="s">
-        <v>143</v>
-      </c>
-      <c r="G4" s="27" t="s">
-        <v>116</v>
-      </c>
-      <c r="H4" s="27" t="s">
+      <c r="G4" s="26" t="s">
+        <v>113</v>
+      </c>
+      <c r="H4" s="26" t="s">
+        <v>141</v>
+      </c>
+      <c r="I4" s="26" t="s">
+        <v>98</v>
+      </c>
+      <c r="J4" s="29" t="s">
+        <v>94</v>
+      </c>
+      <c r="K4" s="29" t="s">
+        <v>94</v>
+      </c>
+      <c r="L4" s="26" t="s">
+        <v>142</v>
+      </c>
+      <c r="M4" s="26" t="s">
         <v>144</v>
       </c>
-      <c r="I4" s="27" t="s">
-        <v>101</v>
-      </c>
-      <c r="J4" s="30" t="s">
-        <v>97</v>
-      </c>
-      <c r="K4" s="30" t="s">
-        <v>97</v>
-      </c>
-      <c r="L4" s="27" t="s">
-        <v>145</v>
-      </c>
-      <c r="M4" s="27" t="s">
-        <v>147</v>
-      </c>
-      <c r="N4" s="27" t="s">
-        <v>153</v>
+      <c r="N4" s="26" t="s">
+        <v>150</v>
       </c>
       <c r="O4" s="18"/>
     </row>
@@ -6234,1031 +6366,1031 @@
       <c r="A5" s="16">
         <v>4</v>
       </c>
-      <c r="B5" s="27" t="s">
-        <v>106</v>
-      </c>
-      <c r="C5" s="27" t="s">
-        <v>107</v>
-      </c>
-      <c r="D5" s="27" t="s">
-        <v>139</v>
-      </c>
-      <c r="E5" s="27" t="s">
-        <v>148</v>
-      </c>
-      <c r="F5" s="27" t="s">
-        <v>143</v>
-      </c>
-      <c r="G5" s="27" t="s">
-        <v>116</v>
-      </c>
-      <c r="H5" s="27" t="s">
+      <c r="B5" s="26" t="s">
+        <v>103</v>
+      </c>
+      <c r="C5" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="D5" s="26" t="s">
+        <v>136</v>
+      </c>
+      <c r="E5" s="26" t="s">
+        <v>145</v>
+      </c>
+      <c r="F5" s="26" t="s">
+        <v>140</v>
+      </c>
+      <c r="G5" s="26" t="s">
+        <v>113</v>
+      </c>
+      <c r="H5" s="26" t="s">
+        <v>141</v>
+      </c>
+      <c r="I5" s="26" t="s">
+        <v>98</v>
+      </c>
+      <c r="J5" s="29" t="s">
+        <v>94</v>
+      </c>
+      <c r="K5" s="29" t="s">
+        <v>94</v>
+      </c>
+      <c r="L5" s="26" t="s">
+        <v>142</v>
+      </c>
+      <c r="M5" s="26" t="s">
         <v>144</v>
       </c>
-      <c r="I5" s="27" t="s">
-        <v>101</v>
-      </c>
-      <c r="J5" s="30" t="s">
-        <v>97</v>
-      </c>
-      <c r="K5" s="30" t="s">
-        <v>97</v>
-      </c>
-      <c r="L5" s="27" t="s">
-        <v>145</v>
-      </c>
-      <c r="M5" s="27" t="s">
-        <v>147</v>
-      </c>
-      <c r="N5" s="27" t="s">
-        <v>153</v>
+      <c r="N5" s="26" t="s">
+        <v>150</v>
       </c>
       <c r="O5" s="18"/>
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="16"/>
-      <c r="B6" s="27"/>
-      <c r="C6" s="27"/>
-      <c r="D6" s="27"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="27"/>
-      <c r="G6" s="27"/>
-      <c r="H6" s="27"/>
-      <c r="I6" s="27"/>
-      <c r="J6" s="30"/>
-      <c r="K6" s="30"/>
-      <c r="L6" s="27"/>
-      <c r="M6" s="27"/>
-      <c r="N6" s="27"/>
+      <c r="B6" s="26"/>
+      <c r="C6" s="26"/>
+      <c r="D6" s="26"/>
+      <c r="E6" s="26"/>
+      <c r="F6" s="26"/>
+      <c r="G6" s="26"/>
+      <c r="H6" s="26"/>
+      <c r="I6" s="26"/>
+      <c r="J6" s="29"/>
+      <c r="K6" s="29"/>
+      <c r="L6" s="26"/>
+      <c r="M6" s="26"/>
+      <c r="N6" s="26"/>
       <c r="O6" s="18"/>
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="16"/>
-      <c r="B7" s="27"/>
-      <c r="C7" s="27"/>
-      <c r="D7" s="27"/>
-      <c r="E7" s="27"/>
-      <c r="F7" s="27"/>
-      <c r="G7" s="27"/>
-      <c r="H7" s="27"/>
-      <c r="I7" s="27"/>
-      <c r="J7" s="30"/>
-      <c r="K7" s="30"/>
-      <c r="L7" s="27"/>
-      <c r="M7" s="27"/>
-      <c r="N7" s="27"/>
+      <c r="B7" s="26"/>
+      <c r="C7" s="26"/>
+      <c r="D7" s="26"/>
+      <c r="E7" s="26"/>
+      <c r="F7" s="26"/>
+      <c r="G7" s="26"/>
+      <c r="H7" s="26"/>
+      <c r="I7" s="26"/>
+      <c r="J7" s="29"/>
+      <c r="K7" s="29"/>
+      <c r="L7" s="26"/>
+      <c r="M7" s="26"/>
+      <c r="N7" s="26"/>
       <c r="O7" s="18"/>
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="16"/>
-      <c r="B8" s="27"/>
-      <c r="C8" s="27"/>
-      <c r="D8" s="27"/>
-      <c r="E8" s="27"/>
-      <c r="F8" s="27"/>
-      <c r="G8" s="27"/>
-      <c r="H8" s="27"/>
-      <c r="I8" s="27"/>
-      <c r="J8" s="30"/>
-      <c r="K8" s="30"/>
-      <c r="L8" s="27"/>
-      <c r="M8" s="27"/>
-      <c r="N8" s="27"/>
+      <c r="B8" s="26"/>
+      <c r="C8" s="26"/>
+      <c r="D8" s="26"/>
+      <c r="E8" s="26"/>
+      <c r="F8" s="26"/>
+      <c r="G8" s="26"/>
+      <c r="H8" s="26"/>
+      <c r="I8" s="26"/>
+      <c r="J8" s="29"/>
+      <c r="K8" s="29"/>
+      <c r="L8" s="26"/>
+      <c r="M8" s="26"/>
+      <c r="N8" s="26"/>
       <c r="O8" s="18"/>
     </row>
     <row r="9" spans="1:15">
       <c r="A9" s="16"/>
-      <c r="B9" s="27"/>
-      <c r="C9" s="27"/>
-      <c r="D9" s="27"/>
-      <c r="E9" s="27"/>
-      <c r="F9" s="27"/>
-      <c r="G9" s="27"/>
-      <c r="H9" s="27"/>
-      <c r="I9" s="27"/>
-      <c r="J9" s="30"/>
-      <c r="K9" s="30"/>
-      <c r="L9" s="27"/>
-      <c r="M9" s="27"/>
-      <c r="N9" s="27"/>
+      <c r="B9" s="26"/>
+      <c r="C9" s="26"/>
+      <c r="D9" s="26"/>
+      <c r="E9" s="26"/>
+      <c r="F9" s="26"/>
+      <c r="G9" s="26"/>
+      <c r="H9" s="26"/>
+      <c r="I9" s="26"/>
+      <c r="J9" s="29"/>
+      <c r="K9" s="29"/>
+      <c r="L9" s="26"/>
+      <c r="M9" s="26"/>
+      <c r="N9" s="26"/>
       <c r="O9" s="18"/>
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="16"/>
-      <c r="B10" s="27"/>
-      <c r="C10" s="27"/>
-      <c r="D10" s="27"/>
-      <c r="E10" s="27"/>
-      <c r="F10" s="27"/>
-      <c r="G10" s="27"/>
-      <c r="H10" s="27"/>
-      <c r="I10" s="27"/>
-      <c r="J10" s="30"/>
-      <c r="K10" s="30"/>
-      <c r="L10" s="27"/>
-      <c r="M10" s="27"/>
-      <c r="N10" s="27"/>
+      <c r="B10" s="26"/>
+      <c r="C10" s="26"/>
+      <c r="D10" s="26"/>
+      <c r="E10" s="26"/>
+      <c r="F10" s="26"/>
+      <c r="G10" s="26"/>
+      <c r="H10" s="26"/>
+      <c r="I10" s="26"/>
+      <c r="J10" s="29"/>
+      <c r="K10" s="29"/>
+      <c r="L10" s="26"/>
+      <c r="M10" s="26"/>
+      <c r="N10" s="26"/>
       <c r="O10" s="18"/>
     </row>
     <row r="11" spans="1:15">
       <c r="A11" s="16"/>
-      <c r="B11" s="27"/>
-      <c r="C11" s="27"/>
-      <c r="D11" s="27"/>
-      <c r="E11" s="27"/>
-      <c r="F11" s="27"/>
-      <c r="G11" s="27"/>
-      <c r="H11" s="27"/>
-      <c r="I11" s="27"/>
-      <c r="J11" s="30"/>
-      <c r="K11" s="30"/>
-      <c r="L11" s="27"/>
-      <c r="M11" s="27"/>
-      <c r="N11" s="27"/>
+      <c r="B11" s="26"/>
+      <c r="C11" s="26"/>
+      <c r="D11" s="26"/>
+      <c r="E11" s="26"/>
+      <c r="F11" s="26"/>
+      <c r="G11" s="26"/>
+      <c r="H11" s="26"/>
+      <c r="I11" s="26"/>
+      <c r="J11" s="29"/>
+      <c r="K11" s="29"/>
+      <c r="L11" s="26"/>
+      <c r="M11" s="26"/>
+      <c r="N11" s="26"/>
       <c r="O11" s="18"/>
     </row>
     <row r="12" spans="1:15">
       <c r="A12" s="16"/>
-      <c r="B12" s="27"/>
-      <c r="C12" s="27"/>
-      <c r="D12" s="27"/>
-      <c r="E12" s="27"/>
-      <c r="F12" s="27"/>
-      <c r="G12" s="27"/>
-      <c r="H12" s="27"/>
-      <c r="I12" s="27"/>
-      <c r="J12" s="30"/>
-      <c r="K12" s="30"/>
-      <c r="L12" s="27"/>
-      <c r="M12" s="27"/>
-      <c r="N12" s="27"/>
+      <c r="B12" s="26"/>
+      <c r="C12" s="26"/>
+      <c r="D12" s="26"/>
+      <c r="E12" s="26"/>
+      <c r="F12" s="26"/>
+      <c r="G12" s="26"/>
+      <c r="H12" s="26"/>
+      <c r="I12" s="26"/>
+      <c r="J12" s="29"/>
+      <c r="K12" s="29"/>
+      <c r="L12" s="26"/>
+      <c r="M12" s="26"/>
+      <c r="N12" s="26"/>
       <c r="O12" s="18"/>
     </row>
     <row r="13" spans="1:15">
       <c r="A13" s="16"/>
-      <c r="B13" s="27"/>
-      <c r="C13" s="27"/>
-      <c r="D13" s="27"/>
-      <c r="E13" s="27"/>
-      <c r="F13" s="27"/>
-      <c r="G13" s="27"/>
-      <c r="H13" s="27"/>
-      <c r="I13" s="27"/>
-      <c r="J13" s="30"/>
-      <c r="K13" s="30"/>
-      <c r="L13" s="27"/>
-      <c r="M13" s="27"/>
-      <c r="N13" s="27"/>
+      <c r="B13" s="26"/>
+      <c r="C13" s="26"/>
+      <c r="D13" s="26"/>
+      <c r="E13" s="26"/>
+      <c r="F13" s="26"/>
+      <c r="G13" s="26"/>
+      <c r="H13" s="26"/>
+      <c r="I13" s="26"/>
+      <c r="J13" s="29"/>
+      <c r="K13" s="29"/>
+      <c r="L13" s="26"/>
+      <c r="M13" s="26"/>
+      <c r="N13" s="26"/>
       <c r="O13" s="18"/>
     </row>
     <row r="14" spans="1:15">
       <c r="A14" s="16"/>
-      <c r="B14" s="27"/>
-      <c r="C14" s="27"/>
-      <c r="D14" s="27"/>
-      <c r="E14" s="27"/>
-      <c r="F14" s="27"/>
-      <c r="G14" s="27"/>
-      <c r="H14" s="27"/>
-      <c r="I14" s="27"/>
-      <c r="J14" s="30"/>
-      <c r="K14" s="30"/>
-      <c r="L14" s="27"/>
-      <c r="M14" s="27"/>
-      <c r="N14" s="27"/>
+      <c r="B14" s="26"/>
+      <c r="C14" s="26"/>
+      <c r="D14" s="26"/>
+      <c r="E14" s="26"/>
+      <c r="F14" s="26"/>
+      <c r="G14" s="26"/>
+      <c r="H14" s="26"/>
+      <c r="I14" s="26"/>
+      <c r="J14" s="29"/>
+      <c r="K14" s="29"/>
+      <c r="L14" s="26"/>
+      <c r="M14" s="26"/>
+      <c r="N14" s="26"/>
       <c r="O14" s="18"/>
     </row>
     <row r="15" spans="1:15">
       <c r="A15" s="16"/>
-      <c r="B15" s="27"/>
-      <c r="C15" s="27"/>
-      <c r="D15" s="27"/>
-      <c r="E15" s="27"/>
-      <c r="F15" s="27"/>
-      <c r="G15" s="27"/>
-      <c r="H15" s="27"/>
-      <c r="I15" s="27"/>
-      <c r="J15" s="30"/>
-      <c r="K15" s="30"/>
-      <c r="L15" s="27"/>
-      <c r="M15" s="27"/>
-      <c r="N15" s="27"/>
+      <c r="B15" s="26"/>
+      <c r="C15" s="26"/>
+      <c r="D15" s="26"/>
+      <c r="E15" s="26"/>
+      <c r="F15" s="26"/>
+      <c r="G15" s="26"/>
+      <c r="H15" s="26"/>
+      <c r="I15" s="26"/>
+      <c r="J15" s="29"/>
+      <c r="K15" s="29"/>
+      <c r="L15" s="26"/>
+      <c r="M15" s="26"/>
+      <c r="N15" s="26"/>
       <c r="O15" s="18"/>
     </row>
     <row r="16" spans="1:15">
       <c r="A16" s="16"/>
-      <c r="B16" s="27"/>
-      <c r="C16" s="27"/>
-      <c r="D16" s="27"/>
-      <c r="E16" s="27"/>
-      <c r="F16" s="27"/>
-      <c r="G16" s="27"/>
-      <c r="H16" s="27"/>
-      <c r="I16" s="27"/>
-      <c r="J16" s="30"/>
-      <c r="K16" s="30"/>
-      <c r="L16" s="27"/>
-      <c r="M16" s="27"/>
-      <c r="N16" s="27"/>
+      <c r="B16" s="26"/>
+      <c r="C16" s="26"/>
+      <c r="D16" s="26"/>
+      <c r="E16" s="26"/>
+      <c r="F16" s="26"/>
+      <c r="G16" s="26"/>
+      <c r="H16" s="26"/>
+      <c r="I16" s="26"/>
+      <c r="J16" s="29"/>
+      <c r="K16" s="29"/>
+      <c r="L16" s="26"/>
+      <c r="M16" s="26"/>
+      <c r="N16" s="26"/>
       <c r="O16" s="18"/>
     </row>
     <row r="17" spans="1:15">
       <c r="A17" s="16"/>
-      <c r="B17" s="27"/>
-      <c r="C17" s="27"/>
-      <c r="D17" s="27"/>
-      <c r="E17" s="27"/>
-      <c r="F17" s="27"/>
-      <c r="G17" s="27"/>
-      <c r="H17" s="27"/>
-      <c r="I17" s="27"/>
-      <c r="J17" s="30"/>
-      <c r="K17" s="30"/>
-      <c r="L17" s="27"/>
-      <c r="M17" s="27"/>
-      <c r="N17" s="27"/>
+      <c r="B17" s="26"/>
+      <c r="C17" s="26"/>
+      <c r="D17" s="26"/>
+      <c r="E17" s="26"/>
+      <c r="F17" s="26"/>
+      <c r="G17" s="26"/>
+      <c r="H17" s="26"/>
+      <c r="I17" s="26"/>
+      <c r="J17" s="29"/>
+      <c r="K17" s="29"/>
+      <c r="L17" s="26"/>
+      <c r="M17" s="26"/>
+      <c r="N17" s="26"/>
       <c r="O17" s="18"/>
     </row>
     <row r="18" spans="1:15">
       <c r="A18" s="16"/>
-      <c r="B18" s="27"/>
-      <c r="C18" s="27"/>
-      <c r="D18" s="27"/>
-      <c r="E18" s="27"/>
-      <c r="F18" s="27"/>
-      <c r="G18" s="27"/>
-      <c r="H18" s="27"/>
-      <c r="I18" s="27"/>
-      <c r="J18" s="30"/>
-      <c r="K18" s="30"/>
-      <c r="L18" s="27"/>
-      <c r="M18" s="27"/>
-      <c r="N18" s="27"/>
+      <c r="B18" s="26"/>
+      <c r="C18" s="26"/>
+      <c r="D18" s="26"/>
+      <c r="E18" s="26"/>
+      <c r="F18" s="26"/>
+      <c r="G18" s="26"/>
+      <c r="H18" s="26"/>
+      <c r="I18" s="26"/>
+      <c r="J18" s="29"/>
+      <c r="K18" s="29"/>
+      <c r="L18" s="26"/>
+      <c r="M18" s="26"/>
+      <c r="N18" s="26"/>
       <c r="O18" s="18"/>
     </row>
     <row r="19" spans="1:15">
       <c r="A19" s="16"/>
-      <c r="B19" s="27"/>
-      <c r="C19" s="27"/>
-      <c r="D19" s="27"/>
-      <c r="E19" s="27"/>
-      <c r="F19" s="27"/>
-      <c r="G19" s="27"/>
-      <c r="H19" s="27"/>
-      <c r="I19" s="27"/>
-      <c r="J19" s="30"/>
-      <c r="K19" s="30"/>
-      <c r="L19" s="27"/>
-      <c r="M19" s="27"/>
-      <c r="N19" s="27"/>
+      <c r="B19" s="26"/>
+      <c r="C19" s="26"/>
+      <c r="D19" s="26"/>
+      <c r="E19" s="26"/>
+      <c r="F19" s="26"/>
+      <c r="G19" s="26"/>
+      <c r="H19" s="26"/>
+      <c r="I19" s="26"/>
+      <c r="J19" s="29"/>
+      <c r="K19" s="29"/>
+      <c r="L19" s="26"/>
+      <c r="M19" s="26"/>
+      <c r="N19" s="26"/>
       <c r="O19" s="18"/>
     </row>
     <row r="20" spans="1:15">
       <c r="A20" s="16"/>
-      <c r="B20" s="27"/>
-      <c r="C20" s="27"/>
-      <c r="D20" s="27"/>
-      <c r="E20" s="27"/>
-      <c r="F20" s="27"/>
-      <c r="G20" s="27"/>
-      <c r="H20" s="27"/>
-      <c r="I20" s="27"/>
-      <c r="J20" s="30"/>
-      <c r="K20" s="30"/>
-      <c r="L20" s="27"/>
-      <c r="M20" s="27"/>
-      <c r="N20" s="27"/>
+      <c r="B20" s="26"/>
+      <c r="C20" s="26"/>
+      <c r="D20" s="26"/>
+      <c r="E20" s="26"/>
+      <c r="F20" s="26"/>
+      <c r="G20" s="26"/>
+      <c r="H20" s="26"/>
+      <c r="I20" s="26"/>
+      <c r="J20" s="29"/>
+      <c r="K20" s="29"/>
+      <c r="L20" s="26"/>
+      <c r="M20" s="26"/>
+      <c r="N20" s="26"/>
       <c r="O20" s="18"/>
     </row>
     <row r="21" spans="1:15">
       <c r="A21" s="16"/>
-      <c r="B21" s="27"/>
-      <c r="C21" s="27"/>
-      <c r="D21" s="27"/>
-      <c r="E21" s="27"/>
-      <c r="F21" s="27"/>
-      <c r="G21" s="27"/>
-      <c r="H21" s="27"/>
-      <c r="I21" s="27"/>
-      <c r="J21" s="30"/>
-      <c r="K21" s="30"/>
-      <c r="L21" s="27"/>
-      <c r="M21" s="27"/>
-      <c r="N21" s="27"/>
+      <c r="B21" s="26"/>
+      <c r="C21" s="26"/>
+      <c r="D21" s="26"/>
+      <c r="E21" s="26"/>
+      <c r="F21" s="26"/>
+      <c r="G21" s="26"/>
+      <c r="H21" s="26"/>
+      <c r="I21" s="26"/>
+      <c r="J21" s="29"/>
+      <c r="K21" s="29"/>
+      <c r="L21" s="26"/>
+      <c r="M21" s="26"/>
+      <c r="N21" s="26"/>
       <c r="O21" s="18"/>
     </row>
     <row r="22" spans="1:15">
       <c r="A22" s="16"/>
-      <c r="B22" s="27"/>
-      <c r="C22" s="27"/>
-      <c r="D22" s="27"/>
-      <c r="E22" s="27"/>
-      <c r="F22" s="27"/>
-      <c r="G22" s="27"/>
-      <c r="H22" s="27"/>
-      <c r="I22" s="27"/>
-      <c r="J22" s="30"/>
-      <c r="K22" s="30"/>
-      <c r="L22" s="27"/>
-      <c r="M22" s="27"/>
-      <c r="N22" s="27"/>
+      <c r="B22" s="26"/>
+      <c r="C22" s="26"/>
+      <c r="D22" s="26"/>
+      <c r="E22" s="26"/>
+      <c r="F22" s="26"/>
+      <c r="G22" s="26"/>
+      <c r="H22" s="26"/>
+      <c r="I22" s="26"/>
+      <c r="J22" s="29"/>
+      <c r="K22" s="29"/>
+      <c r="L22" s="26"/>
+      <c r="M22" s="26"/>
+      <c r="N22" s="26"/>
       <c r="O22" s="18"/>
     </row>
     <row r="23" spans="1:15">
       <c r="A23" s="16"/>
-      <c r="B23" s="27"/>
-      <c r="C23" s="27"/>
-      <c r="D23" s="27"/>
-      <c r="E23" s="27"/>
-      <c r="F23" s="27"/>
-      <c r="G23" s="27"/>
-      <c r="H23" s="27"/>
-      <c r="I23" s="27"/>
-      <c r="J23" s="30"/>
-      <c r="K23" s="30"/>
-      <c r="L23" s="27"/>
-      <c r="M23" s="27"/>
-      <c r="N23" s="27"/>
+      <c r="B23" s="26"/>
+      <c r="C23" s="26"/>
+      <c r="D23" s="26"/>
+      <c r="E23" s="26"/>
+      <c r="F23" s="26"/>
+      <c r="G23" s="26"/>
+      <c r="H23" s="26"/>
+      <c r="I23" s="26"/>
+      <c r="J23" s="29"/>
+      <c r="K23" s="29"/>
+      <c r="L23" s="26"/>
+      <c r="M23" s="26"/>
+      <c r="N23" s="26"/>
       <c r="O23" s="18"/>
     </row>
     <row r="24" spans="1:15">
       <c r="A24" s="16"/>
-      <c r="B24" s="27"/>
-      <c r="C24" s="27"/>
-      <c r="D24" s="27"/>
-      <c r="E24" s="27"/>
-      <c r="F24" s="27"/>
-      <c r="G24" s="27"/>
-      <c r="H24" s="27"/>
-      <c r="I24" s="27"/>
-      <c r="J24" s="30"/>
-      <c r="K24" s="30"/>
-      <c r="L24" s="27"/>
-      <c r="M24" s="27"/>
-      <c r="N24" s="27"/>
+      <c r="B24" s="26"/>
+      <c r="C24" s="26"/>
+      <c r="D24" s="26"/>
+      <c r="E24" s="26"/>
+      <c r="F24" s="26"/>
+      <c r="G24" s="26"/>
+      <c r="H24" s="26"/>
+      <c r="I24" s="26"/>
+      <c r="J24" s="29"/>
+      <c r="K24" s="29"/>
+      <c r="L24" s="26"/>
+      <c r="M24" s="26"/>
+      <c r="N24" s="26"/>
       <c r="O24" s="18"/>
     </row>
     <row r="25" spans="1:15">
       <c r="A25" s="16"/>
-      <c r="B25" s="27"/>
-      <c r="C25" s="27"/>
-      <c r="D25" s="27"/>
-      <c r="E25" s="27"/>
-      <c r="F25" s="27"/>
-      <c r="G25" s="27"/>
-      <c r="H25" s="27"/>
-      <c r="I25" s="27"/>
-      <c r="J25" s="30"/>
-      <c r="K25" s="30"/>
-      <c r="L25" s="27"/>
-      <c r="M25" s="27"/>
-      <c r="N25" s="27"/>
+      <c r="B25" s="26"/>
+      <c r="C25" s="26"/>
+      <c r="D25" s="26"/>
+      <c r="E25" s="26"/>
+      <c r="F25" s="26"/>
+      <c r="G25" s="26"/>
+      <c r="H25" s="26"/>
+      <c r="I25" s="26"/>
+      <c r="J25" s="29"/>
+      <c r="K25" s="29"/>
+      <c r="L25" s="26"/>
+      <c r="M25" s="26"/>
+      <c r="N25" s="26"/>
       <c r="O25" s="18"/>
     </row>
     <row r="26" spans="1:15">
       <c r="A26" s="16"/>
-      <c r="B26" s="27"/>
-      <c r="C26" s="27"/>
-      <c r="D26" s="27"/>
-      <c r="E26" s="27"/>
-      <c r="F26" s="27"/>
-      <c r="G26" s="27"/>
-      <c r="H26" s="27"/>
-      <c r="I26" s="27"/>
-      <c r="J26" s="30"/>
-      <c r="K26" s="30"/>
-      <c r="L26" s="27"/>
-      <c r="M26" s="27"/>
-      <c r="N26" s="27"/>
+      <c r="B26" s="26"/>
+      <c r="C26" s="26"/>
+      <c r="D26" s="26"/>
+      <c r="E26" s="26"/>
+      <c r="F26" s="26"/>
+      <c r="G26" s="26"/>
+      <c r="H26" s="26"/>
+      <c r="I26" s="26"/>
+      <c r="J26" s="29"/>
+      <c r="K26" s="29"/>
+      <c r="L26" s="26"/>
+      <c r="M26" s="26"/>
+      <c r="N26" s="26"/>
       <c r="O26" s="18"/>
     </row>
     <row r="27" spans="1:15">
       <c r="A27" s="16"/>
-      <c r="B27" s="27"/>
-      <c r="C27" s="27"/>
-      <c r="D27" s="27"/>
-      <c r="E27" s="27"/>
-      <c r="F27" s="27"/>
-      <c r="G27" s="27"/>
-      <c r="H27" s="27"/>
-      <c r="I27" s="27"/>
-      <c r="J27" s="30"/>
-      <c r="K27" s="30"/>
-      <c r="L27" s="27"/>
-      <c r="M27" s="27"/>
-      <c r="N27" s="27"/>
+      <c r="B27" s="26"/>
+      <c r="C27" s="26"/>
+      <c r="D27" s="26"/>
+      <c r="E27" s="26"/>
+      <c r="F27" s="26"/>
+      <c r="G27" s="26"/>
+      <c r="H27" s="26"/>
+      <c r="I27" s="26"/>
+      <c r="J27" s="29"/>
+      <c r="K27" s="29"/>
+      <c r="L27" s="26"/>
+      <c r="M27" s="26"/>
+      <c r="N27" s="26"/>
       <c r="O27" s="18"/>
     </row>
     <row r="28" spans="1:15">
       <c r="A28" s="16"/>
-      <c r="B28" s="27"/>
-      <c r="C28" s="27"/>
-      <c r="D28" s="27"/>
-      <c r="E28" s="27"/>
-      <c r="F28" s="27"/>
-      <c r="G28" s="27"/>
-      <c r="H28" s="27"/>
-      <c r="I28" s="27"/>
-      <c r="J28" s="30"/>
-      <c r="K28" s="30"/>
-      <c r="L28" s="27"/>
-      <c r="M28" s="27"/>
-      <c r="N28" s="27"/>
+      <c r="B28" s="26"/>
+      <c r="C28" s="26"/>
+      <c r="D28" s="26"/>
+      <c r="E28" s="26"/>
+      <c r="F28" s="26"/>
+      <c r="G28" s="26"/>
+      <c r="H28" s="26"/>
+      <c r="I28" s="26"/>
+      <c r="J28" s="29"/>
+      <c r="K28" s="29"/>
+      <c r="L28" s="26"/>
+      <c r="M28" s="26"/>
+      <c r="N28" s="26"/>
       <c r="O28" s="18"/>
     </row>
     <row r="29" spans="1:15">
       <c r="A29" s="16"/>
-      <c r="B29" s="27"/>
-      <c r="C29" s="27"/>
-      <c r="D29" s="27"/>
-      <c r="E29" s="27"/>
-      <c r="F29" s="27"/>
-      <c r="G29" s="27"/>
-      <c r="H29" s="27"/>
-      <c r="I29" s="27"/>
-      <c r="J29" s="30"/>
-      <c r="K29" s="30"/>
-      <c r="L29" s="27"/>
-      <c r="M29" s="27"/>
-      <c r="N29" s="27"/>
+      <c r="B29" s="26"/>
+      <c r="C29" s="26"/>
+      <c r="D29" s="26"/>
+      <c r="E29" s="26"/>
+      <c r="F29" s="26"/>
+      <c r="G29" s="26"/>
+      <c r="H29" s="26"/>
+      <c r="I29" s="26"/>
+      <c r="J29" s="29"/>
+      <c r="K29" s="29"/>
+      <c r="L29" s="26"/>
+      <c r="M29" s="26"/>
+      <c r="N29" s="26"/>
       <c r="O29" s="18"/>
     </row>
     <row r="30" spans="1:15">
       <c r="A30" s="16"/>
-      <c r="B30" s="27"/>
-      <c r="C30" s="27"/>
-      <c r="D30" s="27"/>
-      <c r="E30" s="27"/>
-      <c r="F30" s="27"/>
-      <c r="G30" s="27"/>
-      <c r="H30" s="27"/>
-      <c r="I30" s="27"/>
-      <c r="J30" s="30"/>
-      <c r="K30" s="30"/>
-      <c r="L30" s="27"/>
-      <c r="M30" s="27"/>
-      <c r="N30" s="27"/>
+      <c r="B30" s="26"/>
+      <c r="C30" s="26"/>
+      <c r="D30" s="26"/>
+      <c r="E30" s="26"/>
+      <c r="F30" s="26"/>
+      <c r="G30" s="26"/>
+      <c r="H30" s="26"/>
+      <c r="I30" s="26"/>
+      <c r="J30" s="29"/>
+      <c r="K30" s="29"/>
+      <c r="L30" s="26"/>
+      <c r="M30" s="26"/>
+      <c r="N30" s="26"/>
       <c r="O30" s="18"/>
     </row>
     <row r="31" spans="1:15">
       <c r="A31" s="16"/>
-      <c r="B31" s="27"/>
-      <c r="C31" s="27"/>
-      <c r="D31" s="27"/>
-      <c r="E31" s="27"/>
-      <c r="F31" s="27"/>
-      <c r="G31" s="27"/>
-      <c r="H31" s="27"/>
-      <c r="I31" s="27"/>
-      <c r="J31" s="30"/>
-      <c r="K31" s="30"/>
-      <c r="L31" s="27"/>
-      <c r="M31" s="27"/>
-      <c r="N31" s="27"/>
+      <c r="B31" s="26"/>
+      <c r="C31" s="26"/>
+      <c r="D31" s="26"/>
+      <c r="E31" s="26"/>
+      <c r="F31" s="26"/>
+      <c r="G31" s="26"/>
+      <c r="H31" s="26"/>
+      <c r="I31" s="26"/>
+      <c r="J31" s="29"/>
+      <c r="K31" s="29"/>
+      <c r="L31" s="26"/>
+      <c r="M31" s="26"/>
+      <c r="N31" s="26"/>
       <c r="O31" s="18"/>
     </row>
     <row r="32" spans="1:15">
       <c r="A32" s="16"/>
-      <c r="B32" s="27"/>
-      <c r="C32" s="27"/>
-      <c r="D32" s="27"/>
-      <c r="E32" s="27"/>
-      <c r="F32" s="27"/>
-      <c r="G32" s="27"/>
-      <c r="H32" s="27"/>
-      <c r="I32" s="27"/>
-      <c r="J32" s="30"/>
-      <c r="K32" s="30"/>
-      <c r="L32" s="27"/>
-      <c r="M32" s="27"/>
-      <c r="N32" s="27"/>
+      <c r="B32" s="26"/>
+      <c r="C32" s="26"/>
+      <c r="D32" s="26"/>
+      <c r="E32" s="26"/>
+      <c r="F32" s="26"/>
+      <c r="G32" s="26"/>
+      <c r="H32" s="26"/>
+      <c r="I32" s="26"/>
+      <c r="J32" s="29"/>
+      <c r="K32" s="29"/>
+      <c r="L32" s="26"/>
+      <c r="M32" s="26"/>
+      <c r="N32" s="26"/>
       <c r="O32" s="18"/>
     </row>
     <row r="33" spans="1:15">
       <c r="A33" s="16"/>
-      <c r="B33" s="27"/>
-      <c r="C33" s="27"/>
-      <c r="D33" s="27"/>
-      <c r="E33" s="27"/>
-      <c r="F33" s="27"/>
-      <c r="G33" s="27"/>
-      <c r="H33" s="27"/>
-      <c r="I33" s="27"/>
-      <c r="J33" s="30"/>
-      <c r="K33" s="30"/>
-      <c r="L33" s="27"/>
-      <c r="M33" s="27"/>
-      <c r="N33" s="27"/>
+      <c r="B33" s="26"/>
+      <c r="C33" s="26"/>
+      <c r="D33" s="26"/>
+      <c r="E33" s="26"/>
+      <c r="F33" s="26"/>
+      <c r="G33" s="26"/>
+      <c r="H33" s="26"/>
+      <c r="I33" s="26"/>
+      <c r="J33" s="29"/>
+      <c r="K33" s="29"/>
+      <c r="L33" s="26"/>
+      <c r="M33" s="26"/>
+      <c r="N33" s="26"/>
       <c r="O33" s="18"/>
     </row>
     <row r="34" spans="1:15">
       <c r="A34" s="16"/>
-      <c r="B34" s="27"/>
-      <c r="C34" s="27"/>
-      <c r="D34" s="27"/>
-      <c r="E34" s="27"/>
-      <c r="F34" s="27"/>
-      <c r="G34" s="27"/>
-      <c r="H34" s="27"/>
-      <c r="I34" s="27"/>
-      <c r="J34" s="30"/>
-      <c r="K34" s="30"/>
-      <c r="L34" s="27"/>
-      <c r="M34" s="27"/>
-      <c r="N34" s="27"/>
+      <c r="B34" s="26"/>
+      <c r="C34" s="26"/>
+      <c r="D34" s="26"/>
+      <c r="E34" s="26"/>
+      <c r="F34" s="26"/>
+      <c r="G34" s="26"/>
+      <c r="H34" s="26"/>
+      <c r="I34" s="26"/>
+      <c r="J34" s="29"/>
+      <c r="K34" s="29"/>
+      <c r="L34" s="26"/>
+      <c r="M34" s="26"/>
+      <c r="N34" s="26"/>
       <c r="O34" s="18"/>
     </row>
     <row r="35" spans="1:15">
       <c r="A35" s="16"/>
-      <c r="B35" s="27"/>
-      <c r="C35" s="27"/>
-      <c r="D35" s="27"/>
-      <c r="E35" s="27"/>
-      <c r="F35" s="27"/>
-      <c r="G35" s="27"/>
-      <c r="H35" s="27"/>
-      <c r="I35" s="27"/>
-      <c r="J35" s="30"/>
-      <c r="K35" s="30"/>
-      <c r="L35" s="27"/>
-      <c r="M35" s="27"/>
-      <c r="N35" s="27"/>
+      <c r="B35" s="26"/>
+      <c r="C35" s="26"/>
+      <c r="D35" s="26"/>
+      <c r="E35" s="26"/>
+      <c r="F35" s="26"/>
+      <c r="G35" s="26"/>
+      <c r="H35" s="26"/>
+      <c r="I35" s="26"/>
+      <c r="J35" s="29"/>
+      <c r="K35" s="29"/>
+      <c r="L35" s="26"/>
+      <c r="M35" s="26"/>
+      <c r="N35" s="26"/>
       <c r="O35" s="18"/>
     </row>
     <row r="36" spans="1:15">
       <c r="A36" s="16"/>
-      <c r="B36" s="27"/>
-      <c r="C36" s="27"/>
-      <c r="D36" s="27"/>
-      <c r="E36" s="27"/>
-      <c r="F36" s="27"/>
-      <c r="G36" s="27"/>
-      <c r="H36" s="27"/>
-      <c r="I36" s="27"/>
-      <c r="J36" s="30"/>
-      <c r="K36" s="30"/>
-      <c r="L36" s="27"/>
-      <c r="M36" s="27"/>
-      <c r="N36" s="27"/>
+      <c r="B36" s="26"/>
+      <c r="C36" s="26"/>
+      <c r="D36" s="26"/>
+      <c r="E36" s="26"/>
+      <c r="F36" s="26"/>
+      <c r="G36" s="26"/>
+      <c r="H36" s="26"/>
+      <c r="I36" s="26"/>
+      <c r="J36" s="29"/>
+      <c r="K36" s="29"/>
+      <c r="L36" s="26"/>
+      <c r="M36" s="26"/>
+      <c r="N36" s="26"/>
       <c r="O36" s="18"/>
     </row>
     <row r="37" spans="1:15">
       <c r="A37" s="16"/>
-      <c r="B37" s="27"/>
-      <c r="C37" s="27"/>
-      <c r="D37" s="27"/>
-      <c r="E37" s="27"/>
-      <c r="F37" s="27"/>
-      <c r="G37" s="27"/>
-      <c r="H37" s="27"/>
-      <c r="I37" s="27"/>
-      <c r="J37" s="30"/>
-      <c r="K37" s="30"/>
-      <c r="L37" s="27"/>
-      <c r="M37" s="27"/>
-      <c r="N37" s="27"/>
+      <c r="B37" s="26"/>
+      <c r="C37" s="26"/>
+      <c r="D37" s="26"/>
+      <c r="E37" s="26"/>
+      <c r="F37" s="26"/>
+      <c r="G37" s="26"/>
+      <c r="H37" s="26"/>
+      <c r="I37" s="26"/>
+      <c r="J37" s="29"/>
+      <c r="K37" s="29"/>
+      <c r="L37" s="26"/>
+      <c r="M37" s="26"/>
+      <c r="N37" s="26"/>
       <c r="O37" s="18"/>
     </row>
     <row r="38" spans="1:15">
       <c r="A38" s="16"/>
-      <c r="B38" s="27"/>
-      <c r="C38" s="27"/>
-      <c r="D38" s="27"/>
-      <c r="E38" s="27"/>
-      <c r="F38" s="27"/>
-      <c r="G38" s="27"/>
-      <c r="H38" s="27"/>
-      <c r="I38" s="27"/>
-      <c r="J38" s="30"/>
-      <c r="K38" s="30"/>
-      <c r="L38" s="27"/>
-      <c r="M38" s="27"/>
-      <c r="N38" s="27"/>
+      <c r="B38" s="26"/>
+      <c r="C38" s="26"/>
+      <c r="D38" s="26"/>
+      <c r="E38" s="26"/>
+      <c r="F38" s="26"/>
+      <c r="G38" s="26"/>
+      <c r="H38" s="26"/>
+      <c r="I38" s="26"/>
+      <c r="J38" s="29"/>
+      <c r="K38" s="29"/>
+      <c r="L38" s="26"/>
+      <c r="M38" s="26"/>
+      <c r="N38" s="26"/>
       <c r="O38" s="18"/>
     </row>
     <row r="39" spans="1:15">
       <c r="A39" s="16"/>
-      <c r="B39" s="27"/>
-      <c r="C39" s="27"/>
-      <c r="D39" s="27"/>
-      <c r="E39" s="27"/>
-      <c r="F39" s="27"/>
-      <c r="G39" s="27"/>
-      <c r="H39" s="27"/>
-      <c r="I39" s="27"/>
-      <c r="J39" s="30"/>
-      <c r="K39" s="30"/>
-      <c r="L39" s="27"/>
-      <c r="M39" s="27"/>
-      <c r="N39" s="27"/>
+      <c r="B39" s="26"/>
+      <c r="C39" s="26"/>
+      <c r="D39" s="26"/>
+      <c r="E39" s="26"/>
+      <c r="F39" s="26"/>
+      <c r="G39" s="26"/>
+      <c r="H39" s="26"/>
+      <c r="I39" s="26"/>
+      <c r="J39" s="29"/>
+      <c r="K39" s="29"/>
+      <c r="L39" s="26"/>
+      <c r="M39" s="26"/>
+      <c r="N39" s="26"/>
       <c r="O39" s="18"/>
     </row>
     <row r="40" spans="1:15">
       <c r="A40" s="16"/>
-      <c r="B40" s="27"/>
-      <c r="C40" s="27"/>
-      <c r="D40" s="27"/>
-      <c r="E40" s="27"/>
-      <c r="F40" s="27"/>
-      <c r="G40" s="27"/>
-      <c r="H40" s="27"/>
-      <c r="I40" s="27"/>
-      <c r="J40" s="30"/>
-      <c r="K40" s="30"/>
-      <c r="L40" s="27"/>
-      <c r="M40" s="27"/>
-      <c r="N40" s="27"/>
+      <c r="B40" s="26"/>
+      <c r="C40" s="26"/>
+      <c r="D40" s="26"/>
+      <c r="E40" s="26"/>
+      <c r="F40" s="26"/>
+      <c r="G40" s="26"/>
+      <c r="H40" s="26"/>
+      <c r="I40" s="26"/>
+      <c r="J40" s="29"/>
+      <c r="K40" s="29"/>
+      <c r="L40" s="26"/>
+      <c r="M40" s="26"/>
+      <c r="N40" s="26"/>
       <c r="O40" s="18"/>
     </row>
     <row r="41" spans="1:15">
       <c r="A41" s="16"/>
-      <c r="B41" s="27"/>
-      <c r="C41" s="27"/>
-      <c r="D41" s="27"/>
-      <c r="E41" s="27"/>
-      <c r="F41" s="27"/>
-      <c r="G41" s="27"/>
-      <c r="H41" s="27"/>
-      <c r="I41" s="27"/>
-      <c r="J41" s="30"/>
-      <c r="K41" s="30"/>
-      <c r="L41" s="27"/>
-      <c r="M41" s="27"/>
-      <c r="N41" s="27"/>
+      <c r="B41" s="26"/>
+      <c r="C41" s="26"/>
+      <c r="D41" s="26"/>
+      <c r="E41" s="26"/>
+      <c r="F41" s="26"/>
+      <c r="G41" s="26"/>
+      <c r="H41" s="26"/>
+      <c r="I41" s="26"/>
+      <c r="J41" s="29"/>
+      <c r="K41" s="29"/>
+      <c r="L41" s="26"/>
+      <c r="M41" s="26"/>
+      <c r="N41" s="26"/>
       <c r="O41" s="18"/>
     </row>
     <row r="42" spans="1:15">
       <c r="A42" s="16"/>
-      <c r="B42" s="27"/>
-      <c r="C42" s="27"/>
-      <c r="D42" s="27"/>
-      <c r="E42" s="27"/>
-      <c r="F42" s="27"/>
-      <c r="G42" s="27"/>
-      <c r="H42" s="27"/>
-      <c r="I42" s="27"/>
-      <c r="J42" s="30"/>
-      <c r="K42" s="30"/>
-      <c r="L42" s="27"/>
-      <c r="M42" s="27"/>
-      <c r="N42" s="27"/>
+      <c r="B42" s="26"/>
+      <c r="C42" s="26"/>
+      <c r="D42" s="26"/>
+      <c r="E42" s="26"/>
+      <c r="F42" s="26"/>
+      <c r="G42" s="26"/>
+      <c r="H42" s="26"/>
+      <c r="I42" s="26"/>
+      <c r="J42" s="29"/>
+      <c r="K42" s="29"/>
+      <c r="L42" s="26"/>
+      <c r="M42" s="26"/>
+      <c r="N42" s="26"/>
       <c r="O42" s="18"/>
     </row>
     <row r="43" spans="1:15">
       <c r="A43" s="16"/>
-      <c r="B43" s="27"/>
-      <c r="C43" s="27"/>
-      <c r="D43" s="27"/>
-      <c r="E43" s="27"/>
-      <c r="F43" s="27"/>
-      <c r="G43" s="27"/>
-      <c r="H43" s="27"/>
-      <c r="I43" s="27"/>
-      <c r="J43" s="30"/>
-      <c r="K43" s="30"/>
-      <c r="L43" s="27"/>
-      <c r="M43" s="27"/>
-      <c r="N43" s="27"/>
+      <c r="B43" s="26"/>
+      <c r="C43" s="26"/>
+      <c r="D43" s="26"/>
+      <c r="E43" s="26"/>
+      <c r="F43" s="26"/>
+      <c r="G43" s="26"/>
+      <c r="H43" s="26"/>
+      <c r="I43" s="26"/>
+      <c r="J43" s="29"/>
+      <c r="K43" s="29"/>
+      <c r="L43" s="26"/>
+      <c r="M43" s="26"/>
+      <c r="N43" s="26"/>
       <c r="O43" s="18"/>
     </row>
     <row r="44" spans="1:15">
       <c r="A44" s="16"/>
-      <c r="B44" s="27"/>
-      <c r="C44" s="27"/>
-      <c r="D44" s="27"/>
-      <c r="E44" s="27"/>
-      <c r="F44" s="27"/>
-      <c r="G44" s="27"/>
-      <c r="H44" s="27"/>
-      <c r="I44" s="27"/>
-      <c r="J44" s="30"/>
-      <c r="K44" s="30"/>
-      <c r="L44" s="27"/>
-      <c r="M44" s="27"/>
-      <c r="N44" s="27"/>
+      <c r="B44" s="26"/>
+      <c r="C44" s="26"/>
+      <c r="D44" s="26"/>
+      <c r="E44" s="26"/>
+      <c r="F44" s="26"/>
+      <c r="G44" s="26"/>
+      <c r="H44" s="26"/>
+      <c r="I44" s="26"/>
+      <c r="J44" s="29"/>
+      <c r="K44" s="29"/>
+      <c r="L44" s="26"/>
+      <c r="M44" s="26"/>
+      <c r="N44" s="26"/>
       <c r="O44" s="18"/>
     </row>
     <row r="45" spans="1:15">
       <c r="A45" s="16"/>
-      <c r="B45" s="27"/>
-      <c r="C45" s="27"/>
-      <c r="D45" s="27"/>
-      <c r="E45" s="27"/>
-      <c r="F45" s="27"/>
-      <c r="G45" s="27"/>
-      <c r="H45" s="27"/>
-      <c r="I45" s="27"/>
-      <c r="J45" s="30"/>
-      <c r="K45" s="30"/>
-      <c r="L45" s="27"/>
-      <c r="M45" s="27"/>
-      <c r="N45" s="27"/>
+      <c r="B45" s="26"/>
+      <c r="C45" s="26"/>
+      <c r="D45" s="26"/>
+      <c r="E45" s="26"/>
+      <c r="F45" s="26"/>
+      <c r="G45" s="26"/>
+      <c r="H45" s="26"/>
+      <c r="I45" s="26"/>
+      <c r="J45" s="29"/>
+      <c r="K45" s="29"/>
+      <c r="L45" s="26"/>
+      <c r="M45" s="26"/>
+      <c r="N45" s="26"/>
       <c r="O45" s="18"/>
     </row>
     <row r="46" spans="1:15">
       <c r="A46" s="16"/>
-      <c r="B46" s="27"/>
-      <c r="C46" s="27"/>
-      <c r="D46" s="27"/>
-      <c r="E46" s="27"/>
-      <c r="F46" s="27"/>
-      <c r="G46" s="27"/>
-      <c r="H46" s="27"/>
-      <c r="I46" s="27"/>
-      <c r="J46" s="30"/>
-      <c r="K46" s="30"/>
-      <c r="L46" s="27"/>
-      <c r="M46" s="27"/>
-      <c r="N46" s="27"/>
+      <c r="B46" s="26"/>
+      <c r="C46" s="26"/>
+      <c r="D46" s="26"/>
+      <c r="E46" s="26"/>
+      <c r="F46" s="26"/>
+      <c r="G46" s="26"/>
+      <c r="H46" s="26"/>
+      <c r="I46" s="26"/>
+      <c r="J46" s="29"/>
+      <c r="K46" s="29"/>
+      <c r="L46" s="26"/>
+      <c r="M46" s="26"/>
+      <c r="N46" s="26"/>
       <c r="O46" s="18"/>
     </row>
     <row r="47" spans="1:15">
       <c r="A47" s="16"/>
-      <c r="B47" s="27"/>
-      <c r="C47" s="27"/>
-      <c r="D47" s="27"/>
-      <c r="E47" s="27"/>
-      <c r="F47" s="27"/>
-      <c r="G47" s="27"/>
-      <c r="H47" s="27"/>
-      <c r="I47" s="27"/>
-      <c r="J47" s="30"/>
-      <c r="K47" s="30"/>
-      <c r="L47" s="27"/>
-      <c r="M47" s="27"/>
-      <c r="N47" s="27"/>
+      <c r="B47" s="26"/>
+      <c r="C47" s="26"/>
+      <c r="D47" s="26"/>
+      <c r="E47" s="26"/>
+      <c r="F47" s="26"/>
+      <c r="G47" s="26"/>
+      <c r="H47" s="26"/>
+      <c r="I47" s="26"/>
+      <c r="J47" s="29"/>
+      <c r="K47" s="29"/>
+      <c r="L47" s="26"/>
+      <c r="M47" s="26"/>
+      <c r="N47" s="26"/>
       <c r="O47" s="18"/>
     </row>
     <row r="48" spans="1:15">
       <c r="A48" s="16"/>
-      <c r="B48" s="27"/>
-      <c r="C48" s="27"/>
-      <c r="D48" s="27"/>
-      <c r="E48" s="27"/>
-      <c r="F48" s="27"/>
-      <c r="G48" s="27"/>
-      <c r="H48" s="27"/>
-      <c r="I48" s="27"/>
-      <c r="J48" s="30"/>
-      <c r="K48" s="30"/>
-      <c r="L48" s="27"/>
-      <c r="M48" s="27"/>
-      <c r="N48" s="27"/>
+      <c r="B48" s="26"/>
+      <c r="C48" s="26"/>
+      <c r="D48" s="26"/>
+      <c r="E48" s="26"/>
+      <c r="F48" s="26"/>
+      <c r="G48" s="26"/>
+      <c r="H48" s="26"/>
+      <c r="I48" s="26"/>
+      <c r="J48" s="29"/>
+      <c r="K48" s="29"/>
+      <c r="L48" s="26"/>
+      <c r="M48" s="26"/>
+      <c r="N48" s="26"/>
       <c r="O48" s="18"/>
     </row>
     <row r="49" spans="1:15">
       <c r="A49" s="16"/>
-      <c r="B49" s="27"/>
-      <c r="C49" s="27"/>
-      <c r="D49" s="27"/>
-      <c r="E49" s="27"/>
-      <c r="F49" s="27"/>
-      <c r="G49" s="27"/>
-      <c r="H49" s="27"/>
-      <c r="I49" s="27"/>
-      <c r="J49" s="30"/>
-      <c r="K49" s="30"/>
-      <c r="L49" s="27"/>
-      <c r="M49" s="27"/>
-      <c r="N49" s="27"/>
+      <c r="B49" s="26"/>
+      <c r="C49" s="26"/>
+      <c r="D49" s="26"/>
+      <c r="E49" s="26"/>
+      <c r="F49" s="26"/>
+      <c r="G49" s="26"/>
+      <c r="H49" s="26"/>
+      <c r="I49" s="26"/>
+      <c r="J49" s="29"/>
+      <c r="K49" s="29"/>
+      <c r="L49" s="26"/>
+      <c r="M49" s="26"/>
+      <c r="N49" s="26"/>
       <c r="O49" s="18"/>
     </row>
     <row r="50" spans="1:15">
       <c r="A50" s="16"/>
-      <c r="B50" s="27"/>
-      <c r="C50" s="27"/>
-      <c r="D50" s="27"/>
-      <c r="E50" s="27"/>
-      <c r="F50" s="27"/>
-      <c r="G50" s="27"/>
-      <c r="H50" s="27"/>
-      <c r="I50" s="27"/>
-      <c r="J50" s="30"/>
-      <c r="K50" s="30"/>
-      <c r="L50" s="27"/>
-      <c r="M50" s="27"/>
-      <c r="N50" s="27"/>
+      <c r="B50" s="26"/>
+      <c r="C50" s="26"/>
+      <c r="D50" s="26"/>
+      <c r="E50" s="26"/>
+      <c r="F50" s="26"/>
+      <c r="G50" s="26"/>
+      <c r="H50" s="26"/>
+      <c r="I50" s="26"/>
+      <c r="J50" s="29"/>
+      <c r="K50" s="29"/>
+      <c r="L50" s="26"/>
+      <c r="M50" s="26"/>
+      <c r="N50" s="26"/>
       <c r="O50" s="18"/>
     </row>
     <row r="51" spans="1:15">
       <c r="A51" s="16"/>
-      <c r="B51" s="27"/>
-      <c r="C51" s="27"/>
-      <c r="D51" s="27"/>
-      <c r="E51" s="27"/>
-      <c r="F51" s="27"/>
-      <c r="G51" s="27"/>
-      <c r="H51" s="27"/>
-      <c r="I51" s="27"/>
-      <c r="J51" s="30"/>
-      <c r="K51" s="30"/>
-      <c r="L51" s="27"/>
-      <c r="M51" s="27"/>
-      <c r="N51" s="27"/>
+      <c r="B51" s="26"/>
+      <c r="C51" s="26"/>
+      <c r="D51" s="26"/>
+      <c r="E51" s="26"/>
+      <c r="F51" s="26"/>
+      <c r="G51" s="26"/>
+      <c r="H51" s="26"/>
+      <c r="I51" s="26"/>
+      <c r="J51" s="29"/>
+      <c r="K51" s="29"/>
+      <c r="L51" s="26"/>
+      <c r="M51" s="26"/>
+      <c r="N51" s="26"/>
       <c r="O51" s="18"/>
     </row>
     <row r="52" spans="1:15">
       <c r="A52" s="16"/>
-      <c r="B52" s="27"/>
-      <c r="C52" s="27"/>
-      <c r="D52" s="27"/>
-      <c r="E52" s="27"/>
-      <c r="F52" s="27"/>
-      <c r="G52" s="27"/>
-      <c r="H52" s="27"/>
-      <c r="I52" s="27"/>
-      <c r="J52" s="30"/>
-      <c r="K52" s="30"/>
-      <c r="L52" s="27"/>
-      <c r="M52" s="27"/>
-      <c r="N52" s="27"/>
+      <c r="B52" s="26"/>
+      <c r="C52" s="26"/>
+      <c r="D52" s="26"/>
+      <c r="E52" s="26"/>
+      <c r="F52" s="26"/>
+      <c r="G52" s="26"/>
+      <c r="H52" s="26"/>
+      <c r="I52" s="26"/>
+      <c r="J52" s="29"/>
+      <c r="K52" s="29"/>
+      <c r="L52" s="26"/>
+      <c r="M52" s="26"/>
+      <c r="N52" s="26"/>
       <c r="O52" s="18"/>
     </row>
     <row r="53" spans="1:15">
       <c r="A53" s="16"/>
-      <c r="B53" s="27"/>
-      <c r="C53" s="27"/>
-      <c r="D53" s="27"/>
-      <c r="E53" s="27"/>
-      <c r="F53" s="27"/>
-      <c r="G53" s="27"/>
-      <c r="H53" s="27"/>
-      <c r="I53" s="27"/>
-      <c r="J53" s="30"/>
-      <c r="K53" s="30"/>
-      <c r="L53" s="27"/>
-      <c r="M53" s="27"/>
-      <c r="N53" s="27"/>
+      <c r="B53" s="26"/>
+      <c r="C53" s="26"/>
+      <c r="D53" s="26"/>
+      <c r="E53" s="26"/>
+      <c r="F53" s="26"/>
+      <c r="G53" s="26"/>
+      <c r="H53" s="26"/>
+      <c r="I53" s="26"/>
+      <c r="J53" s="29"/>
+      <c r="K53" s="29"/>
+      <c r="L53" s="26"/>
+      <c r="M53" s="26"/>
+      <c r="N53" s="26"/>
       <c r="O53" s="18"/>
     </row>
     <row r="54" spans="1:15">
       <c r="A54" s="16"/>
-      <c r="B54" s="27"/>
-      <c r="C54" s="27"/>
-      <c r="D54" s="27"/>
-      <c r="E54" s="27"/>
-      <c r="F54" s="27"/>
-      <c r="G54" s="27"/>
-      <c r="H54" s="27"/>
-      <c r="I54" s="27"/>
-      <c r="J54" s="30"/>
-      <c r="K54" s="30"/>
-      <c r="L54" s="27"/>
-      <c r="M54" s="27"/>
-      <c r="N54" s="27"/>
+      <c r="B54" s="26"/>
+      <c r="C54" s="26"/>
+      <c r="D54" s="26"/>
+      <c r="E54" s="26"/>
+      <c r="F54" s="26"/>
+      <c r="G54" s="26"/>
+      <c r="H54" s="26"/>
+      <c r="I54" s="26"/>
+      <c r="J54" s="29"/>
+      <c r="K54" s="29"/>
+      <c r="L54" s="26"/>
+      <c r="M54" s="26"/>
+      <c r="N54" s="26"/>
       <c r="O54" s="18"/>
     </row>
     <row r="55" spans="1:15">
       <c r="A55" s="16"/>
-      <c r="B55" s="27"/>
-      <c r="C55" s="27"/>
-      <c r="D55" s="27"/>
-      <c r="E55" s="27"/>
-      <c r="F55" s="27"/>
-      <c r="G55" s="27"/>
-      <c r="H55" s="27"/>
-      <c r="I55" s="27"/>
-      <c r="J55" s="30"/>
-      <c r="K55" s="30"/>
-      <c r="L55" s="27"/>
-      <c r="M55" s="27"/>
-      <c r="N55" s="27"/>
+      <c r="B55" s="26"/>
+      <c r="C55" s="26"/>
+      <c r="D55" s="26"/>
+      <c r="E55" s="26"/>
+      <c r="F55" s="26"/>
+      <c r="G55" s="26"/>
+      <c r="H55" s="26"/>
+      <c r="I55" s="26"/>
+      <c r="J55" s="29"/>
+      <c r="K55" s="29"/>
+      <c r="L55" s="26"/>
+      <c r="M55" s="26"/>
+      <c r="N55" s="26"/>
       <c r="O55" s="18"/>
     </row>
     <row r="56" spans="1:15">
       <c r="A56" s="16"/>
-      <c r="B56" s="27"/>
-      <c r="C56" s="27"/>
-      <c r="D56" s="27"/>
-      <c r="E56" s="27"/>
-      <c r="F56" s="27"/>
-      <c r="G56" s="27"/>
-      <c r="H56" s="27"/>
-      <c r="I56" s="27"/>
-      <c r="J56" s="30"/>
-      <c r="K56" s="30"/>
-      <c r="L56" s="27"/>
-      <c r="M56" s="27"/>
-      <c r="N56" s="27"/>
+      <c r="B56" s="26"/>
+      <c r="C56" s="26"/>
+      <c r="D56" s="26"/>
+      <c r="E56" s="26"/>
+      <c r="F56" s="26"/>
+      <c r="G56" s="26"/>
+      <c r="H56" s="26"/>
+      <c r="I56" s="26"/>
+      <c r="J56" s="29"/>
+      <c r="K56" s="29"/>
+      <c r="L56" s="26"/>
+      <c r="M56" s="26"/>
+      <c r="N56" s="26"/>
       <c r="O56" s="18"/>
     </row>
     <row r="57" spans="1:15">
       <c r="A57" s="16"/>
-      <c r="B57" s="27"/>
-      <c r="C57" s="27"/>
-      <c r="D57" s="27"/>
-      <c r="E57" s="27"/>
-      <c r="F57" s="27"/>
-      <c r="G57" s="27"/>
-      <c r="H57" s="27"/>
-      <c r="I57" s="27"/>
-      <c r="J57" s="30"/>
-      <c r="K57" s="30"/>
-      <c r="L57" s="27"/>
-      <c r="M57" s="27"/>
-      <c r="N57" s="27"/>
+      <c r="B57" s="26"/>
+      <c r="C57" s="26"/>
+      <c r="D57" s="26"/>
+      <c r="E57" s="26"/>
+      <c r="F57" s="26"/>
+      <c r="G57" s="26"/>
+      <c r="H57" s="26"/>
+      <c r="I57" s="26"/>
+      <c r="J57" s="29"/>
+      <c r="K57" s="29"/>
+      <c r="L57" s="26"/>
+      <c r="M57" s="26"/>
+      <c r="N57" s="26"/>
       <c r="O57" s="18"/>
     </row>
     <row r="58" spans="1:15">
       <c r="A58" s="16"/>
-      <c r="B58" s="27"/>
-      <c r="C58" s="27"/>
-      <c r="D58" s="27"/>
-      <c r="E58" s="27"/>
-      <c r="F58" s="27"/>
-      <c r="G58" s="27"/>
-      <c r="H58" s="27"/>
-      <c r="I58" s="27"/>
-      <c r="J58" s="30"/>
-      <c r="K58" s="30"/>
-      <c r="L58" s="27"/>
-      <c r="M58" s="27"/>
-      <c r="N58" s="27"/>
+      <c r="B58" s="26"/>
+      <c r="C58" s="26"/>
+      <c r="D58" s="26"/>
+      <c r="E58" s="26"/>
+      <c r="F58" s="26"/>
+      <c r="G58" s="26"/>
+      <c r="H58" s="26"/>
+      <c r="I58" s="26"/>
+      <c r="J58" s="29"/>
+      <c r="K58" s="29"/>
+      <c r="L58" s="26"/>
+      <c r="M58" s="26"/>
+      <c r="N58" s="26"/>
       <c r="O58" s="18"/>
     </row>
     <row r="59" spans="1:15">
       <c r="A59" s="16"/>
-      <c r="B59" s="27"/>
-      <c r="C59" s="27"/>
-      <c r="D59" s="27"/>
-      <c r="E59" s="27"/>
-      <c r="F59" s="27"/>
-      <c r="G59" s="27"/>
-      <c r="H59" s="27"/>
-      <c r="I59" s="27"/>
-      <c r="J59" s="30"/>
-      <c r="K59" s="30"/>
-      <c r="L59" s="27"/>
-      <c r="M59" s="27"/>
-      <c r="N59" s="27"/>
+      <c r="B59" s="26"/>
+      <c r="C59" s="26"/>
+      <c r="D59" s="26"/>
+      <c r="E59" s="26"/>
+      <c r="F59" s="26"/>
+      <c r="G59" s="26"/>
+      <c r="H59" s="26"/>
+      <c r="I59" s="26"/>
+      <c r="J59" s="29"/>
+      <c r="K59" s="29"/>
+      <c r="L59" s="26"/>
+      <c r="M59" s="26"/>
+      <c r="N59" s="26"/>
       <c r="O59" s="18"/>
     </row>
     <row r="60" spans="1:15">
       <c r="A60" s="16"/>
-      <c r="B60" s="27"/>
-      <c r="C60" s="27"/>
-      <c r="D60" s="27"/>
-      <c r="E60" s="27"/>
-      <c r="F60" s="27"/>
-      <c r="G60" s="27"/>
-      <c r="H60" s="27"/>
-      <c r="I60" s="27"/>
-      <c r="J60" s="30"/>
-      <c r="K60" s="30"/>
-      <c r="L60" s="27"/>
-      <c r="M60" s="27"/>
-      <c r="N60" s="27"/>
+      <c r="B60" s="26"/>
+      <c r="C60" s="26"/>
+      <c r="D60" s="26"/>
+      <c r="E60" s="26"/>
+      <c r="F60" s="26"/>
+      <c r="G60" s="26"/>
+      <c r="H60" s="26"/>
+      <c r="I60" s="26"/>
+      <c r="J60" s="29"/>
+      <c r="K60" s="29"/>
+      <c r="L60" s="26"/>
+      <c r="M60" s="26"/>
+      <c r="N60" s="26"/>
       <c r="O60" s="18"/>
     </row>
     <row r="61" spans="1:15">
       <c r="A61" s="16"/>
-      <c r="B61" s="27"/>
-      <c r="C61" s="27"/>
-      <c r="D61" s="27"/>
-      <c r="E61" s="27"/>
-      <c r="F61" s="27"/>
-      <c r="G61" s="27"/>
-      <c r="H61" s="27"/>
-      <c r="I61" s="27"/>
-      <c r="J61" s="30"/>
-      <c r="K61" s="30"/>
-      <c r="L61" s="27"/>
-      <c r="M61" s="27"/>
-      <c r="N61" s="27"/>
+      <c r="B61" s="26"/>
+      <c r="C61" s="26"/>
+      <c r="D61" s="26"/>
+      <c r="E61" s="26"/>
+      <c r="F61" s="26"/>
+      <c r="G61" s="26"/>
+      <c r="H61" s="26"/>
+      <c r="I61" s="26"/>
+      <c r="J61" s="29"/>
+      <c r="K61" s="29"/>
+      <c r="L61" s="26"/>
+      <c r="M61" s="26"/>
+      <c r="N61" s="26"/>
       <c r="O61" s="18"/>
     </row>
     <row r="62" spans="1:15">
       <c r="A62" s="16"/>
-      <c r="B62" s="27"/>
-      <c r="C62" s="27"/>
-      <c r="D62" s="27"/>
-      <c r="E62" s="27"/>
-      <c r="F62" s="27"/>
-      <c r="G62" s="27"/>
-      <c r="H62" s="27"/>
-      <c r="I62" s="27"/>
-      <c r="J62" s="30"/>
-      <c r="K62" s="30"/>
-      <c r="L62" s="27"/>
-      <c r="M62" s="27"/>
-      <c r="N62" s="27"/>
+      <c r="B62" s="26"/>
+      <c r="C62" s="26"/>
+      <c r="D62" s="26"/>
+      <c r="E62" s="26"/>
+      <c r="F62" s="26"/>
+      <c r="G62" s="26"/>
+      <c r="H62" s="26"/>
+      <c r="I62" s="26"/>
+      <c r="J62" s="29"/>
+      <c r="K62" s="29"/>
+      <c r="L62" s="26"/>
+      <c r="M62" s="26"/>
+      <c r="N62" s="26"/>
       <c r="O62" s="18"/>
     </row>
     <row r="63" spans="1:15">
       <c r="A63" s="16"/>
-      <c r="B63" s="27"/>
-      <c r="C63" s="27"/>
-      <c r="D63" s="27"/>
-      <c r="E63" s="27"/>
-      <c r="F63" s="27"/>
-      <c r="G63" s="27"/>
-      <c r="H63" s="27"/>
-      <c r="I63" s="27"/>
-      <c r="J63" s="30"/>
-      <c r="K63" s="30"/>
-      <c r="L63" s="27"/>
-      <c r="M63" s="27"/>
-      <c r="N63" s="27"/>
+      <c r="B63" s="26"/>
+      <c r="C63" s="26"/>
+      <c r="D63" s="26"/>
+      <c r="E63" s="26"/>
+      <c r="F63" s="26"/>
+      <c r="G63" s="26"/>
+      <c r="H63" s="26"/>
+      <c r="I63" s="26"/>
+      <c r="J63" s="29"/>
+      <c r="K63" s="29"/>
+      <c r="L63" s="26"/>
+      <c r="M63" s="26"/>
+      <c r="N63" s="26"/>
       <c r="O63" s="18"/>
     </row>
   </sheetData>

--- a/01_組織工作盤查.xlsx
+++ b/01_組織工作盤查.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Development\LeaderMethodology\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35AB0298-26D9-421C-93BC-0202C73620BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBFCCBDD-4566-4AA8-B803-B68E67ABFCA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" activeTab="1" xr2:uid="{6274A289-9C1F-4174-8A94-9BA38FCDDB48}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13776" firstSheet="6" activeTab="10" xr2:uid="{6274A289-9C1F-4174-8A94-9BA38FCDDB48}"/>
   </bookViews>
   <sheets>
     <sheet name="Guide" sheetId="1" r:id="rId1"/>
@@ -75,7 +75,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="248">
   <si>
     <t>文件名稱/Document</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1255,6 +1255,146 @@
   <si>
     <t>請確認以下表格，對應 Sheet 內容
 (黃底部要填寫確認結果)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>機台操作手冊?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>機台尺寸?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>機台有多少螢幕?哪些可以操作?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>機台有多少實體按鈕?(開始、結束、暫停、緊停等)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>機台有幾個入料區?(軌道、門口)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>機台有幾個出料區?(軌道、門口)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>機台運作動作?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>機台有多少感測器?偵測或讀取那些資訊?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>機台位子?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>機台會移動位子?(Setup等)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>機台有多少個補充或退出材料區域?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>機台有多少個退料區域?(不良品或異常時暫放區域)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>機台燈號有那些顏色?意思?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>機台外觀?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>機台有接哪些管線(冷熱水管、排氣管、氮氣缸瓶)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>機台內有多少電腦?作業系統?維護方式?版本?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>機台內有Server?路由?分享器?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>機台內的電腦有安裝哪些軟體?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>機台內的電腦用途?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>機台軟體/硬體</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>機台參數</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>機台參數都存在哪裡?可以匯出?可以解析?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>機台參數如何卡控?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>機台有哪些參數要設置?工作檔?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>機台參數如何管理?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>機台 Setup</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>如何得知要 Setup?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>誰知道要 Setup?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>誰負責 Setup?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Setup 時間?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Setup 條件?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Setup 需要的配件?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Setup 動作流程?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Setup SPEC?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>機台參數設置 SPEC?</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1414,7 +1554,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -1469,6 +1609,19 @@
         <color indexed="64"/>
       </right>
       <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -1604,9 +1757,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1632,15 +1782,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1651,6 +1792,18 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4209,52 +4362,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="66.599999999999994" customHeight="1">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="44" t="s">
         <v>86</v>
       </c>
-      <c r="B1" s="49" t="s">
+      <c r="B1" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49" t="s">
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="48"/>
+      <c r="G1" s="48"/>
+      <c r="H1" s="48" t="s">
         <v>147</v>
       </c>
-      <c r="I1" s="49"/>
-      <c r="J1" s="49"/>
-      <c r="K1" s="49"/>
-      <c r="L1" s="49"/>
-      <c r="M1" s="49"/>
+      <c r="I1" s="48"/>
+      <c r="J1" s="48"/>
+      <c r="K1" s="48"/>
+      <c r="L1" s="48"/>
+      <c r="M1" s="48"/>
     </row>
     <row r="2" spans="1:29" ht="15.6">
-      <c r="A2" s="45"/>
-      <c r="B2" s="46" t="s">
+      <c r="A2" s="44"/>
+      <c r="B2" s="45" t="s">
         <v>92</v>
       </c>
-      <c r="C2" s="46"/>
-      <c r="D2" s="47" t="s">
+      <c r="C2" s="45"/>
+      <c r="D2" s="46" t="s">
         <v>93</v>
       </c>
-      <c r="E2" s="47"/>
-      <c r="F2" s="48" t="s">
+      <c r="E2" s="46"/>
+      <c r="F2" s="47" t="s">
         <v>95</v>
       </c>
-      <c r="G2" s="48"/>
-      <c r="H2" s="46" t="s">
+      <c r="G2" s="47"/>
+      <c r="H2" s="45" t="s">
         <v>92</v>
       </c>
-      <c r="I2" s="46"/>
-      <c r="J2" s="47" t="s">
+      <c r="I2" s="45"/>
+      <c r="J2" s="46" t="s">
         <v>93</v>
       </c>
-      <c r="K2" s="47"/>
-      <c r="L2" s="48" t="s">
+      <c r="K2" s="46"/>
+      <c r="L2" s="47" t="s">
         <v>95</v>
       </c>
-      <c r="M2" s="48"/>
+      <c r="M2" s="47"/>
       <c r="AA2" s="22"/>
       <c r="AB2" s="22"/>
     </row>
@@ -4389,14 +4542,14 @@
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
-  <sheetFormatPr defaultRowHeight="15.6"/>
+  <dimension ref="A1:D42"/>
+  <sheetFormatPr defaultColWidth="34.5546875" defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="7.21875" style="21" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.88671875" style="21" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="30.33203125" style="19" customWidth="1"/>
+    <col min="2" max="2" width="15.33203125" style="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="52" style="19" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7.77734375" style="21" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="8.88671875" style="19"/>
+    <col min="5" max="16384" width="34.5546875" style="19"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -4417,124 +4570,333 @@
       <c r="A2" s="16">
         <v>1</v>
       </c>
-      <c r="B2" s="50" t="s">
+      <c r="B2" s="53" t="s">
         <v>153</v>
       </c>
       <c r="C2" s="20" t="s">
         <v>156</v>
       </c>
-      <c r="D2" s="18"/>
+      <c r="D2" s="54"/>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="16">
         <v>2</v>
       </c>
-      <c r="B3" s="51"/>
+      <c r="B3" s="53"/>
       <c r="C3" s="20" t="s">
         <v>155</v>
       </c>
-      <c r="D3" s="18"/>
+      <c r="D3" s="54"/>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="16">
         <v>3</v>
       </c>
-      <c r="B4" s="51"/>
+      <c r="B4" s="53"/>
       <c r="C4" s="20" t="s">
         <v>154</v>
       </c>
-      <c r="D4" s="18"/>
+      <c r="D4" s="54"/>
     </row>
     <row r="5" spans="1:4" ht="31.2">
       <c r="A5" s="16">
         <v>4</v>
       </c>
-      <c r="B5" s="51"/>
+      <c r="B5" s="53"/>
       <c r="C5" s="20" t="s">
         <v>159</v>
       </c>
-      <c r="D5" s="18"/>
+      <c r="D5" s="54"/>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="16">
-        <v>5</v>
-      </c>
-      <c r="B6" s="41" t="s">
+      <c r="A6" s="16"/>
+      <c r="B6" s="16"/>
+      <c r="C6" s="20" t="s">
+        <v>226</v>
+      </c>
+      <c r="D6" s="54"/>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="16"/>
+      <c r="B7" s="16"/>
+      <c r="C7" s="20" t="s">
+        <v>214</v>
+      </c>
+      <c r="D7" s="54"/>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="16"/>
+      <c r="B8" s="16"/>
+      <c r="C8" s="17" t="s">
+        <v>221</v>
+      </c>
+      <c r="D8" s="54"/>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="16"/>
+      <c r="B9" s="16"/>
+      <c r="C9" s="17" t="s">
+        <v>222</v>
+      </c>
+      <c r="D9" s="54"/>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="16"/>
+      <c r="B10" s="55" t="s">
         <v>160</v>
       </c>
-      <c r="C6" s="20" t="s">
+      <c r="C10" s="20" t="s">
         <v>196</v>
       </c>
-      <c r="D6" s="18"/>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="16">
-        <v>6</v>
-      </c>
-      <c r="B7" s="16"/>
-      <c r="C7" s="20"/>
-      <c r="D7" s="18"/>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="16">
-        <v>7</v>
-      </c>
-      <c r="B8" s="16"/>
-      <c r="C8" s="20"/>
-      <c r="D8" s="18"/>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="16">
-        <v>8</v>
-      </c>
-      <c r="B9" s="50" t="s">
+      <c r="D10" s="54"/>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="16"/>
+      <c r="B11" s="53" t="s">
         <v>197</v>
       </c>
-      <c r="C9" s="20" t="s">
+      <c r="C11" s="20" t="s">
         <v>198</v>
       </c>
-      <c r="D9" s="18"/>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="16">
-        <v>9</v>
-      </c>
-      <c r="B10" s="51"/>
-      <c r="C10" s="20" t="s">
+      <c r="D11" s="54"/>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="16"/>
+      <c r="B12" s="53"/>
+      <c r="C12" s="20" t="s">
         <v>157</v>
       </c>
-      <c r="D10" s="18"/>
-    </row>
-    <row r="11" spans="1:4" ht="31.2">
-      <c r="A11" s="16">
-        <v>10</v>
-      </c>
-      <c r="B11" s="52"/>
-      <c r="C11" s="20" t="s">
+      <c r="D12" s="54"/>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="16"/>
+      <c r="B13" s="53"/>
+      <c r="C13" s="20" t="s">
         <v>158</v>
       </c>
-      <c r="D11" s="18"/>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="16">
-        <v>11</v>
-      </c>
-      <c r="B12" s="16"/>
-      <c r="C12" s="20"/>
-      <c r="D12" s="18"/>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="16">
-        <v>12</v>
-      </c>
-      <c r="B13" s="16"/>
-      <c r="C13" s="20"/>
-      <c r="D13" s="18"/>
+      <c r="D13" s="54"/>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="16"/>
+      <c r="B14" s="53" t="s">
+        <v>232</v>
+      </c>
+      <c r="C14" s="20" t="s">
+        <v>213</v>
+      </c>
+      <c r="D14" s="54"/>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="16"/>
+      <c r="B15" s="53"/>
+      <c r="C15" s="20" t="s">
+        <v>214</v>
+      </c>
+      <c r="D15" s="54"/>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="16"/>
+      <c r="B16" s="53"/>
+      <c r="C16" s="17" t="s">
+        <v>215</v>
+      </c>
+      <c r="D16" s="54"/>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="16"/>
+      <c r="B17" s="53"/>
+      <c r="C17" s="17" t="s">
+        <v>228</v>
+      </c>
+      <c r="D17" s="54"/>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="16"/>
+      <c r="B18" s="53"/>
+      <c r="C18" s="56" t="s">
+        <v>230</v>
+      </c>
+      <c r="D18" s="54"/>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="16"/>
+      <c r="B19" s="53"/>
+      <c r="C19" s="56" t="s">
+        <v>231</v>
+      </c>
+      <c r="D19" s="54"/>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="16"/>
+      <c r="B20" s="53"/>
+      <c r="C20" s="17" t="s">
+        <v>229</v>
+      </c>
+      <c r="D20" s="54"/>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="16"/>
+      <c r="B21" s="53"/>
+      <c r="C21" s="17" t="s">
+        <v>216</v>
+      </c>
+      <c r="D21" s="54"/>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="16"/>
+      <c r="B22" s="53"/>
+      <c r="C22" s="17" t="s">
+        <v>217</v>
+      </c>
+      <c r="D22" s="54"/>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="16"/>
+      <c r="B23" s="53"/>
+      <c r="C23" s="17" t="s">
+        <v>218</v>
+      </c>
+      <c r="D23" s="54"/>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="16"/>
+      <c r="B24" s="53"/>
+      <c r="C24" s="17" t="s">
+        <v>223</v>
+      </c>
+      <c r="D24" s="54"/>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="16"/>
+      <c r="B25" s="53"/>
+      <c r="C25" s="17" t="s">
+        <v>224</v>
+      </c>
+      <c r="D25" s="54"/>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="16"/>
+      <c r="B26" s="53"/>
+      <c r="C26" s="17" t="s">
+        <v>219</v>
+      </c>
+      <c r="D26" s="54"/>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="16"/>
+      <c r="B27" s="53"/>
+      <c r="C27" s="17" t="s">
+        <v>220</v>
+      </c>
+      <c r="D27" s="54"/>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="16"/>
+      <c r="B28" s="53"/>
+      <c r="C28" s="17" t="s">
+        <v>225</v>
+      </c>
+      <c r="D28" s="54"/>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="16"/>
+      <c r="B29" s="53"/>
+      <c r="C29" s="17" t="s">
+        <v>227</v>
+      </c>
+      <c r="D29" s="54"/>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="16"/>
+      <c r="B30" s="53" t="s">
+        <v>233</v>
+      </c>
+      <c r="C30" s="56" t="s">
+        <v>247</v>
+      </c>
+      <c r="D30" s="54"/>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="16"/>
+      <c r="B31" s="53"/>
+      <c r="C31" s="56" t="s">
+        <v>236</v>
+      </c>
+      <c r="D31" s="54"/>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="16"/>
+      <c r="B32" s="53"/>
+      <c r="C32" s="56" t="s">
+        <v>234</v>
+      </c>
+      <c r="D32" s="54"/>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="16"/>
+      <c r="B33" s="53"/>
+      <c r="C33" s="56" t="s">
+        <v>235</v>
+      </c>
+      <c r="D33" s="54"/>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" s="16"/>
+      <c r="B34" s="53"/>
+      <c r="C34" s="56" t="s">
+        <v>237</v>
+      </c>
+      <c r="D34" s="54"/>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="B35" s="21" t="s">
+        <v>238</v>
+      </c>
+      <c r="C35" s="19" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="C36" s="19" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="C37" s="19" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="C38" s="19" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="C39" s="19" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="C40" s="19" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="C41" s="19" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="C42" s="19" t="s">
+        <v>245</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="4">
     <mergeCell ref="B2:B5"/>
-    <mergeCell ref="B9:B11"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="B14:B29"/>
+    <mergeCell ref="B30:B34"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4590,7 +4952,7 @@
       <c r="A2" s="16">
         <v>1</v>
       </c>
-      <c r="B2" s="53" t="s">
+      <c r="B2" s="49" t="s">
         <v>162</v>
       </c>
       <c r="C2" s="20" t="s">
@@ -4605,7 +4967,7 @@
       <c r="A3" s="16">
         <v>2</v>
       </c>
-      <c r="B3" s="54"/>
+      <c r="B3" s="50"/>
       <c r="C3" s="20" t="s">
         <v>179</v>
       </c>
@@ -4618,7 +4980,7 @@
       <c r="A4" s="16">
         <v>3</v>
       </c>
-      <c r="B4" s="54"/>
+      <c r="B4" s="50"/>
       <c r="C4" s="20" t="s">
         <v>209</v>
       </c>
@@ -4631,7 +4993,7 @@
       <c r="A5" s="16">
         <v>4</v>
       </c>
-      <c r="B5" s="54"/>
+      <c r="B5" s="50"/>
       <c r="C5" s="20" t="s">
         <v>192</v>
       </c>
@@ -4644,7 +5006,7 @@
       <c r="A6" s="16">
         <v>5</v>
       </c>
-      <c r="B6" s="54"/>
+      <c r="B6" s="50"/>
       <c r="C6" s="20" t="s">
         <v>182</v>
       </c>
@@ -4657,7 +5019,7 @@
       <c r="A7" s="16">
         <v>6</v>
       </c>
-      <c r="B7" s="54"/>
+      <c r="B7" s="50"/>
       <c r="C7" s="20" t="s">
         <v>193</v>
       </c>
@@ -4670,7 +5032,7 @@
       <c r="A8" s="16">
         <v>7</v>
       </c>
-      <c r="B8" s="54"/>
+      <c r="B8" s="50"/>
       <c r="C8" s="20" t="s">
         <v>183</v>
       </c>
@@ -4683,7 +5045,7 @@
       <c r="A9" s="16">
         <v>8</v>
       </c>
-      <c r="B9" s="54"/>
+      <c r="B9" s="50"/>
       <c r="C9" s="20" t="s">
         <v>210</v>
       </c>
@@ -4696,7 +5058,7 @@
       <c r="A10" s="16">
         <v>9</v>
       </c>
-      <c r="B10" s="54"/>
+      <c r="B10" s="50"/>
       <c r="C10" s="20" t="s">
         <v>184</v>
       </c>
@@ -4709,7 +5071,7 @@
       <c r="A11" s="16">
         <v>10</v>
       </c>
-      <c r="B11" s="54"/>
+      <c r="B11" s="50"/>
       <c r="C11" s="20" t="s">
         <v>163</v>
       </c>
@@ -4722,7 +5084,7 @@
       <c r="A12" s="16">
         <v>11</v>
       </c>
-      <c r="B12" s="54"/>
+      <c r="B12" s="50"/>
       <c r="C12" s="20" t="s">
         <v>190</v>
       </c>
@@ -4735,7 +5097,7 @@
       <c r="A13" s="16">
         <v>12</v>
       </c>
-      <c r="B13" s="54"/>
+      <c r="B13" s="50"/>
       <c r="C13" s="20" t="s">
         <v>186</v>
       </c>
@@ -4748,7 +5110,7 @@
       <c r="A14" s="16">
         <v>13</v>
       </c>
-      <c r="B14" s="54"/>
+      <c r="B14" s="50"/>
       <c r="C14" s="20" t="s">
         <v>194</v>
       </c>
@@ -4761,7 +5123,7 @@
       <c r="A15" s="16">
         <v>14</v>
       </c>
-      <c r="B15" s="54"/>
+      <c r="B15" s="50"/>
       <c r="C15" s="17" t="s">
         <v>195</v>
       </c>
@@ -4774,7 +5136,7 @@
       <c r="A16" s="16">
         <v>15</v>
       </c>
-      <c r="B16" s="54"/>
+      <c r="B16" s="50"/>
       <c r="C16" s="17" t="s">
         <v>188</v>
       </c>
@@ -4787,7 +5149,7 @@
       <c r="A17" s="16">
         <v>16</v>
       </c>
-      <c r="B17" s="54"/>
+      <c r="B17" s="50"/>
       <c r="C17" s="17" t="s">
         <v>189</v>
       </c>
@@ -4798,7 +5160,7 @@
       <c r="A18" s="16">
         <v>17</v>
       </c>
-      <c r="B18" s="54"/>
+      <c r="B18" s="50"/>
       <c r="C18" s="17" t="s">
         <v>164</v>
       </c>
@@ -4811,7 +5173,7 @@
       <c r="A19" s="16">
         <v>18</v>
       </c>
-      <c r="B19" s="55"/>
+      <c r="B19" s="51"/>
       <c r="C19" s="17" t="s">
         <v>187</v>
       </c>
@@ -4822,7 +5184,7 @@
       <c r="A20" s="16">
         <v>19</v>
       </c>
-      <c r="B20" s="56" t="s">
+      <c r="B20" s="52" t="s">
         <v>199</v>
       </c>
       <c r="C20" s="17" t="s">
@@ -4835,7 +5197,7 @@
       <c r="A21" s="16">
         <v>20</v>
       </c>
-      <c r="B21" s="56"/>
+      <c r="B21" s="52"/>
       <c r="C21" s="17" t="s">
         <v>204</v>
       </c>
@@ -4846,7 +5208,7 @@
       <c r="A22" s="16">
         <v>21</v>
       </c>
-      <c r="B22" s="56"/>
+      <c r="B22" s="52"/>
       <c r="C22" s="17" t="s">
         <v>206</v>
       </c>
@@ -4857,7 +5219,7 @@
       <c r="A23" s="16">
         <v>22</v>
       </c>
-      <c r="B23" s="56"/>
+      <c r="B23" s="52"/>
       <c r="C23" s="20" t="s">
         <v>205</v>
       </c>
@@ -4868,7 +5230,7 @@
       <c r="A24" s="16">
         <v>23</v>
       </c>
-      <c r="B24" s="56"/>
+      <c r="B24" s="52"/>
       <c r="C24" s="17" t="s">
         <v>201</v>
       </c>
@@ -4879,7 +5241,7 @@
       <c r="A25" s="16">
         <v>24</v>
       </c>
-      <c r="B25" s="56"/>
+      <c r="B25" s="52"/>
       <c r="C25" s="17" t="s">
         <v>200</v>
       </c>
@@ -4890,7 +5252,7 @@
       <c r="A26" s="16">
         <v>25</v>
       </c>
-      <c r="B26" s="56"/>
+      <c r="B26" s="52"/>
       <c r="C26" s="17" t="s">
         <v>203</v>
       </c>
@@ -4901,7 +5263,7 @@
       <c r="A27" s="16">
         <v>26</v>
       </c>
-      <c r="B27" s="56"/>
+      <c r="B27" s="52"/>
       <c r="C27" s="17" t="s">
         <v>207</v>
       </c>
@@ -5247,18 +5609,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="33" customHeight="1">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="43" t="s">
         <v>55</v>
       </c>
-      <c r="B1" s="42" t="s">
+      <c r="B1" s="41" t="s">
         <v>212</v>
       </c>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="44"/>
+      <c r="A2" s="43"/>
       <c r="B2" s="6" t="s">
         <v>18</v>
       </c>
@@ -5273,7 +5635,7 @@
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="44"/>
+      <c r="A3" s="43"/>
       <c r="B3" s="6">
         <v>1</v>
       </c>
@@ -5284,7 +5646,7 @@
       <c r="E3" s="1"/>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="44"/>
+      <c r="A4" s="43"/>
       <c r="B4" s="6">
         <v>2</v>
       </c>
@@ -5295,7 +5657,7 @@
       <c r="E4" s="1"/>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="44"/>
+      <c r="A5" s="43"/>
       <c r="B5" s="6">
         <v>3</v>
       </c>
@@ -5306,7 +5668,7 @@
       <c r="E5" s="1"/>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="44"/>
+      <c r="A6" s="43"/>
       <c r="B6" s="6">
         <v>4</v>
       </c>
@@ -5320,18 +5682,18 @@
       <c r="B7" s="9"/>
     </row>
     <row r="8" spans="1:5" ht="31.8" customHeight="1">
-      <c r="A8" s="44" t="s">
+      <c r="A8" s="43" t="s">
         <v>56</v>
       </c>
-      <c r="B8" s="42" t="s">
+      <c r="B8" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="C8" s="43"/>
-      <c r="D8" s="43"/>
-      <c r="E8" s="43"/>
+      <c r="C8" s="42"/>
+      <c r="D8" s="42"/>
+      <c r="E8" s="42"/>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="44"/>
+      <c r="A9" s="43"/>
       <c r="B9" s="6" t="s">
         <v>18</v>
       </c>
@@ -5346,7 +5708,7 @@
       </c>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="44"/>
+      <c r="A10" s="43"/>
       <c r="B10" s="6" t="s">
         <v>58</v>
       </c>
@@ -5357,7 +5719,7 @@
       <c r="E10" s="1"/>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="44"/>
+      <c r="A11" s="43"/>
       <c r="B11" s="6" t="s">
         <v>59</v>
       </c>
@@ -5368,7 +5730,7 @@
       <c r="E11" s="1"/>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="44"/>
+      <c r="A12" s="43"/>
       <c r="B12" s="6" t="s">
         <v>60</v>
       </c>
@@ -5379,7 +5741,7 @@
       <c r="E12" s="1"/>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="44"/>
+      <c r="A13" s="43"/>
       <c r="B13" s="6" t="s">
         <v>61</v>
       </c>
@@ -5390,11 +5752,11 @@
       <c r="E13" s="1"/>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="44"/>
+      <c r="A14" s="43"/>
       <c r="B14" s="9"/>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="44"/>
+      <c r="A15" s="43"/>
       <c r="B15" s="9"/>
     </row>
     <row r="16" spans="1:5">
@@ -5416,7 +5778,7 @@
           <x14:formula1>
             <xm:f>TB_Check!B:B</xm:f>
           </x14:formula1>
-          <xm:sqref>D1:D6 D8:D13 D17:D1048576</xm:sqref>
+          <xm:sqref>D1:D6 D17:D1048576 D8:D13</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
